--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -760,7 +760,7 @@
         <v>2.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -769,7 +769,7 @@
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>2.08</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H3" t="n">
         <v>2.88</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>3.6</v>
@@ -1154,13 +1154,13 @@
         <v>2.22</v>
       </c>
       <c r="I4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1566,13 +1566,13 @@
         <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
         <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.6</v>
@@ -1590,7 +1590,7 @@
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
@@ -1599,7 +1599,7 @@
         <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
         <v>8.800000000000001</v>
@@ -1647,10 +1647,10 @@
         <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H7" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -763,7 +763,7 @@
         <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>4.9</v>
@@ -772,7 +772,7 @@
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.33</v>
+        <v>2.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I4" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.56</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.52</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
         <v>2.82</v>
@@ -1587,16 +1587,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
         <v>14</v>
@@ -1608,25 +1608,25 @@
         <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
         <v>19</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>14.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
@@ -1635,10 +1635,10 @@
         <v>60</v>
       </c>
       <c r="AN6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
         <v>18.5</v>
@@ -1647,10 +1647,10 @@
         <v>13.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1674,7 +1674,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BB6" t="n">
         <v>32</v>
@@ -1689,14 +1689,14 @@
         <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -766,7 +766,7 @@
         <v>3.05</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
         <v>2.52</v>
@@ -966,7 +966,7 @@
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
         <v>3.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I6" t="n">
         <v>2.88</v>
       </c>
       <c r="J6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>13</v>
@@ -1620,13 +1620,13 @@
         <v>14.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
@@ -1638,7 +1638,7 @@
         <v>17</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP6" t="n">
         <v>18.5</v>
@@ -1650,7 +1650,7 @@
         <v>18</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1662,7 +1662,7 @@
         <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>17</v>
@@ -1680,7 +1680,7 @@
         <v>32</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
         <v>25</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>2.18</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>1.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 07:59:54</t>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>3.45</v>
       </c>
       <c r="G3" t="n">
-        <v>2.52</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 07:59:54</t>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>1.49</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.48</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 07:59:54</t>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Shanghai Port FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS5" t="n">
         <v>2.08</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 07:59:54</t>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,378 +1519,1348 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Tianjin Jinmen Tiger FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.54</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.56</v>
+        <v>5.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.86</v>
+        <v>1.72</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="AQ6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE6" t="n">
         <v>48</v>
       </c>
-      <c r="AB6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>50</v>
-      </c>
       <c r="BF6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 07:59:54</t>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Austrian Bundesliga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SCR Altach</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WSG Wattens</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Austrian Bundesliga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FC Blau Weiss Linz</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RZ Pellets WAC</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Swedish Superettan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Orebro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Norrkoping</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Austrian Bundesliga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Venezuelan Primera Division</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Puerto Cabello</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Trujillanos</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F12" t="n">
         <v>1.04</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G12" t="n">
         <v>1.43</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H12" t="n">
         <v>3.35</v>
       </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.35</v>
       </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-04-19 07:59:54</t>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-19 10:23:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -772,37 +772,37 @@
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
         <v>1.84</v>
@@ -811,116 +811,116 @@
         <v>1.37</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
         <v>1.93</v>
@@ -966,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -978,19 +978,19 @@
         <v>5.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
         <v>1.54</v>
@@ -999,7 +999,7 @@
         <v>2.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1014,13 +1014,13 @@
         <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1047,7 +1047,7 @@
         <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
@@ -1056,28 +1056,28 @@
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
         <v>14.5</v>
@@ -1095,7 +1095,7 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC3" t="n">
         <v>4.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H4" t="n">
         <v>6.4</v>
@@ -1163,40 +1163,40 @@
         <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="X4" t="n">
         <v>36</v>
@@ -1235,7 +1235,7 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK4" t="n">
         <v>15</v>
@@ -1253,13 +1253,13 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS4" t="n">
         <v>10</v>
@@ -1271,10 +1271,10 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1295,10 +1295,10 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
         <v>4.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>5.7</v>
@@ -1354,155 +1354,155 @@
         <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.61</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
         <v>65</v>
       </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AJ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV5" t="n">
         <v>17</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>15</v>
       </c>
-      <c r="AD5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.94</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.04</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.94</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.92</v>
+        <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.08</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.08</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AW6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>27</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>70</v>
+        <v>4.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>48</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
         <v>3.8</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
         <v>2.58</v>
@@ -2512,7 +2512,7 @@
         <v>2.84</v>
       </c>
       <c r="I11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2527,7 +2527,7 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
@@ -2569,7 +2569,7 @@
         <v>48</v>
       </c>
       <c r="AB11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC11" t="n">
         <v>8.6</v>
@@ -2578,7 +2578,7 @@
         <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF11" t="n">
         <v>19</v>
@@ -2590,13 +2590,13 @@
         <v>14.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
         <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
         <v>34</v>
@@ -2605,7 +2605,7 @@
         <v>60</v>
       </c>
       <c r="AN11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
         <v>19.5</v>
@@ -2620,13 +2620,13 @@
         <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT11" t="n">
         <v>13</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +769,7 @@
         <v>2.18</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -787,10 +787,10 @@
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.56</v>
@@ -799,10 +799,10 @@
         <v>2.48</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
         <v>1.84</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="I3" t="n">
         <v>2.14</v>
@@ -1002,7 +1002,7 @@
         <v>1.87</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
         <v>29</v>
@@ -1068,13 +1068,13 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
         <v>9.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
         <v>4.9</v>
@@ -1184,13 +1184,13 @@
         <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,40 +1363,40 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>50</v>
@@ -1408,16 +1408,16 @@
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>70</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
@@ -1429,16 +1429,16 @@
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
         <v>8.800000000000001</v>
@@ -1453,34 +1453,34 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BB5" t="n">
         <v>14</v>
@@ -1489,20 +1489,20 @@
         <v>13.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
         <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
         <v>1.98</v>
@@ -1572,7 +1572,7 @@
         <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
         <v>1.68</v>
@@ -1602,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>12</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>36</v>
@@ -1629,7 +1629,7 @@
         <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>95</v>
@@ -1641,10 +1641,10 @@
         <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
         <v>9.800000000000001</v>
@@ -1653,10 +1653,10 @@
         <v>16</v>
       </c>
       <c r="AT6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>8.800000000000001</v>
@@ -1665,7 +1665,7 @@
         <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -1674,36 +1674,36 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC6" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC6" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P7" t="n">
         <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X10" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB10" t="n">
         <v>2.24</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2.86</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>22</v>
       </c>
-      <c r="AA11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>38</v>
-      </c>
       <c r="AK11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AN11" t="n">
         <v>16.5</v>
       </c>
       <c r="AO11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>19.5</v>
       </c>
-      <c r="AP11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BB11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
         <v>42</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,184 +2683,1542 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>1.43</v>
+        <v>2.22</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Danish 1st Division</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hillerod Fodbold</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lyngby</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Austrian Bundesliga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SV Ried</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1000</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="AN17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trujillanos</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q19" t="n">
         <v>1.01</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-04-19 12:41:44</t>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,10 +853,10 @@
         <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
         <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
         <v>4.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.03</v>
@@ -1014,7 +1014,7 @@
         <v>18.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB3" t="n">
         <v>23</v>
@@ -1047,7 +1047,7 @@
         <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>70</v>
@@ -1056,7 +1056,7 @@
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -1068,7 +1068,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
         <v>16.5</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1095,16 +1095,16 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>19.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
         <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
@@ -1199,7 +1199,7 @@
         <v>2.9</v>
       </c>
       <c r="X4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
         <v>34</v>
@@ -1232,7 +1232,7 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ4" t="n">
         <v>14.5</v>
@@ -1259,7 +1259,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AS4" t="n">
         <v>10</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1357,7 +1357,7 @@
         <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1375,7 +1375,7 @@
         <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
         <v>2.5</v>
@@ -1387,10 +1387,10 @@
         <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
         <v>27</v>
@@ -1414,7 +1414,7 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>13.5</v>
@@ -1492,7 +1492,7 @@
         <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
         <v>6.2</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1539,16 +1539,16 @@
         <v>4.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
@@ -1566,7 +1566,7 @@
         <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1581,7 +1581,7 @@
         <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
         <v>1.26</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
         <v>3.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,37 +1751,37 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
         <v>4.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="n">
         <v>11.5</v>
@@ -1793,7 +1793,7 @@
         <v>95</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
         <v>7.2</v>
@@ -1811,25 +1811,25 @@
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>70</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM7" t="n">
         <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>65</v>
@@ -1862,7 +1862,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
@@ -1877,20 +1877,20 @@
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BG7" t="n">
         <v>42</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
         <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1939,7 +1939,7 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1954,13 +1954,13 @@
         <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
         <v>1.79</v>
@@ -1969,10 +1969,10 @@
         <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2041,7 +2041,7 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU8" t="n">
         <v>5.6</v>
@@ -2059,7 +2059,7 @@
         <v>3.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.7</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>4.1</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2148,10 +2148,10 @@
         <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
         <v>3.4</v>
@@ -2199,10 +2199,10 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ9" t="n">
         <v>34</v>
@@ -2217,10 +2217,10 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP9" t="n">
         <v>12</v>
@@ -2229,10 +2229,10 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2253,39 +2253,39 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB10" t="n">
         <v>20</v>
       </c>
-      <c r="Z10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BC10" t="n">
         <v>20</v>
       </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="BD10" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG10" t="n">
         <v>70</v>
       </c>
-      <c r="AK10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.95</v>
+        <v>2.78</v>
       </c>
       <c r="G11" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.45</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>2.04</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>2.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>2.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>30</v>
+        <v>2.12</v>
       </c>
       <c r="AS11" t="n">
-        <v>40</v>
+        <v>2.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>1.98</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>2.04</v>
       </c>
       <c r="AW11" t="n">
-        <v>32</v>
+        <v>2.16</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.800000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>34</v>
+        <v>2.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>2.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>2.22</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>2.24</v>
       </c>
       <c r="BE11" t="n">
-        <v>42</v>
+        <v>2.34</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>2.34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
         <v>3.85</v>
@@ -2715,13 +2715,13 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
         <v>1.38</v>
@@ -2736,10 +2736,10 @@
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -2769,10 +2769,10 @@
         <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>15.5</v>
@@ -2781,7 +2781,7 @@
         <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>80</v>
@@ -2793,19 +2793,19 @@
         <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
         <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
         <v>9.800000000000001</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
         <v>2.62</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
         <v>3.2</v>
@@ -2924,16 +2924,16 @@
         <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U13" t="n">
         <v>2.02</v>
@@ -2960,7 +2960,7 @@
         <v>9.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
         <v>13.5</v>
@@ -2978,7 +2978,7 @@
         <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
         <v>38</v>
@@ -3005,7 +3005,7 @@
         <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
         <v>48</v>
@@ -3047,14 +3047,14 @@
         <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG13" t="n">
         <v>36</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H14" t="n">
         <v>1.87</v>
@@ -3103,16 +3103,16 @@
         <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
         <v>1.84</v>
@@ -3121,134 +3121,134 @@
         <v>1.86</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -3297,16 +3297,16 @@
         <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P15" t="n">
         <v>1.76</v>
@@ -3315,141 +3315,141 @@
         <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.56</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.84</v>
+        <v>1.89</v>
       </c>
       <c r="I16" t="n">
-        <v>2.86</v>
+        <v>2.12</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.85</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF16" t="n">
         <v>38</v>
       </c>
-      <c r="AK16" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.72</v>
+        <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.76</v>
+        <v>5.5</v>
       </c>
       <c r="H17" t="n">
-        <v>2.88</v>
+        <v>1.82</v>
       </c>
       <c r="I17" t="n">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.55</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,378 +3847,1348 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Academia de Balompie Bol</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>1.33</v>
+        <v>420</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>1.09</v>
       </c>
       <c r="I18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>6.4</v>
+        <v>1.09</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>95</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Venezuelan Primera Division</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Puerto Cabello</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Trujillanos</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-04-19 14:57:30</t>
+      <c r="F24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>19</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -889,7 +889,7 @@
         <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,19 +898,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
         <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>19</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT3" t="n">
         <v>16.5</v>
@@ -1083,7 +1083,7 @@
         <v>14.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -1095,13 +1095,13 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.9</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE3" t="n">
         <v>4.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
         <v>6.4</v>
@@ -1184,7 +1184,7 @@
         <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
@@ -1196,7 +1196,7 @@
         <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1256,7 +1256,7 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
         <v>50</v>
@@ -1271,7 +1271,7 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW4" t="n">
         <v>9.4</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1301,14 +1301,14 @@
         <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
         <v>50</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G5" t="n">
         <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>1.27</v>
@@ -1363,37 +1363,37 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
         <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y5" t="n">
         <v>24</v>
@@ -1423,7 +1423,7 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
@@ -1441,7 +1441,7 @@
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO5" t="n">
         <v>60</v>
@@ -1453,56 +1453,56 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BG5" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -1674,19 +1674,19 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
         <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
         <v>4.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
@@ -1742,7 +1742,7 @@
         <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1778,7 +1778,7 @@
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
         <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1954,7 +1954,7 @@
         <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
@@ -1972,7 +1972,7 @@
         <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2032,7 +2032,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
@@ -2041,10 +2041,10 @@
         <v>4.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -2056,16 +2056,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="BA8" t="n">
         <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BC8" t="n">
         <v>20</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H9" t="n">
         <v>3.2</v>
@@ -2166,7 +2166,7 @@
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
         <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
         <v>1.1</v>
@@ -2339,7 +2339,7 @@
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
         <v>2.24</v>
@@ -2360,7 +2360,7 @@
         <v>1.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
         <v>11</v>
@@ -2417,7 +2417,7 @@
         <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>13.5</v>
@@ -2447,7 +2447,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA10" t="n">
         <v>65</v>
@@ -2468,11 +2468,11 @@
         <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
         <v>2.48</v>
@@ -2548,7 +2548,7 @@
         <v>1.45</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
         <v>1.67</v>
@@ -2581,7 +2581,7 @@
         <v>30</v>
       </c>
       <c r="AF11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG11" t="n">
         <v>20</v>
@@ -2614,37 +2614,37 @@
         <v>2.18</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AV11" t="n">
         <v>2.04</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AX11" t="n">
         <v>2.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AZ11" t="n">
         <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BB11" t="n">
         <v>2.26</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>1.38</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
         <v>2.1</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2933,16 +2933,16 @@
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V13" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
@@ -2981,7 +2981,7 @@
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
@@ -2993,10 +2993,10 @@
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
@@ -3050,11 +3050,11 @@
         <v>26</v>
       </c>
       <c r="BG13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -3300,7 +3300,7 @@
         <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
         <v>3.2</v>
@@ -3318,7 +3318,7 @@
         <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
@@ -3387,10 +3387,10 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="AR15" t="n">
         <v>18</v>
@@ -3399,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
         <v>11</v>
@@ -3417,7 +3417,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>1.89</v>
       </c>
       <c r="I16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>3.35</v>
@@ -3491,7 +3491,7 @@
         <v>4.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.06</v>
@@ -3506,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
         <v>1.39</v>
@@ -3521,10 +3521,10 @@
         <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I17" t="n">
         <v>1.86</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
@@ -3700,7 +3700,7 @@
         <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
@@ -3724,34 +3724,34 @@
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="H18" t="n">
         <v>1.09</v>
@@ -3885,13 +3885,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O18" t="n">
         <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Q18" t="n">
         <v>1.14</v>
@@ -3969,52 +3969,52 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
         <v>14</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
         <v>12.5</v>
@@ -4163,10 +4163,10 @@
         <v>19</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
         <v>20</v>
@@ -4196,13 +4196,13 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB19" t="n">
         <v>34</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
         <v>29</v>
@@ -4214,11 +4214,11 @@
         <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.32</v>
       </c>
       <c r="G20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K20" t="n">
         <v>6.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.24</v>
@@ -4297,10 +4297,10 @@
         <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="X20" t="n">
         <v>30</v>
@@ -4360,7 +4360,7 @@
         <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AR20" t="n">
         <v>38</v>
@@ -4372,7 +4372,7 @@
         <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV20" t="n">
         <v>34</v>
@@ -4387,7 +4387,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
         <v>40</v>
@@ -4405,14 +4405,14 @@
         <v>42</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG20" t="n">
         <v>46</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="n">
         <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I21" t="n">
         <v>2.94</v>
@@ -4461,7 +4461,7 @@
         <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -4476,7 +4476,7 @@
         <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
         <v>1.41</v>
@@ -4494,7 +4494,7 @@
         <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X21" t="n">
         <v>14.5</v>
@@ -4506,7 +4506,7 @@
         <v>19.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB21" t="n">
         <v>12.5</v>
@@ -4527,7 +4527,7 @@
         <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
@@ -4548,7 +4548,7 @@
         <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
         <v>13.5</v>
@@ -4566,7 +4566,7 @@
         <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
         <v>11.5</v>
@@ -4575,7 +4575,7 @@
         <v>27</v>
       </c>
       <c r="AX21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
@@ -4599,14 +4599,14 @@
         <v>34</v>
       </c>
       <c r="BF21" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG21" t="n">
         <v>22</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
         <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>6.4</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
         <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
@@ -4843,158 +4843,158 @@
         <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
         <v>1000</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="J24" t="n">
         <v>4.7</v>
@@ -5043,16 +5043,16 @@
         <v>6.2</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
         <v>1.75</v>
@@ -5061,134 +5061,134 @@
         <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -781,7 +781,7 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -793,7 +793,7 @@
         <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
         <v>2.48</v>
@@ -805,7 +805,7 @@
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
         <v>1.37</v>
@@ -817,10 +817,10 @@
         <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
@@ -901,7 +901,7 @@
         <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC2" t="n">
         <v>4.9</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         <v>1.54</v>
       </c>
       <c r="U3" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.87</v>
@@ -1011,7 +1011,7 @@
         <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
@@ -1104,7 +1104,7 @@
         <v>4.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>19.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1169,28 +1169,28 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q4" t="n">
         <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.27</v>
@@ -1369,19 +1369,19 @@
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
         <v>2.52</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
         <v>2.16</v>
@@ -1390,7 +1390,7 @@
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1423,16 +1423,16 @@
         <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
         <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
@@ -1441,7 +1441,7 @@
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO5" t="n">
         <v>60</v>
@@ -1453,19 +1453,19 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>6.4</v>
@@ -1489,20 +1489,20 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF5" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
@@ -1757,7 +1757,7 @@
         <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
         <v>2.36</v>
@@ -1778,7 +1778,7 @@
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1829,7 +1829,7 @@
         <v>160</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
         <v>65</v>
@@ -1844,7 +1844,7 @@
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1856,7 +1856,7 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX7" t="n">
         <v>9.800000000000001</v>
@@ -1868,10 +1868,10 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
@@ -1880,17 +1880,17 @@
         <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
         <v>42</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1957,16 +1957,16 @@
         <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
         <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="V8" t="n">
         <v>1.31</v>
@@ -2002,13 +2002,13 @@
         <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>38</v>
@@ -2032,7 +2032,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
@@ -2059,10 +2059,10 @@
         <v>3.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -2071,20 +2071,20 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>2.44</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I9" t="n">
         <v>3.5</v>
@@ -2178,7 +2178,7 @@
         <v>25</v>
       </c>
       <c r="AA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
@@ -2190,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="AE9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF9" t="n">
         <v>16.5</v>
@@ -2199,7 +2199,7 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
         <v>50</v>
@@ -2211,13 +2211,13 @@
         <v>27</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM9" t="n">
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>40</v>
@@ -2229,10 +2229,10 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT9" t="n">
         <v>8.6</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2253,39 +2253,39 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
         <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>6.6</v>
       </c>
       <c r="BC9" t="n">
         <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
         <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X10" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD10" t="n">
         <v>2.24</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>38</v>
-      </c>
       <c r="BE10" t="n">
-        <v>42</v>
+        <v>2.34</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="BG10" t="n">
-        <v>75</v>
+        <v>2.34</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="I11" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB11" t="n">
         <v>20</v>
       </c>
-      <c r="Z11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="BC11" t="n">
         <v>20</v>
       </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BD11" t="n">
-        <v>2.24</v>
+        <v>38</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.34</v>
+        <v>42</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.34</v>
+        <v>75</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.45</v>
@@ -2724,19 +2724,19 @@
         <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P12" t="n">
         <v>1.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R12" t="n">
         <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T12" t="n">
         <v>1.86</v>
@@ -2766,7 +2766,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>20</v>
@@ -2802,7 +2802,7 @@
         <v>23</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2826,10 +2826,10 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
         <v>8</v>
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2847,20 +2847,20 @@
         <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>46</v>
+        <v>4.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G14" t="n">
         <v>5.2</v>
@@ -3100,7 +3100,7 @@
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,25 +3109,25 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
         <v>1.94</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -3297,10 +3297,10 @@
         <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
         <v>3.2</v>
@@ -3318,7 +3318,7 @@
         <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
@@ -3327,10 +3327,10 @@
         <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
         <v>14.5</v>
@@ -3387,10 +3387,10 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
         <v>18</v>
@@ -3399,7 +3399,7 @@
         <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
         <v>5.8</v>
@@ -3417,7 +3417,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>5.1</v>
       </c>
       <c r="H16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I16" t="n">
         <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,19 +3581,19 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
@@ -3602,41 +3602,41 @@
         <v>8</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="BG16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>4.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H17" t="n">
         <v>1.81</v>
@@ -3691,13 +3691,13 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
         <v>2.04</v>
@@ -3721,13 +3721,13 @@
         <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA17" t="n">
         <v>30</v>
@@ -3748,7 +3748,7 @@
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH17" t="n">
         <v>30</v>
@@ -3775,19 +3775,19 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
         <v>5.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
         <v>12.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU17" t="n">
         <v>5.3</v>
@@ -3799,38 +3799,38 @@
         <v>12.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AY17" t="n">
         <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
         <v>1000</v>
@@ -3885,13 +3885,13 @@
         <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="O18" t="n">
         <v>1.14</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Q18" t="n">
         <v>1.14</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
         <v>1.71</v>
@@ -4136,7 +4136,7 @@
         <v>18.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>14.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="G20" t="n">
-        <v>1.34</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT20" t="n">
         <v>11</v>
       </c>
-      <c r="I20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="X20" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY20" t="n">
         <v>11</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AZ20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="BA20" t="n">
         <v>38</v>
       </c>
-      <c r="AR20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV20" t="n">
+      <c r="BB20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD20" t="n">
         <v>34</v>
       </c>
-      <c r="AW20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>26</v>
-      </c>
       <c r="BE20" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>20</v>
       </c>
       <c r="BG20" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.68</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>5.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,55 +4628,55 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>420</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.38</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4745,52 +4745,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,373 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Venezuelan Primera Division</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Puerto Cabello</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Trujillanos</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
         <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
         <v>3.9</v>
@@ -793,10 +793,10 @@
         <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
         <v>1.58</v>
@@ -805,10 +805,10 @@
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>26</v>
@@ -844,7 +844,7 @@
         <v>18</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ2" t="n">
         <v>70</v>
@@ -862,7 +862,7 @@
         <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -889,7 +889,7 @@
         <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,19 +898,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD2" t="n">
         <v>5</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
         <v>19</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
         <v>1.56</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
         <v>2.36</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="H4" t="n">
         <v>6.4</v>
@@ -1166,7 +1166,7 @@
         <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>6</v>
@@ -1175,28 +1175,28 @@
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1253,10 +1253,10 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
         <v>50</v>
@@ -1271,7 +1271,7 @@
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
         <v>9.4</v>
@@ -1286,7 +1286,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE4" t="n">
         <v>9.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
         <v>50</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1339,37 +1339,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.6</v>
@@ -1378,19 +1378,19 @@
         <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
         <v>1.63</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1441,7 +1441,7 @@
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO5" t="n">
         <v>60</v>
@@ -1453,13 +1453,13 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS5" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AT5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>8.4</v>
@@ -1468,19 +1468,19 @@
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
         <v>14.5</v>
@@ -1489,20 +1489,20 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BF5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
@@ -1569,22 +1569,22 @@
         <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
         <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1644,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR6" t="n">
         <v>9.800000000000001</v>
@@ -1656,10 +1656,10 @@
         <v>15.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
         <v>14</v>
@@ -1692,11 +1692,11 @@
         <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
@@ -1751,7 +1751,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
@@ -1778,7 +1778,7 @@
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1868,7 +1868,7 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
         <v>9.199999999999999</v>
@@ -1886,11 +1886,11 @@
         <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
         <v>3.75</v>
@@ -1972,7 +1972,7 @@
         <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -1990,10 +1990,10 @@
         <v>9.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
@@ -2002,7 +2002,7 @@
         <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
         <v>25</v>
@@ -2011,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2032,13 +2032,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2050,19 +2050,19 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -2071,20 +2071,20 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>19.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
         <v>7.6</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.68</v>
+        <v>1.98</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB10" t="n">
         <v>20</v>
       </c>
-      <c r="Z10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="BC10" t="n">
         <v>20</v>
       </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BD10" t="n">
-        <v>2.24</v>
+        <v>38</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.34</v>
+        <v>42</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.34</v>
+        <v>15</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.34</v>
+        <v>75</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9</v>
+        <v>1.95</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.48</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AX11" t="n">
         <v>2.24</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>65</v>
+        <v>2.26</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>2.32</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>2.28</v>
       </c>
       <c r="BD11" t="n">
-        <v>38</v>
+        <v>2.28</v>
       </c>
       <c r="BE11" t="n">
-        <v>42</v>
+        <v>2.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>15</v>
+        <v>2.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>75</v>
+        <v>2.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>2.06</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
         <v>3.85</v>
@@ -2748,7 +2748,7 @@
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
         <v>6.4</v>
@@ -2826,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -2847,20 +2847,20 @@
         <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>2.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
         <v>3.05</v>
@@ -2927,13 +2927,13 @@
         <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U13" t="n">
         <v>2.04</v>
@@ -2942,7 +2942,7 @@
         <v>1.47</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
         <v>11</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -3318,19 +3318,19 @@
         <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
         <v>14.5</v>
@@ -3387,10 +3387,10 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="AR15" t="n">
         <v>18</v>
@@ -3399,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.8</v>
+        <v>2.92</v>
       </c>
       <c r="AV15" t="n">
         <v>11</v>
@@ -3414,10 +3414,10 @@
         <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>3.25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3497,10 +3497,10 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -3521,10 +3521,10 @@
         <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
         <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BF16" t="n">
         <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
         <v>1.8</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
         <v>18.5</v>
@@ -4163,10 +4163,10 @@
         <v>19</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>20</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.68</v>
+        <v>1.33</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.84</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.71</v>
       </c>
       <c r="S20" t="n">
-        <v>3.25</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>3.95</v>
       </c>
       <c r="X20" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>380</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC20" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG20" t="n">
         <v>46</v>
       </c>
-      <c r="AB20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>23</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.5</v>
       </c>
-      <c r="I21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V21" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G22" t="n">
-        <v>420</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,201 +4800,395 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>420</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:46:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Venezuelan Primera Division</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Puerto Cabello</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Trujillanos</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>1.29</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>1.38</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>19</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>4.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>6.2</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
         <v>1.05</v>
       </c>
-      <c r="N23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="N24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.34</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="P24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
         <v>3.4</v>
       </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-19 21:36:15</t>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,43 +757,43 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
         <v>2.38</v>
@@ -802,13 +802,13 @@
         <v>1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
         <v>26</v>
@@ -820,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
@@ -832,7 +832,7 @@
         <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="n">
         <v>34</v>
@@ -862,7 +862,7 @@
         <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -889,7 +889,7 @@
         <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,19 +898,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC2" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
         <v>19</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
         <v>2.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
         <v>18</v>
@@ -1017,10 +1017,10 @@
         <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>13</v>
@@ -1029,22 +1029,22 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AL3" t="n">
         <v>40</v>
@@ -1053,68 +1053,68 @@
         <v>70</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY3" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
         <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
         <v>5.7</v>
@@ -1166,37 +1166,37 @@
         <v>1.23</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R4" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
         <v>32</v>
@@ -1238,7 +1238,7 @@
         <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
@@ -1247,22 +1247,22 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>50</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1274,19 +1274,19 @@
         <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
         <v>50</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,146 +1363,146 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>11</v>
       </c>
       <c r="AH5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>20</v>
       </c>
-      <c r="AI5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
         <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AP5" t="n">
         <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
         <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,22 +1557,22 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
         <v>1.7</v>
@@ -1605,7 +1605,7 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
@@ -1665,7 +1665,7 @@
         <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -1677,26 +1677,26 @@
         <v>5.2</v>
       </c>
       <c r="BB6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF6" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V7" t="n">
         <v>1.34</v>
@@ -1853,7 +1853,7 @@
         <v>5.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
         <v>8.199999999999999</v>
@@ -1871,7 +1871,7 @@
         <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
         <v>21</v>
@@ -1883,14 +1883,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
         <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1939,19 +1939,19 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
         <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
         <v>2.28</v>
@@ -1966,13 +1966,13 @@
         <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
         <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
         <v>1.95</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.4</v>
       </c>
-      <c r="L10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
         <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
         <v>8</v>
       </c>
-      <c r="AC10" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB10" t="n">
         <v>19.5</v>
       </c>
-      <c r="AE10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BC10" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA10" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>20</v>
-      </c>
       <c r="BD10" t="n">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>42</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>75</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J11" t="n">
-        <v>2.46</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE11" t="n">
         <v>40</v>
       </c>
-      <c r="AB11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>30</v>
-      </c>
       <c r="AF11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW11" t="n">
         <v>34</v>
       </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI11" t="n">
+      <c r="AX11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE11" t="n">
         <v>40</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BF11" t="n">
-        <v>2.4</v>
+        <v>26</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.4</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
         <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W12" t="n">
         <v>2</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="X12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y12" t="n">
         <v>15</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
         <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG12" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB12" t="n">
         <v>20</v>
       </c>
-      <c r="AE12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>38</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.7</v>
+        <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>75</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>2.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R13" t="n">
         <v>1.48</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X13" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
         <v>2.26</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>2.16</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>2.22</v>
       </c>
       <c r="AS13" t="n">
-        <v>46</v>
+        <v>2.28</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>2.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>2.06</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>2.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>34</v>
+        <v>2.24</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>2.26</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>48</v>
+        <v>2.34</v>
       </c>
       <c r="BB13" t="n">
-        <v>34</v>
+        <v>2.34</v>
       </c>
       <c r="BC13" t="n">
-        <v>28</v>
+        <v>2.34</v>
       </c>
       <c r="BD13" t="n">
-        <v>42</v>
+        <v>2.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>40</v>
+        <v>2.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>26</v>
+        <v>2.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>34</v>
+        <v>2.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.08</v>
@@ -3321,10 +3321,10 @@
         <v>3.95</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3497,10 +3497,10 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
@@ -3530,7 +3530,7 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.7</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AW16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA16" t="n">
         <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BC16" t="n">
         <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BF16" t="n">
         <v>5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="I17" t="n">
         <v>1.86</v>
@@ -3700,7 +3700,7 @@
         <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
@@ -3718,16 +3718,16 @@
         <v>2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA17" t="n">
         <v>30</v>
@@ -3736,7 +3736,7 @@
         <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
         <v>15</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="AS17" t="n">
-        <v>12.5</v>
+        <v>1.52</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.6</v>
+        <v>1.49</v>
       </c>
       <c r="AU17" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>1.44</v>
       </c>
       <c r="AW17" t="n">
-        <v>12.5</v>
+        <v>1.52</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>1.52</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>1.52</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
         <v>1.71</v>
@@ -4130,7 +4130,7 @@
         <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF19" t="n">
         <v>18.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
         <v>27</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
         <v>11</v>
@@ -4393,7 +4393,7 @@
         <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC20" t="n">
         <v>12.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G21" t="n">
         <v>2.7</v>
@@ -4452,7 +4452,7 @@
         <v>2.92</v>
       </c>
       <c r="I21" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -4461,7 +4461,7 @@
         <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -4569,7 +4569,7 @@
         <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW21" t="n">
         <v>27</v>
@@ -4581,7 +4581,7 @@
         <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>36</v>
@@ -4599,21 +4599,21 @@
         <v>65</v>
       </c>
       <c r="BF21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG21" t="n">
         <v>23</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>420</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,22 +4661,22 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.38</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
-        <v>420</v>
+        <v>2.38</v>
       </c>
       <c r="H23" t="n">
-        <v>1.09</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,22 +4855,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,13 +5049,13 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Q24" t="n">
         <v>1.34</v>
@@ -5073,122 +5073,704 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-20 01:57:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-20 01:57:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
         <v>1.05</v>
       </c>
-      <c r="W24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="N26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AC24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AW26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-20 01:57:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X27" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AG24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="AD27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>2026-04-19 23:46:28</t>
+      <c r="AG27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="I2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.6</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.58</v>
-      </c>
       <c r="U2" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
         <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
       </c>
       <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
       <c r="AE2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>34</v>
@@ -847,22 +847,22 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
         <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AP2" t="n">
         <v>19.5</v>
@@ -871,25 +871,25 @@
         <v>11.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AX2" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
         <v>13</v>
@@ -898,19 +898,19 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BF2" t="n">
         <v>19</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -975,55 +975,55 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.59</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.58</v>
-      </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA3" t="n">
         <v>28</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -1032,10 +1032,10 @@
         <v>44</v>
       </c>
       <c r="AG3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH3" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>30</v>
@@ -1065,10 +1065,10 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>16</v>
@@ -1080,19 +1080,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
         <v>18.5</v>
       </c>
       <c r="AY3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>12</v>
-      </c>
       <c r="BA3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BB3" t="n">
         <v>30</v>
@@ -1107,14 +1107,14 @@
         <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1145,55 +1145,55 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
         <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R4" t="n">
         <v>1.77</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
         <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
         <v>3</v>
@@ -1205,7 +1205,7 @@
         <v>34</v>
       </c>
       <c r="Z4" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
         <v>200</v>
@@ -1238,7 +1238,7 @@
         <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
         <v>28</v>
@@ -1247,13 +1247,13 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO4" t="n">
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>9.199999999999999</v>
@@ -1262,7 +1262,7 @@
         <v>50</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
         <v>11</v>
@@ -1274,7 +1274,7 @@
         <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1298,7 +1298,7 @@
         <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
         <v>4.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,31 +1363,31 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
         <v>2.16</v>
@@ -1402,13 +1402,13 @@
         <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1417,10 +1417,10 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1429,7 +1429,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
         <v>17.5</v>
@@ -1438,16 +1438,16 @@
         <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
@@ -1459,13 +1459,13 @@
         <v>38</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
         <v>38</v>
@@ -1474,7 +1474,7 @@
         <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>15.5</v>
@@ -1489,20 +1489,20 @@
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1560,13 +1560,13 @@
         <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
         <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.45</v>
@@ -1578,64 +1578,64 @@
         <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
         <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
         <v>12.5</v>
@@ -1644,28 +1644,28 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
         <v>14</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>13.5</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H7" t="n">
         <v>3.55</v>
@@ -1751,7 +1751,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
@@ -1778,7 +1778,7 @@
         <v>1.34</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1838,13 +1838,13 @@
         <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
         <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1862,22 +1862,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BE7" t="n">
         <v>9.199999999999999</v>
@@ -1886,11 +1886,11 @@
         <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1939,7 +1939,7 @@
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1999,7 +1999,7 @@
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -2011,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>34</v>
@@ -2026,19 +2026,19 @@
         <v>30</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AR8" t="n">
         <v>19.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2050,19 +2050,19 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -2071,20 +2071,20 @@
         <v>20</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF8" t="n">
         <v>18</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
@@ -2139,19 +2139,19 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
         <v>3.4</v>
@@ -2160,13 +2160,13 @@
         <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
         <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
         <v>4.4</v>
@@ -2327,82 +2327,82 @@
         <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
         <v>1.82</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>80</v>
       </c>
       <c r="AJ10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
@@ -2411,10 +2411,10 @@
         <v>140</v>
       </c>
       <c r="AN10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
@@ -2426,7 +2426,7 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2438,7 +2438,7 @@
         <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX10" t="n">
         <v>11.5</v>
@@ -2450,7 +2450,7 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
         <v>19.5</v>
@@ -2459,20 +2459,20 @@
         <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2512,13 +2512,13 @@
         <v>3.05</v>
       </c>
       <c r="I11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
@@ -2548,7 +2548,7 @@
         <v>1.91</v>
       </c>
       <c r="U11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.47</v>
@@ -2605,13 +2605,13 @@
         <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO11" t="n">
         <v>40</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I12" t="n">
         <v>4.9</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>3.35</v>
@@ -2724,10 +2724,10 @@
         <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
         <v>2.22</v>
@@ -2742,7 +2742,7 @@
         <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
@@ -2754,7 +2754,7 @@
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
         <v>36</v>
@@ -2784,7 +2784,7 @@
         <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
         <v>23</v>
@@ -2820,10 +2820,10 @@
         <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW12" t="n">
         <v>55</v>
@@ -2856,11 +2856,11 @@
         <v>15</v>
       </c>
       <c r="BG12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.96</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
@@ -2987,7 +2987,7 @@
         <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
@@ -2999,31 +2999,31 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR13" t="n">
         <v>2.26</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AS13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV13" t="n">
         <v>2.16</v>
       </c>
-      <c r="AR13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AW13" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AY13" t="n">
         <v>9.800000000000001</v>
@@ -3032,29 +3032,29 @@
         <v>10.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3094,13 +3094,13 @@
         <v>1.87</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,22 +3109,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.34</v>
+        <v>1.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>1.75</v>
@@ -3133,7 +3133,7 @@
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W14" t="n">
         <v>1.24</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2.24</v>
       </c>
       <c r="G15" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -3330,7 +3330,7 @@
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
         <v>14.5</v>
@@ -3357,10 +3357,10 @@
         <v>60</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>23</v>
@@ -3381,28 +3381,28 @@
         <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR15" t="n">
         <v>18</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AV15" t="n">
         <v>11</v>
@@ -3414,35 +3414,35 @@
         <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC15" t="n">
         <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
         <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I16" t="n">
         <v>2.04</v>
@@ -3515,7 +3515,7 @@
         <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
         <v>2.12</v>
@@ -3530,7 +3530,7 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ16" t="n">
         <v>7.6</v>
@@ -3593,50 +3593,50 @@
         <v>17</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="BF16" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="BG16" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3688,19 +3688,19 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="O17" t="n">
         <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
         <v>1.26</v>
@@ -3721,10 +3721,10 @@
         <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
         <v>15.5</v>
@@ -3736,7 +3736,7 @@
         <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD17" t="n">
         <v>15</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.46</v>
+        <v>1.95</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.52</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.49</v>
+        <v>9.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.52</v>
+        <v>12.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.52</v>
+        <v>12.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.52</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4073,13 +4073,13 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.33</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.34</v>
       </c>
       <c r="H20" t="n">
         <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.27</v>
@@ -4273,7 +4273,7 @@
         <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.17</v>
@@ -4285,13 +4285,13 @@
         <v>1.52</v>
       </c>
       <c r="R20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
         <v>2.04</v>
@@ -4300,7 +4300,7 @@
         <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="X20" t="n">
         <v>30</v>
@@ -4321,7 +4321,7 @@
         <v>14.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AE20" t="n">
         <v>160</v>
@@ -4339,22 +4339,22 @@
         <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK20" t="n">
         <v>13.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AO20" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP20" t="n">
         <v>27</v>
@@ -4375,10 +4375,10 @@
         <v>13.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX20" t="n">
         <v>8.6</v>
@@ -4405,14 +4405,14 @@
         <v>42</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG20" t="n">
         <v>46</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I21" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.55</v>
@@ -4488,10 +4488,10 @@
         <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.59</v>
@@ -4548,7 +4548,7 @@
         <v>22</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP21" t="n">
         <v>13.5</v>
@@ -4569,13 +4569,13 @@
         <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW21" t="n">
         <v>27</v>
       </c>
       <c r="AX21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
@@ -4596,17 +4596,17 @@
         <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BF21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG21" t="n">
         <v>23</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
         <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="H24" t="n">
-        <v>3.35</v>
+        <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT24" t="n">
         <v>3.3</v>
       </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AU24" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.13</v>
+        <v>5.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.13</v>
+        <v>3.25</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.13</v>
+        <v>4.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.13</v>
+        <v>5.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.13</v>
+        <v>5.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.13</v>
+        <v>3.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.13</v>
+        <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.13</v>
+        <v>5.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>3.35</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.13</v>
+        <v>5.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
         <v>2.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5246,7 +5246,7 @@
         <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>1.49</v>
+        <v>1.02</v>
       </c>
       <c r="P25" t="n">
         <v>1.57</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>4.5</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H26" t="n">
         <v>1.74</v>
       </c>
       <c r="I26" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J26" t="n">
         <v>3.95</v>
@@ -5446,13 +5446,13 @@
         <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.46</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
         <v>1.71</v>
@@ -5569,14 +5569,14 @@
         <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="BG26" t="n">
         <v>7.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5616,13 +5616,13 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
         <v>3.75</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5634,19 +5634,19 @@
         <v>4.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
         <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R27" t="n">
         <v>1.46</v>
       </c>
       <c r="S27" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
         <v>1.69</v>
@@ -5655,7 +5655,7 @@
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
         <v>1.98</v>
@@ -5691,19 +5691,19 @@
         <v>11</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
@@ -5715,40 +5715,40 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>10</v>
       </c>
       <c r="AY27" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ27" t="n">
         <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
         <v>7.2</v>
@@ -5757,20 +5757,20 @@
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
         <v>1.89</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -793,10 +793,10 @@
         <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -805,25 +805,25 @@
         <v>2.48</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y2" t="n">
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -832,40 +832,40 @@
         <v>11.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO2" t="n">
         <v>9</v>
       </c>
       <c r="AP2" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11.5</v>
@@ -874,7 +874,7 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>17.5</v>
@@ -889,38 +889,38 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8</v>
       </c>
-      <c r="BD2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>3.55</v>
       </c>
       <c r="H3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="I3" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -975,34 +975,34 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X3" t="n">
         <v>25</v>
@@ -1020,7 +1020,7 @@
         <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
@@ -1029,7 +1029,7 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1047,49 +1047,49 @@
         <v>34</v>
       </c>
       <c r="AL3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>19.5</v>
@@ -1101,20 +1101,20 @@
         <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
         <v>29</v>
       </c>
       <c r="BF3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1145,136 +1145,136 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
         <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD4" t="n">
         <v>32</v>
       </c>
-      <c r="Y4" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>27</v>
-      </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK4" t="n">
         <v>14</v>
       </c>
       <c r="AL4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AO4" t="n">
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
         <v>11</v>
       </c>
       <c r="AV4" t="n">
-        <v>22</v>
+        <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1283,10 +1283,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
-        <v>50</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.84</v>
       </c>
       <c r="G5" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1372,31 +1372,31 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
         <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>38</v>
@@ -1408,7 +1408,7 @@
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5" t="n">
         <v>18.5</v>
@@ -1441,7 +1441,7 @@
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO5" t="n">
         <v>46</v>
@@ -1459,16 +1459,16 @@
         <v>38</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1477,19 +1477,19 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
@@ -1498,11 +1498,11 @@
         <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I6" t="n">
         <v>2.04</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1566,28 +1566,28 @@
         <v>2.16</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
         <v>1.96</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
@@ -1605,7 +1605,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
         <v>21</v>
@@ -1626,16 +1626,16 @@
         <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
         <v>12.5</v>
@@ -1656,54 +1656,54 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY6" t="n">
         <v>14</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>4.3</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,123 +1907,123 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
         <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
         <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
@@ -2032,19 +2032,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -2053,38 +2053,38 @@
         <v>4.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
         <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>5.1</v>
       </c>
       <c r="BD8" t="n">
         <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="I9" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG9" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AH9" t="n">
         <v>25</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AI9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL9" t="n">
         <v>60</v>
       </c>
-      <c r="AB9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>40</v>
-      </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AN9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.7</v>
       </c>
-      <c r="I10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
         <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
         <v>22</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX10" t="n">
         <v>12</v>
       </c>
-      <c r="AW10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY10" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.5</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
         <v>14</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.12</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.35</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX11" t="n">
         <v>11</v>
       </c>
-      <c r="Y11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>48</v>
+        <v>5.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>42</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>40</v>
+        <v>5.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.35</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="X12" t="n">
         <v>11</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM12" t="n">
         <v>120</v>
       </c>
-      <c r="AB12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>130</v>
-      </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AO12" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="BG12" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.96</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.66</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR13" t="n">
         <v>30</v>
       </c>
-      <c r="Y13" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AS13" t="n">
         <v>40</v>
       </c>
-      <c r="AB13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AT13" t="n">
-        <v>2.24</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.16</v>
+        <v>17.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.3</v>
+        <v>55</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.36</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.4</v>
+        <v>65</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.38</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.38</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.4</v>
+        <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.44</v>
+        <v>42</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.46</v>
+        <v>15</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.46</v>
+        <v>70</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hillerod Fodbold</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="I14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K14" t="n">
+        <v>950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X14" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX14" t="n">
         <v>2.36</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>2.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Hillerod Fodbold</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I15" t="n">
         <v>2.24</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3.8</v>
-      </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="O15" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.96</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="H16" t="n">
-        <v>1.93</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="O16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.29</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.12</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="AU16" t="n">
         <v>6.8</v>
       </c>
       <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
         <v>4</v>
       </c>
-      <c r="AW16" t="n">
-        <v>5</v>
-      </c>
       <c r="AX16" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.8</v>
+        <v>3.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.6</v>
+        <v>19.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.6</v>
+        <v>16.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,100 +3658,100 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
         <v>5</v>
       </c>
-      <c r="G17" t="n">
-        <v>5.7</v>
-      </c>
       <c r="H17" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="I17" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>1.65</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD17" t="n">
-        <v>15</v>
-      </c>
       <c r="AE17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
         <v>1000</v>
@@ -3775,69 +3775,69 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="AQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB17" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BC17" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.16</v>
+        <v>4.7</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,60 +3847,60 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bol</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.04</v>
       </c>
-      <c r="G18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N18" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.14</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.87</v>
       </c>
       <c r="T18" t="n">
         <v>1.01</v>
@@ -3909,43 +3909,43 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF18" t="n">
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3969,69 +3969,69 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Academia de Balompie Bol</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
         <v>2.56</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>1.33</v>
+        <v>2.58</v>
       </c>
       <c r="H20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY20" t="n">
         <v>11</v>
       </c>
-      <c r="I20" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AZ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA20" t="n">
         <v>30</v>
       </c>
-      <c r="Y20" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>40</v>
-      </c>
       <c r="BB20" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>12.5</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF20" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="BG20" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>1.3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>1.31</v>
       </c>
       <c r="H21" t="n">
-        <v>2.94</v>
+        <v>11.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.98</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W21" t="n">
         <v>4.2</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.59</v>
-      </c>
       <c r="X21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU21" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y21" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AV21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC21" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI21" t="n">
+      <c r="BD21" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE21" t="n">
         <v>42</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>34</v>
-      </c>
       <c r="BF21" t="n">
-        <v>19.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG21" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>420</v>
+        <v>2.66</v>
       </c>
       <c r="H22" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="J22" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
-        <v>1.38</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,67 +4822,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.38</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="G24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.38</v>
       </c>
-      <c r="H24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J24" t="n">
+      <c r="P24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD24" t="n">
         <v>4.6</v>
       </c>
-      <c r="K24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="BE24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AV24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BG24" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.48</v>
+        <v>1.29</v>
       </c>
       <c r="G25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.05</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="O25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
         <v>3.4</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.56</v>
-      </c>
       <c r="X25" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.08</v>
+        <v>5.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.24</v>
+        <v>5.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="AT25" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="AY25" t="n">
-        <v>2.14</v>
+        <v>4.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="G26" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>1.56</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="P26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AV26" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AW26" t="n">
-        <v>14.5</v>
+        <v>2.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="AY26" t="n">
-        <v>16</v>
+        <v>2.12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>2.24</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.6</v>
+        <v>2.32</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>2.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="G27" t="n">
-        <v>2.02</v>
+        <v>5.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,40 +5631,40 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P27" t="n">
         <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,22 +5673,22 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
         <v>11</v>
       </c>
-      <c r="AC27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>17</v>
-      </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
         <v>1000</v>
@@ -5697,80 +5697,274 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
         <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="AR27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC27" t="n">
         <v>8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>15</v>
       </c>
       <c r="BD27" t="n">
         <v>8</v>
       </c>
       <c r="BE27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT28" t="n">
         <v>9.4</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="AU28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF28" t="n">
         <v>10</v>
       </c>
-      <c r="BG27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-04-20 04:08:36</t>
+      <c r="BG28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -787,19 +787,19 @@
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
         <v>2.48</v>
@@ -817,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA2" t="n">
         <v>26</v>
@@ -847,7 +847,7 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
@@ -889,7 +889,7 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -901,26 +901,26 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD2" t="n">
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
         <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -978,143 +978,143 @@
         <v>5.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN3" t="n">
         <v>30</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB3" t="n">
         <v>34</v>
       </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>30</v>
-      </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF3" t="n">
         <v>18</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G4" t="n">
         <v>1.48</v>
@@ -1154,7 +1154,7 @@
         <v>6.8</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
         <v>5.3</v>
@@ -1163,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1178,22 +1178,22 @@
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R4" t="n">
         <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
         <v>3.05</v>
@@ -1202,19 +1202,19 @@
         <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>210</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD4" t="n">
         <v>32</v>
@@ -1223,7 +1223,7 @@
         <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
@@ -1232,16 +1232,16 @@
         <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM4" t="n">
         <v>95</v>
@@ -1253,40 +1253,40 @@
         <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>46</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.4</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1378,7 +1378,7 @@
         <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
         <v>1.68</v>
@@ -1417,7 +1417,7 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1438,7 +1438,7 @@
         <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>9.4</v>
@@ -1468,7 +1468,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1498,11 +1498,11 @@
         <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1590,55 +1590,55 @@
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
         <v>12.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1674,36 +1674,36 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>34</v>
+        <v>4.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,33 +1713,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>MFK Stara Lubovna</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Zlate Moravce</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="G7" t="n">
-        <v>2.68</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>2.26</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1748,38 +1748,38 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.59</v>
-      </c>
       <c r="X7" t="n">
         <v>1000</v>
       </c>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>4.3</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
         <v>13.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>Al-Raed (KSA)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>1.24</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.1</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ12" t="n">
         <v>40</v>
       </c>
       <c r="AK12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN12" t="n">
         <v>32</v>
       </c>
-      <c r="AL12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>30</v>
-      </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
         <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>48</v>
+        <v>4.1</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>4.1</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>48</v>
+        <v>4.1</v>
       </c>
       <c r="BB12" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>42</v>
+        <v>4.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>36</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:05:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Al-Anwar Club</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>2.24</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>6.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.4</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
       <c r="X13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:05:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>Al Bukayriyah</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>1.96</v>
+        <v>2.72</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z14" t="n">
         <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AF14" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AK14" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.26</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.16</v>
+        <v>9.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.3</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.36</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.38</v>
+        <v>22</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.46</v>
+        <v>19.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.46</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hillerod Fodbold</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="I15" t="n">
-        <v>2.24</v>
+        <v>1.86</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,34 +3303,34 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -3459,108 +3459,108 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G16" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.74</v>
       </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="X16" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y16" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y16" t="n">
-        <v>15</v>
-      </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
         <v>38</v>
@@ -3569,81 +3569,81 @@
         <v>34</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4</v>
-      </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.25</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB17" t="n">
         <v>5</v>
       </c>
-      <c r="H17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BC17" t="n">
-        <v>4.7</v>
+        <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
         <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.800000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,117 +3847,117 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>2.76</v>
       </c>
       <c r="G18" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="I18" t="n">
-        <v>1.86</v>
+        <v>2.66</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U18" t="n">
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="Y18" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
         <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG18" t="n">
-        <v>30</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3969,69 +3969,69 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.91</v>
+        <v>2.26</v>
       </c>
       <c r="AS18" t="n">
-        <v>12</v>
+        <v>2.34</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>2.24</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="AY18" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13</v>
+        <v>2.22</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bol</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.26</v>
       </c>
-      <c r="I19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,184 +4235,184 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.85</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF20" t="n">
         <v>15</v>
       </c>
-      <c r="Z20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
       <c r="AH20" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>18.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AW20" t="n">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>17.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>30</v>
+        <v>4.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BC20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>18</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.3</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="H21" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="I21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG21" t="n">
         <v>12</v>
       </c>
-      <c r="J21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="AH21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN21" t="n">
         <v>30</v>
       </c>
-      <c r="Y21" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AO21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD21" t="n">
         <v>42</v>
       </c>
-      <c r="AE21" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="BE21" t="n">
         <v>40</v>
       </c>
-      <c r="AR21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV21" t="n">
+      <c r="BF21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG21" t="n">
         <v>36</v>
       </c>
-      <c r="AW21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>42</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>50</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Hillerod Fodbold</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.64</v>
+        <v>3.35</v>
       </c>
       <c r="G22" t="n">
-        <v>2.66</v>
+        <v>5.2</v>
       </c>
       <c r="H22" t="n">
-        <v>2.96</v>
+        <v>1.89</v>
       </c>
       <c r="I22" t="n">
-        <v>2.98</v>
+        <v>2.22</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G23" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,72 +5011,72 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>FK Velez Mostar</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>1.02</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5133,69 +5133,69 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,78 +5205,78 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>1.38</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4</v>
+        <v>1.93</v>
       </c>
       <c r="I25" t="n">
-        <v>17.5</v>
+        <v>2.06</v>
       </c>
       <c r="J25" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.84</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>1.02</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="W25" t="n">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,111 +5285,111 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>70</v>
+        <v>12.5</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>7.6</v>
       </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AR25" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BA25" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,105 +5399,105 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9</v>
+        <v>1.78</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>1.87</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="W26" t="n">
-        <v>1.56</v>
+        <v>1.21</v>
       </c>
       <c r="X26" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AH26" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5506,7 +5506,7 @@
         <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
         <v>1000</v>
@@ -5521,69 +5521,69 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.06</v>
+        <v>4.9</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.99</v>
+        <v>9.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.94</v>
+        <v>5.3</v>
       </c>
       <c r="AV26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX26" t="n">
         <v>2.16</v>
       </c>
-      <c r="AW26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AY26" t="n">
-        <v>2.12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.24</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,378 +5593,2318 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="G27" t="n">
-        <v>5.2</v>
+        <v>2.58</v>
       </c>
       <c r="H27" t="n">
-        <v>1.75</v>
+        <v>2.84</v>
       </c>
       <c r="I27" t="n">
-        <v>1.85</v>
+        <v>2.86</v>
       </c>
       <c r="J27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M27" t="n">
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="U27" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="V27" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="X27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY27" t="n">
         <v>11</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF27" t="n">
         <v>15</v>
       </c>
-      <c r="BA27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>8</v>
-      </c>
       <c r="BG27" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 06:19:34</t>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Academia de Balompie Bol</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Spanish La Liga</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>420</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>70</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Argentinian Primera B Metropolitana</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deportivo Merlo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Comunicaciones B Aires</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CD Gualberto Villarroel</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Puerto Cabello</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Trujillanos</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I34" t="n">
+        <v>19</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X34" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bolivar</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Club Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K35" t="n">
+        <v>950</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X37" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Pumas UNAM</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>FC Juarez</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="F38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="I28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="I38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J38" t="n">
         <v>3.8</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K38" t="n">
         <v>4.1</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
         <v>1.05</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N38" t="n">
         <v>4.3</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O38" t="n">
         <v>1.26</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P38" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="Q38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R38" t="n">
         <v>1.46</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S38" t="n">
         <v>2.92</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V28" t="n">
+      <c r="T38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.3</v>
       </c>
-      <c r="W28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X28" t="n">
+      <c r="W38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X38" t="n">
         <v>21</v>
       </c>
-      <c r="Y28" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="Y38" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AC38" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AD38" t="n">
         <v>17</v>
       </c>
-      <c r="AE28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AE38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF38" t="n">
         <v>15.5</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AG38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX38" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN28" t="n">
+      <c r="AY38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>13</v>
       </c>
-      <c r="AO28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS28" t="n">
+      <c r="BA38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE38" t="n">
         <v>5.6</v>
       </c>
-      <c r="AT28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF28" t="n">
+      <c r="BF38" t="n">
         <v>10</v>
       </c>
-      <c r="BG28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-04-20 06:19:34</t>
+      <c r="BG38" t="n">
+        <v>38</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:31:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -790,25 +790,25 @@
         <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>28</v>
@@ -823,10 +823,10 @@
         <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
         <v>11.5</v>
@@ -835,10 +835,10 @@
         <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>18.5</v>
@@ -847,22 +847,22 @@
         <v>32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL2" t="n">
         <v>48</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AP2" t="n">
         <v>18.5</v>
@@ -889,7 +889,7 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -901,26 +901,26 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
         <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.85</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
@@ -969,7 +969,7 @@
         <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -981,22 +981,22 @@
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
         <v>2.48</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
         <v>2.04</v>
@@ -1008,22 +1008,22 @@
         <v>38</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
         <v>34</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
@@ -1038,7 +1038,7 @@
         <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
         <v>75</v>
@@ -1047,31 +1047,31 @@
         <v>42</v>
       </c>
       <c r="AL3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP3" t="n">
         <v>21</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
@@ -1080,7 +1080,7 @@
         <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>27</v>
@@ -1092,19 +1092,19 @@
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB3" t="n">
         <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF3" t="n">
         <v>18</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
         <v>6.8</v>
@@ -1160,7 +1160,7 @@
         <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1175,7 +1175,7 @@
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
         <v>1.45</v>
@@ -1196,13 +1196,13 @@
         <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1229,13 +1229,13 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK4" t="n">
         <v>13.5</v>
@@ -1256,10 +1256,10 @@
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AS4" t="n">
         <v>46</v>
@@ -1268,10 +1268,10 @@
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>34</v>
@@ -1283,10 +1283,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -1351,7 +1351,7 @@
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>4.4</v>
@@ -1372,7 +1372,7 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
@@ -1381,7 +1381,7 @@
         <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
         <v>2.34</v>
@@ -1390,67 +1390,67 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
         <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
         <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR5" t="n">
         <v>22</v>
@@ -1465,44 +1465,44 @@
         <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>4.4</v>
@@ -1542,7 +1542,7 @@
         <v>1.93</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
@@ -1563,10 +1563,10 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1575,19 +1575,19 @@
         <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>12.5</v>
@@ -1596,16 +1596,16 @@
         <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Ykkosliiga</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,60 +1907,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Finnish Ykkosliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,72 +2101,72 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.68</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="O9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.24</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>1.23</v>
       </c>
       <c r="T9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2271,21 +2271,21 @@
         <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,72 +2295,72 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12:55:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Raed (KSA)</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.39</v>
+        <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W10" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2378,10 +2378,10 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2390,7 +2390,7 @@
         <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,60 +2489,60 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:55:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zeljeznicar</t>
+          <t>Al-Raed (KSA)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Zeljeznicar</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>1.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,184 +2877,184 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13:05:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al Batin</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Anwar Club</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.45</v>
       </c>
-      <c r="H13" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.2</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.95</v>
       </c>
-      <c r="O13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Arabi Al-Saudi</t>
+          <t>Al Batin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Bukayriyah</t>
+          <t>Al-Anwar Club</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:15:00</t>
+          <t>13:05:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al Taee</t>
+          <t>Al-Arabi Al-Saudi</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Bukayriyah</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AS15" t="n">
         <v>4</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="AT15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AV15" t="n">
         <v>3.4</v>
       </c>
-      <c r="K15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WSG Wattens</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>1.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>2.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RZ Pellets WAC</t>
+          <t>WSG Wattens</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.5</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.31</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="n">
         <v>70</v>
       </c>
-      <c r="AB17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP17" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AQ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>18</v>
-      </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Norrkoping</t>
+          <t>RZ Pellets WAC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.04</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="X18" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL18" t="n">
         <v>44</v>
       </c>
-      <c r="AL18" t="n">
-        <v>48</v>
-      </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.26</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>2.36</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.22</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.38</v>
+        <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.46</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>2.24</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>2.76</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.48</v>
       </c>
-      <c r="M19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AB19" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>70</v>
       </c>
-      <c r="AF19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>23</v>
-      </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>30</v>
+        <v>2.26</v>
       </c>
       <c r="AS19" t="n">
-        <v>40</v>
+        <v>2.34</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>2.24</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>2.16</v>
       </c>
       <c r="AW19" t="n">
-        <v>55</v>
+        <v>2.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>2.36</v>
       </c>
       <c r="AY19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>2.22</v>
       </c>
       <c r="BA19" t="n">
-        <v>65</v>
+        <v>2.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>20</v>
+        <v>2.38</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>2.38</v>
       </c>
       <c r="BD19" t="n">
-        <v>38</v>
+        <v>2.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>42</v>
+        <v>2.44</v>
       </c>
       <c r="BF19" t="n">
-        <v>15</v>
+        <v>2.46</v>
       </c>
       <c r="BG19" t="n">
-        <v>70</v>
+        <v>2.46</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.12</v>
-      </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
         <v>110</v>
       </c>
       <c r="AB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
         <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AO20" t="n">
         <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>65</v>
       </c>
       <c r="BB20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.1</v>
+        <v>46</v>
       </c>
       <c r="BF20" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>70</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.64</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.66</v>
       </c>
       <c r="H21" t="n">
         <v>3.1</v>
@@ -4455,10 +4455,10 @@
         <v>3.15</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.49</v>
@@ -4485,16 +4485,16 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
@@ -4560,13 +4560,13 @@
         <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
         <v>12.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hillerod Fodbold</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>5.2</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>1.89</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Hillerod Fodbold</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.45</v>
+        <v>1.91</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>2.34</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="O23" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="P23" t="n">
         <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.74</v>
       </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FK Velez Mostar</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Siroki Brijeg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,72 +5205,72 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>FK Velez Mostar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K25" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>1.51</v>
       </c>
       <c r="T25" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5288,10 +5288,10 @@
         <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5327,69 +5327,69 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB26" t="n">
         <v>5.7</v>
       </c>
-      <c r="H26" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.16</v>
+        <v>5.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.16</v>
+        <v>5.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.16</v>
+        <v>5.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.16</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>2.84</v>
+        <v>1.79</v>
       </c>
       <c r="I27" t="n">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="J27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.85</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>5.1</v>
+        <v>1.67</v>
       </c>
       <c r="O27" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z27" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>21</v>
-      </c>
       <c r="AA27" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AB27" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AD27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>25</v>
-      </c>
       <c r="AX27" t="n">
-        <v>17.5</v>
+        <v>2.16</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>30</v>
+        <v>2.16</v>
       </c>
       <c r="BB27" t="n">
-        <v>34</v>
+        <v>2.16</v>
       </c>
       <c r="BC27" t="n">
-        <v>22</v>
+        <v>2.16</v>
       </c>
       <c r="BD27" t="n">
-        <v>29</v>
+        <v>2.16</v>
       </c>
       <c r="BE27" t="n">
-        <v>55</v>
+        <v>2.16</v>
       </c>
       <c r="BF27" t="n">
-        <v>15</v>
+        <v>2.16</v>
       </c>
       <c r="BG27" t="n">
-        <v>17.5</v>
+        <v>2.16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="G28" t="n">
         <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
         <v>1.14</v>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
         <v>1.14</v>
@@ -5849,7 +5849,7 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
         <v>1.01</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="G29" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="H29" t="n">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="I29" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="T29" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U29" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X29" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB29" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y29" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>12</v>
-      </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>12.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
       </c>
       <c r="AH29" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AJ29" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK29" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL29" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AM29" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AP29" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>38</v>
       </c>
       <c r="AT29" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA29" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="BB29" t="n">
         <v>34</v>
       </c>
       <c r="BC29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD29" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE29" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="BF29" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>2.64</v>
       </c>
       <c r="G30" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="H30" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB30" t="n">
         <v>12</v>
       </c>
-      <c r="I30" t="n">
-        <v>13</v>
-      </c>
-      <c r="J30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD30" t="n">
         <v>34</v>
       </c>
-      <c r="Y30" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>420</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>27</v>
-      </c>
       <c r="BE30" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>6.6</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>2.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.12</v>
+        <v>1.74</v>
       </c>
       <c r="S31" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>36</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,19 +6568,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>1.04</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
         <v>1.04</v>
@@ -6589,10 +6589,10 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6601,22 +6601,22 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="P32" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6628,7 +6628,7 @@
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,52 +6685,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,68 +6762,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="H33" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I33" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>1.09</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="O33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.38</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.76</v>
-      </c>
       <c r="X33" t="n">
         <v>1000</v>
       </c>
@@ -6879,69 +6879,69 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,73 +6956,73 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.29</v>
+        <v>2.08</v>
       </c>
       <c r="G34" t="n">
-        <v>1.34</v>
+        <v>2.32</v>
       </c>
       <c r="H34" t="n">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="J34" t="n">
-        <v>4.9</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
         <v>3.05</v>
       </c>
       <c r="O34" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P34" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.84</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.46</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>3.9</v>
+        <v>1.76</v>
       </c>
       <c r="X34" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
         <v>1000</v>
@@ -7031,111 +7031,111 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR34" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AS34" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.35</v>
+        <v>6.6</v>
       </c>
       <c r="AU34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC34" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>4.6</v>
       </c>
-      <c r="BD34" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE34" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,78 +7145,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Independiente Petrolero</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G35" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.02</v>
       </c>
-      <c r="K35" t="n">
-        <v>950</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.07</v>
-      </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7225,111 +7225,111 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,36 +7339,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Independiente Petrolero</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>3.1</v>
+        <v>1.25</v>
       </c>
       <c r="H36" t="n">
-        <v>2.9</v>
+        <v>1.09</v>
       </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J36" t="n">
-        <v>2.6</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
-        <v>3.3</v>
+        <v>950</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,67 +7377,67 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="P36" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.26</v>
+        <v>1.07</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="X36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7446,7 +7446,7 @@
         <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
         <v>1000</v>
@@ -7461,69 +7461,69 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,184 +7533,184 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="G37" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="H37" t="n">
-        <v>1.75</v>
+        <v>2.88</v>
       </c>
       <c r="I37" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
-        <v>3.95</v>
+        <v>2.6</v>
       </c>
       <c r="K37" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>4.3</v>
+        <v>1.56</v>
       </c>
       <c r="O37" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="P37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X37" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AV37" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U37" t="n">
+      <c r="AW37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX37" t="n">
         <v>2.18</v>
       </c>
-      <c r="V37" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X37" t="n">
-        <v>23</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AY37" t="n">
-        <v>14.5</v>
+        <v>2.12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>13.5</v>
+        <v>2.24</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>5</v>
+        <v>2.32</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.2</v>
+        <v>2.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 08:31:25</t>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>
@@ -7732,31 +7732,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="G38" t="n">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>1.85</v>
       </c>
       <c r="J38" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7768,143 +7768,337 @@
         <v>4.3</v>
       </c>
       <c r="O38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="R38" t="n">
         <v>1.46</v>
       </c>
       <c r="S38" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="T38" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="U38" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V38" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="W38" t="n">
-        <v>1.94</v>
+        <v>1.23</v>
       </c>
       <c r="X38" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE38" t="n">
         <v>21</v>
       </c>
-      <c r="Y38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>55</v>
-      </c>
       <c r="AF38" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="AG38" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AH38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ38" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="AO38" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="AP38" t="n">
         <v>16</v>
       </c>
       <c r="AQ38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT38" t="n">
         <v>15</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AU38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB38" t="n">
         <v>5</v>
       </c>
-      <c r="AS38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT38" t="n">
+      <c r="BC38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X39" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT39" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AU39" t="n">
         <v>8</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AV39" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX38" t="n">
+      <c r="AW39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX39" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="AY39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="AZ39" t="n">
         <v>13</v>
       </c>
-      <c r="BA38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF38" t="n">
+      <c r="BA39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF39" t="n">
         <v>10</v>
       </c>
-      <c r="BG38" t="n">
-        <v>38</v>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-04-20 08:31:25</t>
+      <c r="BG39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:44:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>1.95</v>
@@ -790,19 +790,19 @@
         <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V2" t="n">
         <v>1.98</v>
@@ -862,7 +862,7 @@
         <v>36</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP2" t="n">
         <v>18.5</v>
@@ -907,20 +907,20 @@
         <v>6</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2" t="n">
         <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
         <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
         <v>1.61</v>
@@ -990,49 +990,49 @@
         <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
         <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="W3" t="n">
         <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
         <v>16.5</v>
@@ -1041,43 +1041,43 @@
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
         <v>16.5</v>
@@ -1089,7 +1089,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>18.5</v>
@@ -1098,7 +1098,7 @@
         <v>34</v>
       </c>
       <c r="BC3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD3" t="n">
         <v>34</v>
@@ -1107,14 +1107,14 @@
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
         <v>5.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1184,31 +1184,31 @@
         <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
       </c>
       <c r="Y4" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
         <v>14.5</v>
@@ -1223,13 +1223,13 @@
         <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1241,13 +1241,13 @@
         <v>13.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AO4" t="n">
         <v>75</v>
@@ -1256,7 +1256,7 @@
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>55</v>
@@ -1271,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
         <v>34</v>
@@ -1280,13 +1280,13 @@
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
         <v>4.9</v>
@@ -1372,7 +1372,7 @@
         <v>2.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
@@ -1390,31 +1390,31 @@
         <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
         <v>12.5</v>
@@ -1423,34 +1423,34 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AP5" t="n">
         <v>18</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>22</v>
@@ -1462,31 +1462,31 @@
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
         <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
         <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
         <v>19.5</v>
@@ -1495,14 +1495,14 @@
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,28 +1563,28 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1599,7 +1599,7 @@
         <v>26</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9</v>
@@ -1611,16 +1611,16 @@
         <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
         <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
         <v>85</v>
@@ -1629,13 +1629,13 @@
         <v>55</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO6" t="n">
         <v>13.5</v>
@@ -1653,7 +1653,7 @@
         <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD6" t="n">
         <v>5.8</v>
       </c>
-      <c r="BB6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>970</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.58</v>
+        <v>1.7</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -1924,43 +1924,43 @@
         <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
         <v>1.38</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P8" t="n">
         <v>1.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.32</v>
       </c>
       <c r="G10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
         <v>2.68</v>
@@ -2321,7 +2321,7 @@
         <v>3.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
         <v>4.8</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2351,7 +2351,7 @@
         <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
         <v>2.32</v>
@@ -2426,13 +2426,13 @@
         <v>4.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AV10" t="n">
         <v>4.1</v>
@@ -2444,16 +2444,16 @@
         <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.4</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>4.8</v>
@@ -2465,14 +2465,14 @@
         <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
         <v>4.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
         <v>13.5</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
         <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
         <v>3.85</v>
@@ -2906,13 +2906,13 @@
         <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
         <v>3.1</v>
@@ -2921,7 +2921,7 @@
         <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
         <v>2.3</v>
@@ -2948,7 +2948,7 @@
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
         <v>30</v>
@@ -2999,16 +2999,16 @@
         <v>75</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR13" t="n">
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3032,10 +3032,10 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
         <v>20</v>
@@ -3044,7 +3044,7 @@
         <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
         <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3118,13 +3118,13 @@
         <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="W15" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT15" t="n">
         <v>9.4</v>
       </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG15" t="n">
+      <c r="AU15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX15" t="n">
         <v>15</v>
       </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY15" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
         <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
@@ -3691,13 +3691,13 @@
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
         <v>2.26</v>
@@ -3715,10 +3715,10 @@
         <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -3733,7 +3733,7 @@
         <v>110</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC17" t="n">
         <v>9</v>
@@ -3757,7 +3757,7 @@
         <v>85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17" t="n">
         <v>34</v>
@@ -3769,7 +3769,7 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
@@ -3784,7 +3784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT17" t="n">
         <v>7.2</v>
@@ -3796,7 +3796,7 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -3805,7 +3805,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BA17" t="n">
         <v>4.2</v>
@@ -3817,20 +3817,20 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3909,10 +3909,10 @@
         <v>2.16</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
         <v>17.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4103,10 +4103,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="X19" t="n">
         <v>30</v>
@@ -4190,7 +4190,7 @@
         <v>2.36</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
         <v>2.22</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>3.55</v>
@@ -4276,13 +4276,13 @@
         <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
         <v>1.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.29</v>
@@ -4297,10 +4297,10 @@
         <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X20" t="n">
         <v>11</v>
@@ -4309,22 +4309,22 @@
         <v>14.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4333,7 +4333,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>80</v>
@@ -4348,13 +4348,13 @@
         <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
         <v>40</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -4378,7 +4378,7 @@
         <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
@@ -4387,7 +4387,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
         <v>65</v>
@@ -4402,7 +4402,7 @@
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF20" t="n">
         <v>15</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.62</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.64</v>
-      </c>
       <c r="H21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.35</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -4473,7 +4473,7 @@
         <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q21" t="n">
         <v>2.26</v>
@@ -4485,13 +4485,13 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W21" t="n">
         <v>1.61</v>
@@ -4533,7 +4533,7 @@
         <v>55</v>
       </c>
       <c r="AJ21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK21" t="n">
         <v>32</v>
@@ -4545,10 +4545,10 @@
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
@@ -4560,7 +4560,7 @@
         <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
@@ -4575,7 +4575,7 @@
         <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
@@ -4587,7 +4587,7 @@
         <v>48</v>
       </c>
       <c r="BB21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
         <v>3.45</v>
@@ -4655,43 +4655,43 @@
         <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P22" t="n">
         <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
         <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y22" t="n">
         <v>17.5</v>
@@ -4703,10 +4703,10 @@
         <v>110</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>21</v>
@@ -4745,16 +4745,16 @@
         <v>80</v>
       </c>
       <c r="AP22" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT22" t="n">
         <v>7.4</v>
@@ -4766,10 +4766,10 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.199999999999999</v>
@@ -4778,29 +4778,29 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H23" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="I23" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,13 +4855,13 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="O23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -4879,10 +4879,10 @@
         <v>1.94</v>
       </c>
       <c r="V23" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="W23" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -5028,19 +5028,19 @@
         <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
         <v>1.45</v>
@@ -5049,13 +5049,13 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
         <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
         <v>2.12</v>
@@ -5073,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5103,10 +5103,10 @@
         <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -5118,7 +5118,7 @@
         <v>38</v>
       </c>
       <c r="AK24" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
@@ -5127,7 +5127,7 @@
         <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO24" t="n">
         <v>65</v>
@@ -5142,7 +5142,7 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -5154,41 +5154,41 @@
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC24" t="n">
         <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
         <v>16.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G26" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
         <v>1.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
@@ -5461,7 +5461,7 @@
         <v>2.12</v>
       </c>
       <c r="V26" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
@@ -5545,7 +5545,7 @@
         <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY26" t="n">
         <v>4.8</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -5631,13 +5631,13 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="O27" t="n">
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -5745,7 +5745,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>2.02</v>
       </c>
       <c r="BA27" t="n">
         <v>2.16</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>1.14</v>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.14</v>
@@ -5852,7 +5852,7 @@
         <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6001,10 +6001,10 @@
         <v>2.6</v>
       </c>
       <c r="H29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I29" t="n">
         <v>2.82</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.84</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6013,7 +6013,7 @@
         <v>3.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -6025,16 +6025,16 @@
         <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R29" t="n">
         <v>1.56</v>
       </c>
       <c r="S29" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T29" t="n">
         <v>1.6</v>
@@ -6052,7 +6052,7 @@
         <v>20</v>
       </c>
       <c r="Y29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z29" t="n">
         <v>21</v>
@@ -6082,7 +6082,7 @@
         <v>14.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ29" t="n">
         <v>36</v>
@@ -6154,11 +6154,11 @@
         <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.64</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.68</v>
-      </c>
       <c r="H30" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>3.5</v>
@@ -6219,28 +6219,28 @@
         <v>1.29</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
         <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U30" t="n">
         <v>2.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6261,7 +6261,7 @@
         <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>32</v>
@@ -6288,19 +6288,19 @@
         <v>40</v>
       </c>
       <c r="AM30" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
         <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP30" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
         <v>18</v>
@@ -6348,11 +6348,11 @@
         <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6383,64 +6383,64 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.31</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.32</v>
-      </c>
       <c r="H31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J31" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="S31" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T31" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U31" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="Z31" t="n">
         <v>120</v>
@@ -6449,28 +6449,28 @@
         <v>460</v>
       </c>
       <c r="AB31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AD31" t="n">
         <v>42</v>
       </c>
       <c r="AE31" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>27</v>
       </c>
       <c r="AI31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ31" t="n">
         <v>10.5</v>
@@ -6485,16 +6485,16 @@
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AO31" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP31" t="n">
         <v>29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AR31" t="n">
         <v>40</v>
@@ -6503,13 +6503,13 @@
         <v>55</v>
       </c>
       <c r="AT31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AW31" t="n">
         <v>44</v>
@@ -6527,7 +6527,7 @@
         <v>40</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
         <v>12.5</v>
@@ -6536,17 +6536,17 @@
         <v>27</v>
       </c>
       <c r="BE31" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BG31" t="n">
         <v>80</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -6616,7 +6616,7 @@
         <v>1.12</v>
       </c>
       <c r="S32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="G33" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="H33" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,146 +6795,146 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="S33" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W33" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H34" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I34" t="n">
         <v>4.3</v>
@@ -7004,19 +7004,19 @@
         <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="T34" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U34" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W34" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7082,13 +7082,13 @@
         <v>4.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT34" t="n">
         <v>6.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AV34" t="n">
         <v>4</v>
@@ -7103,16 +7103,16 @@
         <v>8.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC34" t="n">
         <v>4.4</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>4.3</v>
       </c>
       <c r="BD34" t="n">
         <v>4.6</v>
@@ -7124,11 +7124,11 @@
         <v>4.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -7168,10 +7168,10 @@
         <v>10.5</v>
       </c>
       <c r="I35" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K35" t="n">
         <v>6.2</v>
@@ -7189,19 +7189,19 @@
         <v>1.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="T35" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="U35" t="n">
         <v>1.53</v>
@@ -7213,10 +7213,10 @@
         <v>3.9</v>
       </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7225,104 +7225,104 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AD35" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG35" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AL35" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.4</v>
+        <v>1.88</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="AR35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="AS35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.3</v>
+        <v>1.79</v>
       </c>
       <c r="AU35" t="n">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.6</v>
+        <v>2.18</v>
       </c>
       <c r="AW35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.3</v>
+        <v>1.81</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.3</v>
+        <v>2.14</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="BB35" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.6</v>
+        <v>2.18</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="BG35" t="n">
-        <v>5.9</v>
+        <v>1.84</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="H36" t="n">
-        <v>1.09</v>
+        <v>13.5</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,37 +7377,37 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P36" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.08</v>
+        <v>1.74</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.81</v>
+        <v>5.7</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="Y36" t="n">
         <v>1000</v>
@@ -7419,104 +7419,104 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G37" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="H37" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,10 +7571,10 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P37" t="n">
         <v>1.56</v>
@@ -7592,13 +7592,13 @@
         <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V37" t="n">
         <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X37" t="n">
         <v>970</v>
@@ -7640,7 +7640,7 @@
         <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU37" t="n">
         <v>2.02</v>
       </c>
-      <c r="AQ37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AV37" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -7747,10 +7747,10 @@
         <v>5.2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I38" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J38" t="n">
         <v>3.95</v>
@@ -7783,7 +7783,7 @@
         <v>2.74</v>
       </c>
       <c r="T38" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U38" t="n">
         <v>2.18</v>
@@ -7822,7 +7822,7 @@
         <v>46</v>
       </c>
       <c r="AG38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH38" t="n">
         <v>21</v>
@@ -7873,7 +7873,7 @@
         <v>13.5</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY38" t="n">
         <v>14.5</v>
@@ -7882,29 +7882,29 @@
         <v>13.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB38" t="n">
         <v>5</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF38" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>4.8</v>
       </c>
       <c r="BG38" t="n">
         <v>7.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G39" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,34 +7959,34 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O39" t="n">
         <v>1.26</v>
       </c>
       <c r="P39" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.92</v>
       </c>
       <c r="T39" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U39" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V39" t="n">
         <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>21</v>
@@ -8001,22 +8001,22 @@
         <v>100</v>
       </c>
       <c r="AB39" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC39" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD39" t="n">
         <v>16.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH39" t="n">
         <v>17</v>
@@ -8025,19 +8025,19 @@
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK39" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
         <v>48</v>
@@ -8052,10 +8052,10 @@
         <v>24</v>
       </c>
       <c r="AS39" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AT39" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU39" t="n">
         <v>8</v>
@@ -8064,41 +8064,41 @@
         <v>14.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BB39" t="n">
         <v>19.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE39" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="BF39" t="n">
         <v>10</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.199999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 10:44:51</t>
+          <t>2026-04-20 12:58:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -763,7 +763,7 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="I2" t="n">
         <v>2.02</v>
@@ -781,28 +781,28 @@
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q2" t="n">
         <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="V2" t="n">
         <v>1.98</v>
@@ -811,40 +811,40 @@
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
         <v>14</v>
       </c>
       <c r="Z2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG2" t="n">
         <v>16.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>19</v>
-      </c>
       <c r="AH2" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ2" t="n">
         <v>85</v>
@@ -853,28 +853,28 @@
         <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
         <v>75</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
         <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>17.5</v>
@@ -883,44 +883,44 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -951,40 +951,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
         <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R3" t="n">
         <v>1.6</v>
@@ -993,109 +993,109 @@
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AP3" t="n">
         <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>18.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC3" t="n">
         <v>32</v>
@@ -1107,14 +1107,14 @@
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4" t="n">
         <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.21</v>
@@ -1184,19 +1184,19 @@
         <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
         <v>1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1223,7 +1223,7 @@
         <v>90</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1256,10 +1256,10 @@
         <v>22</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AS4" t="n">
         <v>46</v>
@@ -1268,7 +1268,7 @@
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
         <v>17.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -1369,16 +1369,16 @@
         <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
         <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
         <v>1.69</v>
@@ -1393,16 +1393,16 @@
         <v>2.16</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5" t="n">
         <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1417,7 +1417,7 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1432,7 +1432,7 @@
         <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>32</v>
@@ -1456,13 +1456,13 @@
         <v>22</v>
       </c>
       <c r="AS5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT5" t="n">
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>15.5</v>
@@ -1471,7 +1471,7 @@
         <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
@@ -1483,10 +1483,10 @@
         <v>27</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
         <v>19.5</v>
@@ -1495,14 +1495,14 @@
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
         <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J6" t="n">
         <v>3.8</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,7 +1563,7 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
         <v>1.77</v>
@@ -1581,7 +1581,7 @@
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
@@ -1680,23 +1680,23 @@
         <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE6" t="n">
         <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -1727,34 +1727,34 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>970</v>
       </c>
       <c r="H7" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
         <v>1.89</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
         <v>1.89</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,94 +1969,94 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>680</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX8" t="n">
         <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AZ8" t="n">
         <v>1.03</v>
@@ -2077,14 +2077,14 @@
         <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2357,10 +2357,10 @@
         <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2378,10 +2378,10 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AW10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
         <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
         <v>4.9</v>
@@ -2530,19 +2530,19 @@
         <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
         <v>1.7</v>
@@ -2551,7 +2551,7 @@
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
         <v>2.32</v>
@@ -2575,13 +2575,13 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2596,19 +2596,19 @@
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
@@ -2617,10 +2617,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX11" t="n">
         <v>8.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -2697,91 +2697,91 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.09</v>
+        <v>2.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.52</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -2891,25 +2891,25 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G13" t="n">
         <v>2.42</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2933,13 +2933,13 @@
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.95</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
         <v>1.71</v>
@@ -2963,10 +2963,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF13" t="n">
         <v>16.5</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3041,7 +3041,7 @@
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
         <v>4.2</v>
@@ -3050,11 +3050,11 @@
         <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3306,7 +3306,7 @@
         <v>3.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
         <v>1.87</v>
@@ -3315,34 +3315,34 @@
         <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
         <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB15" t="n">
         <v>14.5</v>
@@ -3354,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
@@ -3369,7 +3369,7 @@
         <v>48</v>
       </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="n">
         <v>44</v>
@@ -3384,7 +3384,7 @@
         <v>40</v>
       </c>
       <c r="AO15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
@@ -3396,7 +3396,7 @@
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3414,35 +3414,35 @@
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
         <v>18</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>1.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
         <v>1.98</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -3676,16 +3676,16 @@
         <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
         <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -3718,7 +3718,7 @@
         <v>1.3</v>
       </c>
       <c r="W17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -3873,10 +3873,10 @@
         <v>3.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,19 +3885,19 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
         <v>3.25</v>
@@ -3954,22 +3954,22 @@
         <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
@@ -3978,10 +3978,10 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
         <v>6.4</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,7 +4002,7 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB18" t="n">
         <v>5</v>
@@ -4011,20 +4011,20 @@
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I19" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="J19" t="n">
         <v>3.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,22 +4079,22 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
         <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="T19" t="n">
         <v>1.45</v>
@@ -4103,13 +4103,13 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
         <v>970</v>
@@ -4145,7 +4145,7 @@
         <v>40</v>
       </c>
       <c r="AJ19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK19" t="n">
         <v>44</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AV19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW19" t="n">
         <v>2.16</v>
       </c>
-      <c r="AW19" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AX19" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.22</v>
+        <v>9.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G20" t="n">
         <v>1.98</v>
@@ -4261,7 +4261,7 @@
         <v>4.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
         <v>3.55</v>
@@ -4288,7 +4288,7 @@
         <v>1.29</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
         <v>1.99</v>
@@ -4297,13 +4297,13 @@
         <v>1.96</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
         <v>2.02</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
         <v>14.5</v>
@@ -4321,10 +4321,10 @@
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
         <v>11</v>
@@ -4348,7 +4348,7 @@
         <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
         <v>16.5</v>
@@ -4357,7 +4357,7 @@
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
         <v>13.5</v>
@@ -4378,7 +4378,7 @@
         <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
@@ -4396,23 +4396,23 @@
         <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD20" t="n">
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF20" t="n">
         <v>15</v>
       </c>
       <c r="BG20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J21" t="n">
         <v>3.3</v>
@@ -4494,7 +4494,7 @@
         <v>1.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
@@ -4557,7 +4557,7 @@
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS21" t="n">
         <v>48</v>
@@ -4596,7 +4596,7 @@
         <v>42</v>
       </c>
       <c r="BE21" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BF21" t="n">
         <v>26</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -4640,28 +4640,28 @@
         <v>1.99</v>
       </c>
       <c r="G22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.36</v>
@@ -4676,19 +4676,19 @@
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
         <v>15.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O23" t="n">
         <v>1.31</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H24" t="n">
         <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J24" t="n">
         <v>3.25</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -5437,19 +5437,19 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
         <v>3.1</v>
@@ -5458,7 +5458,7 @@
         <v>1.74</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
         <v>2</v>
@@ -5470,7 +5470,7 @@
         <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT26" t="n">
         <v>12.5</v>
@@ -5539,44 +5539,44 @@
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>2.06</v>
       </c>
       <c r="H28" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="O28" t="n">
         <v>1.14</v>
@@ -5840,7 +5840,7 @@
         <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H29" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I29" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
         <v>1.33</v>
@@ -6025,7 +6025,7 @@
         <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
         <v>1.69</v>
@@ -6043,10 +6043,10 @@
         <v>2.6</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X29" t="n">
         <v>20</v>
@@ -6061,7 +6061,7 @@
         <v>42</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC29" t="n">
         <v>8.800000000000001</v>
@@ -6073,10 +6073,10 @@
         <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH29" t="n">
         <v>14.5</v>
@@ -6124,10 +6124,10 @@
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -6145,7 +6145,7 @@
         <v>22</v>
       </c>
       <c r="BD29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE29" t="n">
         <v>50</v>
@@ -6154,11 +6154,11 @@
         <v>15</v>
       </c>
       <c r="BG29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
         <v>2.64</v>
@@ -6216,7 +6216,7 @@
         <v>4.2</v>
       </c>
       <c r="O30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P30" t="n">
         <v>2.04</v>
@@ -6231,10 +6231,10 @@
         <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V30" t="n">
         <v>1.5</v>
@@ -6303,7 +6303,7 @@
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS30" t="n">
         <v>38</v>
@@ -6345,14 +6345,14 @@
         <v>65</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG30" t="n">
         <v>24</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
         <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>1.48</v>
@@ -6422,7 +6422,7 @@
         <v>1.81</v>
       </c>
       <c r="S31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T31" t="n">
         <v>1.92</v>
@@ -6476,7 +6476,7 @@
         <v>10.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AL31" t="n">
         <v>29</v>
@@ -6491,7 +6491,7 @@
         <v>170</v>
       </c>
       <c r="AP31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ31" t="n">
         <v>44</v>
@@ -6512,7 +6512,7 @@
         <v>38</v>
       </c>
       <c r="AW31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX31" t="n">
         <v>8.800000000000001</v>
@@ -6521,16 +6521,16 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
       </c>
       <c r="BC31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD31" t="n">
         <v>27</v>
@@ -6542,11 +6542,11 @@
         <v>3.7</v>
       </c>
       <c r="BG31" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K32" t="n">
         <v>950</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="G33" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H33" t="n">
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>4.4</v>
       </c>
       <c r="K33" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6804,13 +6804,13 @@
         <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="R33" t="n">
         <v>1.82</v>
       </c>
       <c r="S33" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T33" t="n">
         <v>1.47</v>
@@ -6819,7 +6819,7 @@
         <v>2.68</v>
       </c>
       <c r="V33" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W33" t="n">
         <v>2.1</v>
@@ -6894,22 +6894,22 @@
         <v>14</v>
       </c>
       <c r="AU33" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
         <v>4.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY33" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA33" t="n">
         <v>4.6</v>
@@ -6918,23 +6918,23 @@
         <v>17.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD33" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BE33" t="n">
         <v>4.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G34" t="n">
         <v>2.3</v>
@@ -6977,10 +6977,10 @@
         <v>4.3</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6995,19 +6995,19 @@
         <v>1.38</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
         <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U34" t="n">
         <v>1.96</v>
@@ -7076,7 +7076,7 @@
         <v>3.75</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR34" t="n">
         <v>4.4</v>
@@ -7085,10 +7085,10 @@
         <v>4.9</v>
       </c>
       <c r="AT34" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU34" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.25</v>
       </c>
       <c r="AV34" t="n">
         <v>4</v>
@@ -7100,7 +7100,7 @@
         <v>3.85</v>
       </c>
       <c r="AY34" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="AZ34" t="n">
         <v>4.2</v>
@@ -7121,14 +7121,14 @@
         <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BG34" t="n">
         <v>4.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -7168,10 +7168,10 @@
         <v>10.5</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
         <v>6.2</v>
@@ -7189,34 +7189,34 @@
         <v>1.34</v>
       </c>
       <c r="P35" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>2.88</v>
+        <v>1.02</v>
       </c>
       <c r="T35" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="U35" t="n">
         <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
         <v>3.9</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7225,10 +7225,10 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AC35" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7237,92 +7237,92 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AG35" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.88</v>
+        <v>5.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.78</v>
+        <v>6.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.84</v>
+        <v>7.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.79</v>
+        <v>3.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.89</v>
+        <v>4.8</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.18</v>
+        <v>6.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.84</v>
+        <v>7.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.81</v>
+        <v>3.7</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.14</v>
+        <v>6.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.84</v>
+        <v>7.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.18</v>
+        <v>6.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.84</v>
+        <v>7.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.84</v>
+        <v>7.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
         <v>1.21</v>
       </c>
       <c r="H36" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="K36" t="n">
         <v>9.800000000000001</v>
@@ -7380,28 +7380,28 @@
         <v>9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P36" t="n">
         <v>3.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R36" t="n">
         <v>2.08</v>
       </c>
       <c r="S36" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="T36" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U36" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
         <v>5.7</v>
@@ -7410,7 +7410,7 @@
         <v>65</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,7 +7419,7 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AC36" t="n">
         <v>27</v>
@@ -7434,10 +7434,10 @@
         <v>13</v>
       </c>
       <c r="AG36" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7446,77 +7446,77 @@
         <v>12.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AL36" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="AV36" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX36" t="n">
         <v>9.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB36" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.54</v>
       </c>
       <c r="G37" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H37" t="n">
         <v>3.3</v>
@@ -7559,7 +7559,7 @@
         <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="K37" t="n">
         <v>3.3</v>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="O37" t="n">
         <v>1.5</v>
@@ -7580,19 +7580,19 @@
         <v>1.56</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
         <v>1.4</v>
@@ -7601,25 +7601,25 @@
         <v>1.59</v>
       </c>
       <c r="X37" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC37" t="n">
         <v>10</v>
       </c>
       <c r="AD37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
@@ -7628,10 +7628,10 @@
         <v>23</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.02</v>
+        <v>5.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.46</v>
+        <v>1.78</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.54</v>
+        <v>1.79</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.44</v>
+        <v>1.77</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.42</v>
+        <v>1.76</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.48</v>
+        <v>1.79</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.54</v>
+        <v>1.82</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H38" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I38" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="J38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
         <v>4.4</v>
@@ -7765,40 +7765,40 @@
         <v>1.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S38" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V38" t="n">
         <v>2.18</v>
       </c>
-      <c r="V38" t="n">
-        <v>2.2</v>
-      </c>
       <c r="W38" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X38" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z38" t="n">
         <v>14</v>
@@ -7810,16 +7810,16 @@
         <v>23</v>
       </c>
       <c r="AC38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD38" t="n">
         <v>11</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>12</v>
       </c>
       <c r="AE38" t="n">
         <v>21</v>
       </c>
       <c r="AF38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG38" t="n">
         <v>22</v>
@@ -7834,7 +7834,7 @@
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
@@ -7846,65 +7846,65 @@
         <v>65</v>
       </c>
       <c r="AO38" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AP38" t="n">
         <v>16</v>
       </c>
       <c r="AQ38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS38" t="n">
         <v>16.5</v>
       </c>
       <c r="AT38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW38" t="n">
         <v>15</v>
       </c>
-      <c r="AU38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AX38" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY38" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ38" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB38" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG38" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>
@@ -7941,7 +7941,7 @@
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
@@ -7959,7 +7959,7 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
         <v>1.26</v>
@@ -7968,10 +7968,10 @@
         <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
         <v>2.92</v>
@@ -8001,7 +8001,7 @@
         <v>100</v>
       </c>
       <c r="AB39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC39" t="n">
         <v>9</v>
@@ -8037,10 +8037,10 @@
         <v>80</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO39" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP39" t="n">
         <v>16</v>
@@ -8052,7 +8052,7 @@
         <v>24</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AT39" t="n">
         <v>9.800000000000001</v>
@@ -8076,29 +8076,29 @@
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB39" t="n">
         <v>19.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BF39" t="n">
         <v>10</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 12:58:28</t>
+          <t>2026-04-20 15:12:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.27</v>
@@ -790,7 +790,7 @@
         <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R2" t="n">
         <v>1.6</v>
@@ -805,7 +805,7 @@
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
@@ -820,13 +820,13 @@
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
@@ -847,7 +847,7 @@
         <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
         <v>42</v>
@@ -865,7 +865,7 @@
         <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
@@ -883,13 +883,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW2" t="n">
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -901,10 +901,10 @@
         <v>18.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BD2" t="n">
         <v>24</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
         <v>2.04</v>
@@ -966,7 +966,7 @@
         <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -996,7 +996,7 @@
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.96</v>
@@ -1026,7 +1026,7 @@
         <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF3" t="n">
         <v>60</v>
@@ -1041,7 +1041,7 @@
         <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK3" t="n">
         <v>42</v>
@@ -1056,7 +1056,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
         <v>17</v>
@@ -1107,14 +1107,14 @@
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
         <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
         <v>1.65</v>
@@ -1214,7 +1214,7 @@
         <v>14.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>32</v>
@@ -1286,7 +1286,7 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.3</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,76 +1363,76 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T5" t="n">
         <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
         <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>32</v>
@@ -1441,19 +1441,19 @@
         <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
         <v>36</v>
@@ -1462,13 +1462,13 @@
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
         <v>11.5</v>
@@ -1477,32 +1477,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1539,19 +1539,19 @@
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1581,7 +1581,7 @@
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>970</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="n">
-        <v>2.96</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
@@ -1763,10 +1763,10 @@
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
         <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="J8" t="n">
         <v>3.15</v>
@@ -1945,7 +1945,7 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.55</v>
@@ -1954,13 +1954,13 @@
         <v>1.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.12</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,122 +1969,122 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AG8" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>120</v>
       </c>
       <c r="AJ8" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="AK8" t="n">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AL8" t="n">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="AM8" t="n">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="AN8" t="n">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>95</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
         <v>2.42</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
         <v>4.3</v>
@@ -2339,16 +2339,16 @@
         <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.61</v>
@@ -2357,122 +2357,122 @@
         <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
         <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>15.5</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.61</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
         <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
@@ -2536,25 +2536,25 @@
         <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U11" t="n">
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X11" t="n">
         <v>25</v>
@@ -2575,7 +2575,7 @@
         <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
         <v>80</v>
@@ -2596,19 +2596,19 @@
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>36</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP11" t="n">
         <v>16</v>
@@ -2617,10 +2617,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX11" t="n">
         <v>8.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BE11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -2727,7 +2727,7 @@
         <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
         <v>2.58</v>
@@ -2736,19 +2736,19 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>9.6</v>
@@ -2757,13 +2757,13 @@
         <v>9.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC12" t="n">
         <v>8</v>
@@ -2775,10 +2775,10 @@
         <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
         <v>26</v>
@@ -2790,7 +2790,7 @@
         <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2808,59 +2808,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT12" t="n">
         <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV12" t="n">
         <v>10.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2915,7 +2915,7 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
         <v>1.42</v>
@@ -2924,7 +2924,7 @@
         <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -2933,10 +2933,10 @@
         <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
         <v>1.36</v>
@@ -3035,7 +3035,7 @@
         <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC13" t="n">
         <v>20</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
         <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
         <v>6.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3321,7 +3321,7 @@
         <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
         <v>2.1</v>
@@ -3354,22 +3354,22 @@
         <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
         <v>48</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK15" t="n">
         <v>44</v>
@@ -3390,13 +3390,13 @@
         <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR15" t="n">
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3405,7 +3405,7 @@
         <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW15" t="n">
         <v>21</v>
@@ -3420,29 +3420,29 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
         <v>18</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>1.88</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>8</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
         <v>3.75</v>
@@ -3688,7 +3688,7 @@
         <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
         <v>3</v>
@@ -3715,10 +3715,10 @@
         <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -3769,7 +3769,7 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
         <v>90</v>
@@ -3808,7 +3808,7 @@
         <v>3.8</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3820,7 +3820,7 @@
         <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -3861,58 +3861,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
         <v>3.3</v>
       </c>
       <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.55</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
         <v>17.5</v>
@@ -3945,25 +3945,25 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO18" t="n">
         <v>36</v>
@@ -3978,19 +3978,19 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,29 +4002,29 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC18" t="n">
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,7 +4079,7 @@
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O19" t="n">
         <v>1.19</v>
@@ -4097,16 +4097,16 @@
         <v>2.52</v>
       </c>
       <c r="T19" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U19" t="n">
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,7 +4163,7 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
@@ -4172,22 +4172,22 @@
         <v>2.12</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="AW19" t="n">
         <v>2.16</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
@@ -4196,7 +4196,7 @@
         <v>9.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BB19" t="n">
         <v>2.24</v>
@@ -4205,10 +4205,10 @@
         <v>2.24</v>
       </c>
       <c r="BD19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BE19" t="n">
         <v>2.26</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>2.28</v>
       </c>
       <c r="BF19" t="n">
         <v>2.28</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.97</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.98</v>
       </c>
       <c r="H20" t="n">
         <v>4.8</v>
@@ -4267,37 +4267,37 @@
         <v>3.55</v>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
         <v>2.02</v>
@@ -4306,7 +4306,7 @@
         <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
         <v>34</v>
@@ -4315,7 +4315,7 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
@@ -4336,7 +4336,7 @@
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="n">
         <v>22</v>
@@ -4348,16 +4348,16 @@
         <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO20" t="n">
         <v>85</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
         <v>13.5</v>
@@ -4372,7 +4372,7 @@
         <v>7.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
         <v>17.5</v>
@@ -4387,7 +4387,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>65</v>
@@ -4396,23 +4396,23 @@
         <v>20</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BF20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4452,13 +4452,13 @@
         <v>3.15</v>
       </c>
       <c r="I21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.25</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
       </c>
       <c r="L21" t="n">
         <v>1.5</v>
@@ -4476,7 +4476,7 @@
         <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
@@ -4485,7 +4485,7 @@
         <v>4.3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
@@ -4494,7 +4494,7 @@
         <v>1.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X21" t="n">
         <v>11</v>
@@ -4509,10 +4509,10 @@
         <v>55</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
         <v>13.5</v>
@@ -4521,7 +4521,7 @@
         <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
@@ -4536,7 +4536,7 @@
         <v>38</v>
       </c>
       <c r="AK21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
         <v>48</v>
@@ -4551,16 +4551,16 @@
         <v>42</v>
       </c>
       <c r="AP21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
         <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
@@ -4575,38 +4575,38 @@
         <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY21" t="n">
         <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB21" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
       </c>
       <c r="BD21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE21" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="BF21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG21" t="n">
         <v>36</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.45</v>
@@ -4661,43 +4661,43 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y22" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>17.5</v>
-      </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
         <v>110</v>
@@ -4706,10 +4706,10 @@
         <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>70</v>
@@ -4721,13 +4721,13 @@
         <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK22" t="n">
         <v>28</v>
@@ -4748,59 +4748,59 @@
         <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT22" t="n">
         <v>7.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV22" t="n">
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="AX22" t="n">
         <v>10.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>18.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="J23" t="n">
         <v>3.3</v>
@@ -4855,10 +4855,10 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.87</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
         <v>1.86</v>
@@ -4870,19 +4870,19 @@
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="T23" t="n">
         <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="V23" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W23" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H24" t="n">
         <v>3.55</v>
@@ -5040,7 +5040,7 @@
         <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.45</v>
@@ -5055,7 +5055,7 @@
         <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q24" t="n">
         <v>2.12</v>
@@ -5067,10 +5067,10 @@
         <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
         <v>1.34</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5219,61 +5219,61 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5431,13 +5431,13 @@
         <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>1.29</v>
@@ -5449,16 +5449,16 @@
         <v>1.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
         <v>1.74</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V26" t="n">
         <v>2</v>
@@ -5473,7 +5473,7 @@
         <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
@@ -5530,7 +5530,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT26" t="n">
         <v>12.5</v>
@@ -5539,44 +5539,44 @@
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5613,31 +5613,31 @@
         <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="J27" t="n">
         <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="O27" t="n">
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -5649,19 +5649,19 @@
         <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W27" t="n">
         <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
@@ -5715,13 +5715,13 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AQ27" t="n">
         <v>4.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AS27" t="n">
         <v>12</v>
@@ -5733,44 +5733,44 @@
         <v>5.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AW27" t="n">
         <v>12.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="AY27" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BB27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BF27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BG27" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G28" t="n">
         <v>2.06</v>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O28" t="n">
         <v>1.14</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q28" t="n">
         <v>1.14</v>
@@ -5840,7 +5840,7 @@
         <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.52</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H29" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I29" t="n">
         <v>2.86</v>
@@ -6049,31 +6049,31 @@
         <v>1.64</v>
       </c>
       <c r="X29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
         <v>15.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB29" t="n">
         <v>14</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
       </c>
       <c r="AF29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG29" t="n">
         <v>11.5</v>
@@ -6082,7 +6082,7 @@
         <v>14.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ29" t="n">
         <v>36</v>
@@ -6097,10 +6097,10 @@
         <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP29" t="n">
         <v>19.5</v>
@@ -6112,10 +6112,10 @@
         <v>20</v>
       </c>
       <c r="AS29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
@@ -6127,7 +6127,7 @@
         <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -6148,17 +6148,17 @@
         <v>28</v>
       </c>
       <c r="BE29" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BG29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6198,13 +6198,13 @@
         <v>2.96</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
         <v>1.4</v>
@@ -6231,7 +6231,7 @@
         <v>3.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U30" t="n">
         <v>2.28</v>
@@ -6240,7 +6240,7 @@
         <v>1.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6270,7 +6270,7 @@
         <v>17.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
         <v>16</v>
@@ -6318,10 +6318,10 @@
         <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6389,10 +6389,10 @@
         <v>1.31</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
         <v>6.6</v>
@@ -6401,13 +6401,13 @@
         <v>6.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O31" t="n">
         <v>1.15</v>
@@ -6416,13 +6416,13 @@
         <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R31" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="S31" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T31" t="n">
         <v>1.92</v>
@@ -6434,7 +6434,7 @@
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="X31" t="n">
         <v>36</v>
@@ -6446,7 +6446,7 @@
         <v>120</v>
       </c>
       <c r="AA31" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AB31" t="n">
         <v>12</v>
@@ -6467,7 +6467,7 @@
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>120</v>
@@ -6482,10 +6482,10 @@
         <v>29</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AO31" t="n">
         <v>170</v>
@@ -6494,13 +6494,13 @@
         <v>30</v>
       </c>
       <c r="AQ31" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AR31" t="n">
         <v>40</v>
       </c>
       <c r="AS31" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6521,10 +6521,10 @@
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA31" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB31" t="n">
         <v>10</v>
@@ -6539,14 +6539,14 @@
         <v>40</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="G33" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K33" t="n">
         <v>4.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6795,73 +6795,73 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="R33" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="S33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W33" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X33" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE33" t="n">
         <v>42</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>48</v>
       </c>
       <c r="AF33" t="n">
         <v>19</v>
       </c>
       <c r="AG33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI33" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK33" t="n">
         <v>19</v>
@@ -6873,22 +6873,22 @@
         <v>55</v>
       </c>
       <c r="AN33" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AO33" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT33" t="n">
         <v>14</v>
@@ -6897,44 +6897,44 @@
         <v>9.4</v>
       </c>
       <c r="AV33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC33" t="n">
         <v>14</v>
       </c>
-      <c r="AW33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD33" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="G34" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I34" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,22 +6989,22 @@
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O34" t="n">
         <v>1.38</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
         <v>2.08</v>
       </c>
       <c r="R34" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="T34" t="n">
         <v>1.86</v>
@@ -7013,10 +7013,10 @@
         <v>1.96</v>
       </c>
       <c r="V34" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7031,10 +7031,10 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BF34" t="n">
         <v>15.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7186,10 +7186,10 @@
         <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P35" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q35" t="n">
         <v>1.92</v>
@@ -7201,7 +7201,7 @@
         <v>1.02</v>
       </c>
       <c r="T35" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
         <v>1.53</v>
@@ -7303,7 +7303,7 @@
         <v>7.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC35" t="n">
         <v>5.3</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7356,13 +7356,13 @@
         <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="H36" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
         <v>8.6</v>
@@ -7377,40 +7377,40 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R36" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="T36" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X36" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y36" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,7 +7419,7 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC36" t="n">
         <v>27</v>
@@ -7431,92 +7431,92 @@
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>13</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AK36" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH36" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>17</v>
-      </c>
       <c r="AL36" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="AO36" t="n">
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AT36" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AU36" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
         <v>1.59</v>
       </c>
       <c r="X37" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AQ37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.82</v>
       </c>
-      <c r="AR37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BB37" t="n">
+      <c r="BC37" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BD37" t="n">
         <v>1.77</v>
       </c>
-      <c r="BC37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>1.79</v>
-      </c>
       <c r="BE37" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>1.78</v>
       </c>
       <c r="I38" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -7771,16 +7771,16 @@
         <v>1.25</v>
       </c>
       <c r="P38" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="Q38" t="n">
         <v>1.74</v>
       </c>
       <c r="R38" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S38" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="T38" t="n">
         <v>1.74</v>
@@ -7789,7 +7789,7 @@
         <v>2.22</v>
       </c>
       <c r="V38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W38" t="n">
         <v>1.24</v>
@@ -7801,7 +7801,7 @@
         <v>11</v>
       </c>
       <c r="Z38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA38" t="n">
         <v>20</v>
@@ -7873,7 +7873,7 @@
         <v>15</v>
       </c>
       <c r="AX38" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY38" t="n">
         <v>16</v>
@@ -7882,29 +7882,29 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC38" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC38" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD38" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE38" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF38" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>6.4</v>
       </c>
       <c r="BG38" t="n">
         <v>8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>
@@ -7938,13 +7938,13 @@
         <v>1.92</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H39" t="n">
         <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J39" t="n">
         <v>3.85</v>
@@ -7962,19 +7962,19 @@
         <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S39" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T39" t="n">
         <v>1.69</v>
@@ -7992,10 +7992,10 @@
         <v>21</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
         <v>100</v>
@@ -8004,13 +8004,13 @@
         <v>11</v>
       </c>
       <c r="AC39" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD39" t="n">
         <v>16.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF39" t="n">
         <v>13.5</v>
@@ -8031,13 +8031,13 @@
         <v>19.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO39" t="n">
         <v>50</v>
@@ -8049,10 +8049,10 @@
         <v>15</v>
       </c>
       <c r="AR39" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AS39" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT39" t="n">
         <v>9.800000000000001</v>
@@ -8070,35 +8070,35 @@
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ39" t="n">
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB39" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC39" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD39" t="n">
         <v>8</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BE39" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF39" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>10</v>
-      </c>
       <c r="BG39" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 15:12:44</t>
+          <t>2026-04-20 17:26:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
         <v>4</v>
@@ -835,7 +835,7 @@
         <v>18.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG2" t="n">
         <v>16.5</v>
@@ -847,25 +847,25 @@
         <v>29</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
         <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
@@ -883,13 +883,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BB2" t="n">
         <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BG2" t="n">
         <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
         <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
         <v>26</v>
@@ -1041,16 +1041,16 @@
         <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -1065,13 +1065,13 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
@@ -1080,10 +1080,10 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>13.5</v>
@@ -1092,10 +1092,10 @@
         <v>13.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BC3" t="n">
         <v>32</v>
@@ -1107,14 +1107,14 @@
         <v>48</v>
       </c>
       <c r="BF3" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="BG3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
         <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1175,28 +1175,28 @@
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
         <v>1.45</v>
       </c>
       <c r="R4" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X4" t="n">
         <v>38</v>
@@ -1208,7 +1208,7 @@
         <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB4" t="n">
         <v>14.5</v>
@@ -1220,7 +1220,7 @@
         <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
         <v>13</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK4" t="n">
         <v>13.5</v>
@@ -1247,13 +1247,13 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ4" t="n">
         <v>30</v>
@@ -1268,13 +1268,13 @@
         <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1283,22 +1283,22 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
         <v>4.3</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,67 +1363,67 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
         <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
         <v>18.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI5" t="n">
         <v>48</v>
@@ -1435,16 +1435,16 @@
         <v>19</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
         <v>17.5</v>
@@ -1453,7 +1453,7 @@
         <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>36</v>
@@ -1462,47 +1462,47 @@
         <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
         <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC5" t="n">
         <v>16.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF5" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BG5" t="n">
         <v>24</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>3.95</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
         <v>2.04</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,7 +1563,7 @@
         <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.77</v>
@@ -1572,25 +1572,25 @@
         <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
         <v>14</v>
@@ -1605,40 +1605,40 @@
         <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
         <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
@@ -1650,7 +1650,7 @@
         <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
         <v>14.5</v>
@@ -1662,10 +1662,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.3</v>
@@ -1769,13 +1769,13 @@
         <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U7" t="n">
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
         <v>1.23</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
         <v>6.8</v>
@@ -1930,10 +1930,10 @@
         <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>3.6</v>
@@ -1942,28 +1942,28 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
@@ -1975,10 +1975,10 @@
         <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z8" t="n">
         <v>10</v>
@@ -1987,104 +1987,104 @@
         <v>23</v>
       </c>
       <c r="AB8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AF8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="AK8" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AL8" t="n">
-        <v>330</v>
+        <v>170</v>
       </c>
       <c r="AM8" t="n">
-        <v>600</v>
+        <v>290</v>
       </c>
       <c r="AN8" t="n">
-        <v>600</v>
+        <v>240</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW8" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.9</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG8" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
@@ -2163,112 +2163,112 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
         <v>1.01</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AQ9" t="n">
         <v>1.01</v>
       </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2309,76 +2309,76 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
         <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
         <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>14.5</v>
@@ -2387,7 +2387,7 @@
         <v>38</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
         <v>12</v>
@@ -2396,83 +2396,83 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO10" t="n">
         <v>34</v>
       </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>32</v>
-      </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
         <v>8</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
@@ -2533,7 +2533,7 @@
         <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.64</v>
@@ -2542,7 +2542,7 @@
         <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T11" t="n">
         <v>1.71</v>
@@ -2551,7 +2551,7 @@
         <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
         <v>2.36</v>
@@ -2572,16 +2572,16 @@
         <v>12.5</v>
       </c>
       <c r="AC11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF11" t="n">
         <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
@@ -2599,28 +2599,28 @@
         <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11" t="n">
         <v>70</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2632,19 +2632,19 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AX11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2709,25 +2709,25 @@
         <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>2.52</v>
+        <v>1.51</v>
       </c>
       <c r="O12" t="n">
-        <v>1.54</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
         <v>2.58</v>
@@ -2736,7 +2736,7 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.4</v>
+        <v>2.58</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
@@ -2751,49 +2751,49 @@
         <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z12" t="n">
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>9.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AK12" t="n">
         <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2808,28 +2808,28 @@
         <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU12" t="n">
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
@@ -2838,29 +2838,29 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -2894,22 +2894,22 @@
         <v>2.28</v>
       </c>
       <c r="G13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
         <v>3.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2918,7 +2918,7 @@
         <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P13" t="n">
         <v>1.71</v>
@@ -2942,7 +2942,7 @@
         <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -2957,7 +2957,7 @@
         <v>95</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC13" t="n">
         <v>8.800000000000001</v>
@@ -2990,7 +2990,7 @@
         <v>60</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
         <v>32</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3032,29 +3032,29 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="BC13" t="n">
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
         <v>3.5</v>
@@ -3100,7 +3100,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
         <v>1.96</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
         <v>1.96</v>
@@ -3127,7 +3127,7 @@
         <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
@@ -3154,7 +3154,7 @@
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD14" t="n">
         <v>1000</v>
@@ -3169,13 +3169,13 @@
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.43</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.37</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.42</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G15" t="n">
         <v>3.6</v>
@@ -3312,7 +3312,7 @@
         <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
@@ -3345,10 +3345,10 @@
         <v>40</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD15" t="n">
         <v>14</v>
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
         <v>65</v>
@@ -3396,7 +3396,7 @@
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
@@ -3420,10 +3420,10 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
         <v>25</v>
@@ -3432,17 +3432,17 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
         <v>18</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
@@ -3497,16 +3497,16 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -3515,13 +3515,13 @@
         <v>2.42</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="W16" t="n">
         <v>1.17</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3578,65 +3578,65 @@
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>2.16</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
         <v>3.75</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>3.25</v>
@@ -3700,7 +3700,7 @@
         <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
@@ -3709,7 +3709,7 @@
         <v>4.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U17" t="n">
         <v>1.9</v>
@@ -3718,7 +3718,7 @@
         <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X17" t="n">
         <v>13</v>
@@ -3730,7 +3730,7 @@
         <v>34</v>
       </c>
       <c r="AA17" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB17" t="n">
         <v>9.6</v>
@@ -3742,37 +3742,37 @@
         <v>20</v>
       </c>
       <c r="AE17" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AF17" t="n">
         <v>16</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH17" t="n">
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AJ17" t="n">
         <v>36</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM17" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP17" t="n">
         <v>9.4</v>
@@ -3784,7 +3784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT17" t="n">
         <v>7.2</v>
@@ -3796,7 +3796,7 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -3805,32 +3805,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.24</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
         <v>3.3</v>
@@ -3873,10 +3873,10 @@
         <v>3.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.13</v>
@@ -3885,7 +3885,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
@@ -3906,13 +3906,13 @@
         <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X18" t="n">
         <v>17.5</v>
@@ -3924,61 +3924,61 @@
         <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AF18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,29 +4002,29 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BC18" t="n">
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="G19" t="n">
         <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4085,7 +4085,7 @@
         <v>1.19</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
         <v>1.53</v>
@@ -4094,7 +4094,7 @@
         <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
         <v>1.47</v>
@@ -4103,10 +4103,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4115,43 +4115,43 @@
         <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
         <v>23</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>970</v>
       </c>
       <c r="AE19" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG19" t="n">
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AI19" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4160,65 +4160,65 @@
         <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.98</v>
+        <v>2.46</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.6</v>
+        <v>2.58</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.22</v>
+        <v>2.86</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.24</v>
+        <v>2.86</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.28</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -4276,10 +4276,10 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q20" t="n">
         <v>2.16</v>
@@ -4291,82 +4291,82 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AH20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK20" t="n">
         <v>21</v>
       </c>
-      <c r="AI20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>22</v>
-      </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
         <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -4375,51 +4375,51 @@
         <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE21" t="n">
         <v>55</v>
       </c>
-      <c r="AB21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>40</v>
-      </c>
       <c r="AF21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AK21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>5.3</v>
       </c>
       <c r="AS21" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>50</v>
+        <v>5.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>34</v>
+        <v>5.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="BG21" t="n">
-        <v>36</v>
+        <v>5.3</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
         <v>4.3</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.95</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AF22" t="n">
         <v>15</v>
       </c>
       <c r="AG22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK22" t="n">
         <v>30</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AO22" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.2</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>48</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.2</v>
+        <v>38</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I23" t="n">
         <v>2.22</v>
@@ -4846,7 +4846,7 @@
         <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>2.24</v>
       </c>
       <c r="G24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H24" t="n">
         <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J24" t="n">
         <v>3.25</v>
@@ -5043,28 +5043,28 @@
         <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
         <v>1.72</v>
@@ -5073,13 +5073,13 @@
         <v>2.02</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
         <v>1.73</v>
       </c>
       <c r="X24" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
         <v>15</v>
@@ -5088,19 +5088,19 @@
         <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB24" t="n">
         <v>11</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD24" t="n">
         <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="AF24" t="n">
         <v>17</v>
@@ -5112,25 +5112,25 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="AK24" t="n">
         <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM24" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN24" t="n">
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AP24" t="n">
         <v>10.5</v>
@@ -5142,7 +5142,7 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -5151,44 +5151,44 @@
         <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AX24" t="n">
         <v>10.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="BC24" t="n">
         <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF24" t="n">
         <v>16.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
         <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>3.9</v>
@@ -5258,7 +5258,7 @@
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="T25" t="n">
         <v>2.42</v>
@@ -5276,7 +5276,7 @@
         <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,10 +5285,10 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5297,10 +5297,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5309,7 +5309,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK25" t="n">
         <v>1000</v>
@@ -5330,25 +5330,25 @@
         <v>4.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="AT25" t="n">
         <v>3.45</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="AX25" t="n">
         <v>4.2</v>
@@ -5357,32 +5357,32 @@
         <v>4.9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.68</v>
+        <v>6.8</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.87</v>
+        <v>3.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC25" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.87</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>1.91</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
@@ -5461,7 +5461,7 @@
         <v>2.1</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
@@ -5530,7 +5530,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT26" t="n">
         <v>12.5</v>
@@ -5539,44 +5539,44 @@
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BE26" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
         <v>1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,61 +5631,61 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>1.02</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>1.02</v>
       </c>
       <c r="T27" t="n">
         <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V27" t="n">
         <v>2.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y27" t="n">
         <v>11</v>
       </c>
       <c r="Z27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
         <v>23</v>
       </c>
       <c r="AC27" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD27" t="n">
         <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5694,7 +5694,7 @@
         <v>30</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="n">
         <v>1000</v>
@@ -5712,16 +5712,16 @@
         <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>4.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.95</v>
+        <v>6.8</v>
       </c>
       <c r="AS27" t="n">
         <v>12</v>
@@ -5730,54 +5730,54 @@
         <v>9.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.97</v>
+        <v>6.2</v>
       </c>
       <c r="AW27" t="n">
         <v>12.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.97</v>
+        <v>16</v>
       </c>
       <c r="AY27" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.04</v>
+        <v>13</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.97</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.97</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bol</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.45</v>
+        <v>2.56</v>
       </c>
       <c r="G28" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="H28" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="J28" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="S28" t="n">
-        <v>1.82</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,179 +5986,179 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Academia de Balompie Bol</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.52</v>
+        <v>1.54</v>
       </c>
       <c r="G29" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="I29" t="n">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="R29" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.74</v>
+        <v>1.82</v>
       </c>
       <c r="T29" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>19.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>14.5</v>
+        <v>1.14</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>1.14</v>
       </c>
       <c r="AS29" t="n">
-        <v>40</v>
+        <v>1.14</v>
       </c>
       <c r="AT29" t="n">
-        <v>13</v>
+        <v>1.1</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.6</v>
+        <v>1.11</v>
       </c>
       <c r="AV29" t="n">
-        <v>12</v>
+        <v>1.14</v>
       </c>
       <c r="AW29" t="n">
-        <v>24</v>
+        <v>1.14</v>
       </c>
       <c r="AX29" t="n">
-        <v>17.5</v>
+        <v>1.14</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>1.11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>14</v>
+        <v>1.14</v>
       </c>
       <c r="BA29" t="n">
-        <v>30</v>
+        <v>1.14</v>
       </c>
       <c r="BB29" t="n">
-        <v>34</v>
+        <v>1.14</v>
       </c>
       <c r="BC29" t="n">
-        <v>22</v>
+        <v>1.12</v>
       </c>
       <c r="BD29" t="n">
-        <v>28</v>
+        <v>1.14</v>
       </c>
       <c r="BE29" t="n">
-        <v>55</v>
+        <v>1.14</v>
       </c>
       <c r="BF29" t="n">
-        <v>14</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
-        <v>17.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="G30" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H30" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.55</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U30" t="n">
         <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6249,79 +6249,79 @@
         <v>13</v>
       </c>
       <c r="Z30" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC30" t="n">
         <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM30" t="n">
         <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP30" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -6330,29 +6330,29 @@
         <v>15</v>
       </c>
       <c r="BA30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G31" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="H31" t="n">
         <v>12.5</v>
@@ -6395,10 +6395,10 @@
         <v>13</v>
       </c>
       <c r="J31" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -6407,58 +6407,58 @@
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O31" t="n">
         <v>1.15</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S31" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="V31" t="n">
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X31" t="n">
         <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA31" t="n">
-        <v>430</v>
+        <v>560</v>
       </c>
       <c r="AB31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC31" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE31" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AF31" t="n">
         <v>9.4</v>
@@ -6467,49 +6467,49 @@
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AK31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AM31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AP31" t="n">
         <v>30</v>
       </c>
       <c r="AQ31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR31" t="n">
         <v>42</v>
       </c>
-      <c r="AR31" t="n">
-        <v>40</v>
-      </c>
       <c r="AS31" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AT31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU31" t="n">
         <v>14</v>
       </c>
       <c r="AV31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW31" t="n">
         <v>48</v>
@@ -6518,42 +6518,42 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
         <v>48</v>
       </c>
       <c r="BB31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
       </c>
       <c r="BD31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BG31" t="n">
         <v>120</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,81 +6563,81 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H32" t="n">
-        <v>1.04</v>
+        <v>1.92</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O32" t="n">
         <v>1.01</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
         <v>1.02</v>
       </c>
       <c r="T32" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U32" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
         <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y32" t="n">
         <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
@@ -6685,69 +6685,69 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>2.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="G33" t="n">
-        <v>1.99</v>
+        <v>3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="I33" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>1.28</v>
       </c>
       <c r="O33" t="n">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.47</v>
+        <v>2.66</v>
       </c>
       <c r="R33" t="n">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="X33" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="AQ33" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.8</v>
+        <v>1.12</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.7</v>
+        <v>1.12</v>
       </c>
       <c r="AT33" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>9.4</v>
+        <v>4.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.7</v>
+        <v>1.12</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.4</v>
+        <v>1.12</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.6</v>
+        <v>1.12</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.1</v>
+        <v>1.12</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.5</v>
+        <v>1.12</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.9</v>
+        <v>1.12</v>
       </c>
       <c r="BB33" t="n">
-        <v>18</v>
+        <v>1.12</v>
       </c>
       <c r="BC33" t="n">
-        <v>14</v>
+        <v>1.12</v>
       </c>
       <c r="BD33" t="n">
-        <v>19</v>
+        <v>1.12</v>
       </c>
       <c r="BE33" t="n">
-        <v>38</v>
+        <v>1.12</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.8</v>
+        <v>1.12</v>
       </c>
       <c r="BG33" t="n">
-        <v>20</v>
+        <v>1.55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,186 +6956,186 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="H34" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I34" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="K34" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="O34" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.08</v>
+        <v>1.47</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="S34" t="n">
-        <v>3.85</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.96</v>
+        <v>2.62</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.4</v>
+        <v>29</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.3</v>
+        <v>14</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AW34" t="n">
         <v>7.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>5.2</v>
+        <v>13.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BC34" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BD34" t="n">
         <v>6.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="BF34" t="n">
-        <v>15.5</v>
+        <v>6</v>
       </c>
       <c r="BG34" t="n">
         <v>7.2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,73 +7150,73 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.29</v>
+        <v>2.22</v>
       </c>
       <c r="G35" t="n">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="H35" t="n">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="I35" t="n">
-        <v>17.5</v>
+        <v>3.95</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="K35" t="n">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
         <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="R35" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="V35" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="W35" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="X35" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="Y35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7225,10 +7225,10 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AC35" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7237,99 +7237,99 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW35" t="n">
         <v>7.2</v>
       </c>
-      <c r="AG35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="AX35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD35" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BE35" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
         <v>7.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Independiente Petrolero</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="G36" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="H36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="X36" t="n">
         <v>16</v>
       </c>
-      <c r="I36" t="n">
-        <v>19</v>
-      </c>
-      <c r="J36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="K36" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="Y36" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX36" t="n">
         <v>3.9</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>70</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>10</v>
-      </c>
       <c r="AY36" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB36" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="BC36" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.46</v>
+        <v>4</v>
       </c>
       <c r="BG36" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,36 +7533,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Independiente Petrolero</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.54</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76</v>
+        <v>1.22</v>
       </c>
       <c r="H37" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>2.96</v>
+        <v>8.6</v>
       </c>
       <c r="K37" t="n">
-        <v>3.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,40 +7571,40 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="P37" t="n">
-        <v>1.56</v>
+        <v>3.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>1.72</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.59</v>
+        <v>5.5</v>
       </c>
       <c r="X37" t="n">
-        <v>12.5</v>
+        <v>70</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z37" t="n">
         <v>1000</v>
@@ -7613,111 +7613,111 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AC37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX37" t="n">
         <v>10</v>
       </c>
-      <c r="AD37" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AY37" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.84</v>
+        <v>6</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.82</v>
+        <v>9.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.81</v>
+        <v>10</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.77</v>
+        <v>6</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,184 +7727,184 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.6</v>
+        <v>2.54</v>
       </c>
       <c r="G38" t="n">
-        <v>5.1</v>
+        <v>2.76</v>
       </c>
       <c r="H38" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="I38" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="K38" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="O38" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.12</v>
+        <v>1.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="R38" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW38" t="n">
         <v>2.66</v>
       </c>
-      <c r="T38" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR38" t="n">
+      <c r="AX38" t="n">
         <v>10</v>
       </c>
-      <c r="AS38" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AY38" t="n">
-        <v>16</v>
+        <v>2.04</v>
       </c>
       <c r="AZ38" t="n">
-        <v>15</v>
+        <v>1.92</v>
       </c>
       <c r="BA38" t="n">
-        <v>6.4</v>
+        <v>2.26</v>
       </c>
       <c r="BB38" t="n">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="BC38" t="n">
-        <v>6.8</v>
+        <v>2.76</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.8</v>
+        <v>1.97</v>
       </c>
       <c r="BE38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BF38" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="BG38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 17:26:11</t>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>
@@ -7926,31 +7926,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.92</v>
+        <v>4.6</v>
       </c>
       <c r="G39" t="n">
-        <v>1.99</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J39" t="n">
         <v>4</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>4.4</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.2</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,146 +7959,340 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O39" t="n">
         <v>1.25</v>
       </c>
       <c r="P39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U39" t="n">
         <v>2.22</v>
       </c>
-      <c r="Q39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.3</v>
-      </c>
       <c r="V39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X39" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:39:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V40" t="n">
         <v>1.3</v>
       </c>
-      <c r="W39" t="n">
+      <c r="W40" t="n">
         <v>2</v>
       </c>
-      <c r="X39" t="n">
+      <c r="X40" t="n">
         <v>21</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y40" t="n">
         <v>21</v>
       </c>
-      <c r="Z39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="Z40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA40" t="n">
         <v>100</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AB40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
         <v>11</v>
       </c>
-      <c r="AC39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO39" t="n">
+      <c r="AO40" t="n">
         <v>50</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AP40" t="n">
         <v>16</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AQ40" t="n">
         <v>15</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AR40" t="n">
         <v>8</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AS40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY40" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV39" t="n">
+      <c r="AZ40" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF39" t="n">
+      <c r="BA40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF40" t="n">
         <v>9.6</v>
       </c>
-      <c r="BG39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-04-20 17:26:11</t>
+      <c r="BG40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:39:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -775,13 +775,13 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
@@ -790,13 +790,13 @@
         <v>2.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -820,7 +820,7 @@
         <v>15</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
         <v>21</v>
@@ -832,7 +832,7 @@
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AF2" t="n">
         <v>32</v>
@@ -841,10 +841,10 @@
         <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ2" t="n">
         <v>160</v>
@@ -853,25 +853,25 @@
         <v>40</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -880,7 +880,7 @@
         <v>17.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
@@ -889,7 +889,7 @@
         <v>15.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE2" t="n">
         <v>34</v>
       </c>
-      <c r="BC2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>38</v>
-      </c>
       <c r="BF2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -951,127 +951,127 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
         <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
         <v>13.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
         <v>20</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ3" t="n">
         <v>500</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL3" t="n">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU3" t="n">
         <v>8.4</v>
@@ -1080,41 +1080,41 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>24</v>
       </c>
-      <c r="AY3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>21</v>
-      </c>
       <c r="BB3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BD3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE3" t="n">
         <v>34</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>48</v>
       </c>
       <c r="BF3" t="n">
         <v>24</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="H4" t="n">
         <v>6.6</v>
@@ -1157,124 +1157,124 @@
         <v>7.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S4" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AA4" t="n">
         <v>190</v>
       </c>
       <c r="AB4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC4" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ4" t="n">
         <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
         <v>30</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
         <v>46</v>
       </c>
       <c r="AT4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1283,7 +1283,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BE4" t="n">
         <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G5" t="n">
         <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
@@ -1357,43 +1357,43 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q5" t="n">
         <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
         <v>1.97</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
         <v>18.5</v>
@@ -1402,19 +1402,19 @@
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB5" t="n">
         <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
         <v>14</v>
@@ -1426,31 +1426,31 @@
         <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP5" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1459,10 +1459,10 @@
         <v>36</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
@@ -1471,38 +1471,38 @@
         <v>36</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1533,61 +1533,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W6" t="n">
         <v>1.31</v>
       </c>
       <c r="X6" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
@@ -1596,64 +1596,64 @@
         <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
         <v>500</v>
       </c>
       <c r="AK6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="n">
         <v>48</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1662,10 +1662,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -1942,10 +1942,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="O8" t="n">
         <v>1.55</v>
@@ -1957,7 +1957,7 @@
         <v>1.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S8" t="n">
         <v>5.5</v>
@@ -1975,25 +1975,25 @@
         <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
         <v>8.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>27</v>
@@ -2002,10 +2002,10 @@
         <v>50</v>
       </c>
       <c r="AG8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
         <v>70</v>
@@ -2032,59 +2032,59 @@
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7</v>
       </c>
-      <c r="AU8" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AV8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AY8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE8" t="n">
         <v>14</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>7</v>
-      </c>
       <c r="BF8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2148,13 @@
         <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.23</v>
+        <v>1.86</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>2.28</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
         <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2345,7 +2345,7 @@
         <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
         <v>3.05</v>
@@ -2354,28 +2354,28 @@
         <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
         <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
@@ -2396,16 +2396,16 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
         <v>25</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
         <v>85</v>
@@ -2414,19 +2414,19 @@
         <v>21</v>
       </c>
       <c r="AO10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2435,13 +2435,13 @@
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
@@ -2450,29 +2450,29 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8</v>
       </c>
       <c r="BE10" t="n">
         <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
         <v>15.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -2823,28 +2823,28 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW12" t="n">
         <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA12" t="n">
         <v>7.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BD12" t="n">
         <v>7.2</v>
@@ -2853,14 +2853,14 @@
         <v>7.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
         <v>2.38</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3041,7 +3041,7 @@
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE13" t="n">
         <v>5.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
         <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="I16" t="n">
         <v>2.02</v>
@@ -3488,7 +3488,7 @@
         <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3536,7 +3536,7 @@
         <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>1000</v>
@@ -3548,7 +3548,7 @@
         <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
         <v>4.2</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G18" t="n">
         <v>2.36</v>
@@ -3924,7 +3924,7 @@
         <v>28</v>
       </c>
       <c r="AA18" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,10 +4002,10 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
         <v>18.5</v>
@@ -4014,7 +4014,7 @@
         <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G19" t="n">
         <v>3.75</v>
@@ -4070,7 +4070,7 @@
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4088,13 +4088,13 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R19" t="n">
         <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T19" t="n">
         <v>1.47</v>
@@ -4112,40 +4112,40 @@
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AA19" t="n">
         <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AC19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD19" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
       </c>
       <c r="AJ19" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
         <v>500</v>
@@ -4154,40 +4154,40 @@
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.58</v>
+        <v>6.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AX19" t="n">
-        <v>2.86</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
         <v>8.800000000000001</v>
@@ -4196,29 +4196,29 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="BG19" t="n">
         <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
         <v>5.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.2</v>
       </c>
       <c r="J20" t="n">
         <v>3.6</v>
@@ -4276,7 +4276,7 @@
         <v>3.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
         <v>1.84</v>
@@ -4294,10 +4294,10 @@
         <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W20" t="n">
         <v>2.1</v>
@@ -4318,7 +4318,7 @@
         <v>8</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
         <v>20</v>
@@ -4330,7 +4330,7 @@
         <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
@@ -4360,13 +4360,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -4381,7 +4381,7 @@
         <v>60</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
         <v>9.4</v>
@@ -4405,14 +4405,14 @@
         <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
         <v>75</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.02</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
         <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>110</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU21" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU21" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
@@ -4724,13 +4724,13 @@
         <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -4790,7 +4790,7 @@
         <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
         <v>27</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
         <v>2.04</v>
@@ -4843,10 +4843,10 @@
         <v>2.22</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,13 +4855,13 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
         <v>2</v>
@@ -4870,16 +4870,16 @@
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
         <v>1.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="V23" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W23" t="n">
         <v>1.29</v>
@@ -4903,7 +4903,7 @@
         <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.02</v>
+        <v>6.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.02</v>
+        <v>1.97</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.02</v>
+        <v>1.86</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.02</v>
+        <v>1.76</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.02</v>
+        <v>1.98</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.02</v>
+        <v>1.71</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5055,10 +5055,10 @@
         <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5109,7 +5109,7 @@
         <v>13.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AI24" t="n">
         <v>500</v>
@@ -5142,7 +5142,7 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
@@ -5154,10 +5154,10 @@
         <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AY24" t="n">
         <v>6.4</v>
@@ -5166,7 +5166,7 @@
         <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB24" t="n">
         <v>5</v>
@@ -5175,10 +5175,10 @@
         <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
         <v>16.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G26" t="n">
         <v>4.7</v>
@@ -5470,13 +5470,13 @@
         <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
         <v>1000</v>
@@ -5485,10 +5485,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF26" t="n">
         <v>1000</v>
@@ -5497,7 +5497,7 @@
         <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5509,16 +5509,16 @@
         <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
         <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
@@ -5530,7 +5530,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT26" t="n">
         <v>12.5</v>
@@ -5539,7 +5539,7 @@
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
@@ -5548,35 +5548,35 @@
         <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD26" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="G27" t="n">
         <v>6.6</v>
@@ -5619,10 +5619,10 @@
         <v>1.88</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5646,7 +5646,7 @@
         <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="T27" t="n">
         <v>1.59</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>1.22</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q28" t="n">
         <v>1.69</v>
@@ -5840,7 +5840,7 @@
         <v>1.56</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5879,10 +5879,10 @@
         <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>14</v>
@@ -5903,13 +5903,13 @@
         <v>60</v>
       </c>
       <c r="AN28" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO28" t="n">
         <v>18.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>14.5</v>
@@ -5933,10 +5933,10 @@
         <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>13.5</v>
@@ -5957,14 +5957,14 @@
         <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG28" t="n">
         <v>17.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6001,16 @@
         <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>1.92</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6043,7 +6043,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
         <v>1.94</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="BG29" t="n">
         <v>1.55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.52</v>
       </c>
       <c r="G30" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H30" t="n">
         <v>3.1</v>
@@ -6216,7 +6216,7 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
         <v>2.02</v>
@@ -6237,7 +6237,7 @@
         <v>2.28</v>
       </c>
       <c r="V30" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W30" t="n">
         <v>1.64</v>
@@ -6252,7 +6252,7 @@
         <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB30" t="n">
         <v>11.5</v>
@@ -6291,7 +6291,7 @@
         <v>85</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>30</v>
@@ -6327,7 +6327,7 @@
         <v>11</v>
       </c>
       <c r="AZ30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA30" t="n">
         <v>40</v>
@@ -6348,11 +6348,11 @@
         <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.28</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.29</v>
-      </c>
       <c r="H31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -6410,10 +6410,10 @@
         <v>7.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q31" t="n">
         <v>1.46</v>
@@ -6428,46 +6428,46 @@
         <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V31" t="n">
         <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X31" t="n">
         <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z31" t="n">
         <v>130</v>
       </c>
       <c r="AA31" t="n">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="AB31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC31" t="n">
         <v>16</v>
       </c>
       <c r="AD31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE31" t="n">
         <v>180</v>
       </c>
       <c r="AF31" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>130</v>
@@ -6485,7 +6485,7 @@
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AO31" t="n">
         <v>210</v>
@@ -6494,7 +6494,7 @@
         <v>30</v>
       </c>
       <c r="AQ31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AR31" t="n">
         <v>42</v>
@@ -6503,16 +6503,16 @@
         <v>110</v>
       </c>
       <c r="AT31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW31" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX31" t="n">
         <v>8.800000000000001</v>
@@ -6521,13 +6521,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA31" t="n">
         <v>48</v>
       </c>
       <c r="BB31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6536,17 +6536,17 @@
         <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="BF31" t="n">
         <v>3.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>4.8</v>
       </c>
       <c r="G32" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.02</v>
@@ -6601,44 +6601,44 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T32" t="n">
         <v>1.97</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z32" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>11</v>
-      </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6682,10 +6682,10 @@
         <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ32" t="n">
         <v>6</v>
@@ -6694,7 +6694,7 @@
         <v>8.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT32" t="n">
         <v>12</v>
@@ -6709,7 +6709,7 @@
         <v>16.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AY32" t="n">
         <v>15.5</v>
@@ -6718,29 +6718,29 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="BB32" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="K33" t="n">
         <v>10.5</v>
@@ -6795,7 +6795,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O33" t="n">
         <v>1.56</v>
@@ -6840,7 +6840,7 @@
         <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD33" t="n">
         <v>1000</v>
@@ -6885,10 +6885,10 @@
         <v>4.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AT33" t="n">
         <v>4.2</v>
@@ -6897,44 +6897,44 @@
         <v>4.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.12</v>
+        <v>1.52</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.12</v>
+        <v>1.59</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.12</v>
+        <v>1.58</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.12</v>
+        <v>1.59</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.12</v>
+        <v>1.59</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.84</v>
       </c>
       <c r="G34" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H34" t="n">
         <v>3.9</v>
@@ -6980,7 +6980,7 @@
         <v>4.2</v>
       </c>
       <c r="K34" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -7010,7 +7010,7 @@
         <v>1.5</v>
       </c>
       <c r="U34" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V34" t="n">
         <v>1.3</v>
@@ -7028,7 +7028,7 @@
         <v>38</v>
       </c>
       <c r="AA34" t="n">
-        <v>75</v>
+        <v>470</v>
       </c>
       <c r="AB34" t="n">
         <v>16.5</v>
@@ -7037,13 +7037,13 @@
         <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AE34" t="n">
         <v>42</v>
       </c>
       <c r="AF34" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG34" t="n">
         <v>11.5</v>
@@ -7073,40 +7073,40 @@
         <v>26</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AQ34" t="n">
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AX34" t="n">
         <v>13.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>25</v>
+        <v>7.6</v>
       </c>
       <c r="BB34" t="n">
         <v>18</v>
@@ -7115,7 +7115,7 @@
         <v>15.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE34" t="n">
         <v>36</v>
@@ -7124,11 +7124,11 @@
         <v>6</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7213,10 +7213,10 @@
         <v>1.73</v>
       </c>
       <c r="X35" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7234,25 +7234,25 @@
         <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7261,22 +7261,22 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AR35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS35" t="n">
         <v>8.4</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>7.6</v>
       </c>
       <c r="AT35" t="n">
         <v>7.4</v>
@@ -7285,44 +7285,44 @@
         <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY35" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE35" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF35" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.29</v>
       </c>
       <c r="G36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H36" t="n">
         <v>10.5</v>
@@ -7425,7 +7425,7 @@
         <v>13.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
@@ -7512,11 +7512,11 @@
         <v>4</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
         <v>1.29</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S37" t="n">
         <v>1.72</v>
@@ -7601,10 +7601,10 @@
         <v>5.5</v>
       </c>
       <c r="X37" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Y37" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Z37" t="n">
         <v>1000</v>
@@ -7655,7 +7655,7 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ37" t="n">
         <v>6</v>
@@ -7667,7 +7667,7 @@
         <v>6.4</v>
       </c>
       <c r="AT37" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AU37" t="n">
         <v>19.5</v>
@@ -7682,25 +7682,25 @@
         <v>10</v>
       </c>
       <c r="AY37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BA37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB37" t="n">
         <v>9.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF37" t="n">
         <v>2.46</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7747,7 @@
         <v>2.76</v>
       </c>
       <c r="H38" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I38" t="n">
         <v>3.6</v>
@@ -7756,7 +7756,7 @@
         <v>2.96</v>
       </c>
       <c r="K38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7768,7 +7768,7 @@
         <v>2.18</v>
       </c>
       <c r="O38" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="P38" t="n">
         <v>1.48</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.66</v>
+        <v>1.8</v>
       </c>
       <c r="AX38" t="n">
         <v>10</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="BB38" t="n">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.76</v>
+        <v>1.78</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="BF38" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -7959,22 +7959,22 @@
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P39" t="n">
         <v>2.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R39" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T39" t="n">
         <v>1.74</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>
@@ -8153,16 +8153,16 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P40" t="n">
         <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R40" t="n">
         <v>1.5</v>
@@ -8177,7 +8177,7 @@
         <v>2.36</v>
       </c>
       <c r="V40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W40" t="n">
         <v>2</v>
@@ -8243,7 +8243,7 @@
         <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS40" t="n">
         <v>9</v>
@@ -8273,13 +8273,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE40" t="n">
         <v>8.6</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 19:39:32</t>
+          <t>2026-04-20 21:52:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I2" t="n">
         <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.61</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.6</v>
       </c>
       <c r="U2" t="n">
         <v>2.56</v>
       </c>
       <c r="V2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="W2" t="n">
         <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
@@ -826,13 +826,13 @@
         <v>21</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AF2" t="n">
         <v>32</v>
@@ -841,7 +841,7 @@
         <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
         <v>28</v>
@@ -859,10 +859,10 @@
         <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP2" t="n">
         <v>20</v>
@@ -871,7 +871,7 @@
         <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -880,16 +880,16 @@
         <v>17.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
@@ -898,29 +898,29 @@
         <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BF2" t="n">
         <v>24</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>4.1</v>
@@ -981,16 +981,16 @@
         <v>1.21</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
         <v>1.6</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T3" t="n">
         <v>1.6</v>
@@ -999,7 +999,7 @@
         <v>2.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1029,7 +1029,7 @@
         <v>18.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AG3" t="n">
         <v>16.5</v>
@@ -1041,7 +1041,7 @@
         <v>28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="n">
         <v>40</v>
@@ -1056,7 +1056,7 @@
         <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP3" t="n">
         <v>19.5</v>
@@ -1077,16 +1077,16 @@
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
@@ -1098,23 +1098,23 @@
         <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BF3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
         <v>8.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G4" t="n">
         <v>1.49</v>
@@ -1160,37 +1160,37 @@
         <v>5.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
         <v>1.15</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
@@ -1199,91 +1199,91 @@
         <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Z4" t="n">
-        <v>450</v>
+        <v>70</v>
       </c>
       <c r="AA4" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC4" t="n">
         <v>14.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="n">
-        <v>400</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AJ4" t="n">
         <v>15</v>
       </c>
       <c r="AK4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AO4" t="n">
         <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
         <v>46</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU4" t="n">
         <v>11.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>50</v>
@@ -1292,23 +1292,23 @@
         <v>12.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
@@ -1357,46 +1357,46 @@
         <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
         <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1438,7 +1438,7 @@
         <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>10.5</v>
@@ -1447,22 +1447,22 @@
         <v>36</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>36</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
@@ -1483,26 +1483,26 @@
         <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1533,61 +1533,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G6" t="n">
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
@@ -1599,16 +1599,16 @@
         <v>25</v>
       </c>
       <c r="AB6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
@@ -1620,7 +1620,7 @@
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
         <v>500</v>
@@ -1629,22 +1629,22 @@
         <v>44</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AM6" t="n">
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
         <v>12</v>
@@ -1653,7 +1653,7 @@
         <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
         <v>7.8</v>
@@ -1662,7 +1662,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -1674,29 +1674,29 @@
         <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>9.199999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="BE6" t="n">
         <v>21</v>
       </c>
       <c r="BF6" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD7" t="n">
         <v>11.5</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.17</v>
+        <v>8</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.21</v>
+        <v>17.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.22</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.18</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.22</v>
+        <v>12.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.21</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.22</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.22</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.22</v>
+        <v>9.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         <v>5.5</v>
       </c>
       <c r="T8" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
@@ -2041,7 +2041,7 @@
         <v>17.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -2071,7 +2071,7 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE8" t="n">
         <v>14</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2357,7 +2357,7 @@
         <v>2.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
         <v>1.75</v>
@@ -2396,13 +2396,13 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>80</v>
@@ -2411,13 +2411,13 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
         <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2426,7 +2426,7 @@
         <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
         <v>7.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
@@ -2450,29 +2450,29 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.4</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD10" t="n">
         <v>16</v>
       </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
         <v>24</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
         <v>6.2</v>
@@ -2593,7 +2593,7 @@
         <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK11" t="n">
         <v>19</v>
@@ -2605,7 +2605,7 @@
         <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
         <v>70</v>
@@ -2617,10 +2617,10 @@
         <v>17</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
         <v>8.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
         <v>12.5</v>
@@ -2656,17 +2656,17 @@
         <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
         <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2715,19 +2715,19 @@
         <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O12" t="n">
         <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q12" t="n">
         <v>2.58</v>
@@ -2745,7 +2745,7 @@
         <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
         <v>1.51</v>
@@ -2757,7 +2757,7 @@
         <v>9.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
         <v>500</v>
@@ -2769,7 +2769,7 @@
         <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>230</v>
@@ -2790,7 +2790,7 @@
         <v>420</v>
       </c>
       <c r="AK12" t="n">
-        <v>48</v>
+        <v>290</v>
       </c>
       <c r="AL12" t="n">
         <v>170</v>
@@ -2814,7 +2814,7 @@
         <v>15.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>4.9</v>
@@ -2823,13 +2823,13 @@
         <v>6</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
         <v>11</v>
@@ -2838,29 +2838,29 @@
         <v>19</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
         <v>3.25</v>
@@ -2921,10 +2921,10 @@
         <v>1.41</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
         <v>1.26</v>
@@ -2936,10 +2936,10 @@
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
         <v>1.73</v>
@@ -2963,7 +2963,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>60</v>
@@ -2978,7 +2978,7 @@
         <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ13" t="n">
         <v>40</v>
@@ -2996,10 +2996,10 @@
         <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>8.6</v>
@@ -3008,7 +3008,7 @@
         <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3020,7 +3020,7 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
@@ -3032,7 +3032,7 @@
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB13" t="n">
         <v>14.5</v>
@@ -3041,10 +3041,10 @@
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
         <v>3.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I15" t="n">
         <v>2.5</v>
@@ -3297,7 +3297,7 @@
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3354,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF15" t="n">
         <v>25</v>
@@ -3423,7 +3423,7 @@
         <v>5.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC15" t="n">
         <v>25</v>
@@ -3432,7 +3432,7 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
         <v>3.25</v>
@@ -3715,7 +3715,7 @@
         <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17" t="n">
         <v>1.77</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.26</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H18" t="n">
         <v>3.3</v>
@@ -3873,10 +3873,10 @@
         <v>3.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
         <v>1.13</v>
@@ -3894,31 +3894,31 @@
         <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R18" t="n">
         <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>1.69</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>28</v>
@@ -3978,7 +3978,7 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -4002,7 +4002,7 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB18" t="n">
         <v>6.4</v>
@@ -4011,20 +4011,20 @@
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
         <v>3.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I19" t="n">
         <v>2.58</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4163,16 +4163,16 @@
         <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AQ19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AT19" t="n">
         <v>2.8</v>
@@ -4196,19 +4196,19 @@
         <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BB19" t="n">
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BD19" t="n">
         <v>3</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BF19" t="n">
         <v>3.9</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
         <v>1.24</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X20" t="n">
         <v>12</v>
@@ -4309,7 +4309,7 @@
         <v>16</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA20" t="n">
         <v>130</v>
@@ -4318,10 +4318,10 @@
         <v>8</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE20" t="n">
         <v>75</v>
@@ -4366,13 +4366,13 @@
         <v>32</v>
       </c>
       <c r="AS20" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV20" t="n">
         <v>18</v>
@@ -4387,13 +4387,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
         <v>70</v>
       </c>
       <c r="BB20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -4405,14 +4405,14 @@
         <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
         <v>75</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>4.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>3.75</v>
@@ -4470,25 +4470,25 @@
         <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
         <v>2.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
         <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
         <v>1.29</v>
@@ -4500,7 +4500,7 @@
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
         <v>32</v>
@@ -4509,13 +4509,13 @@
         <v>110</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>65</v>
@@ -4527,7 +4527,7 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>75</v>
@@ -4539,31 +4539,31 @@
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7.4</v>
@@ -4572,19 +4572,19 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
         <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4596,17 +4596,17 @@
         <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
         <v>15</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.62</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
         <v>3.25</v>
@@ -4661,16 +4661,16 @@
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
@@ -4730,7 +4730,7 @@
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4784,13 +4784,13 @@
         <v>34</v>
       </c>
       <c r="BC22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
         <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF22" t="n">
         <v>27</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -4843,10 +4843,10 @@
         <v>2.22</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4948,10 +4948,10 @@
         <v>6.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AU23" t="n">
         <v>4.4</v>
@@ -4960,41 +4960,41 @@
         <v>6.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5225,10 +5225,10 @@
         <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>3.4</v>
@@ -5243,7 +5243,7 @@
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="O25" t="n">
         <v>1.53</v>
@@ -5267,13 +5267,13 @@
         <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
         <v>2.3</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="Y25" t="n">
         <v>500</v>
@@ -5291,7 +5291,7 @@
         <v>15</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5330,59 +5330,59 @@
         <v>4.8</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AU25" t="n">
         <v>4.9</v>
       </c>
       <c r="AV25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BE25" t="n">
         <v>6.8</v>
       </c>
-      <c r="AW25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ25" t="n">
+      <c r="BF25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG25" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5425,10 +5425,10 @@
         <v>2.04</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>1.34</v>
@@ -5437,7 +5437,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
         <v>1.29</v>
@@ -5455,10 +5455,10 @@
         <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U26" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
         <v>1.97</v>
@@ -5482,7 +5482,7 @@
         <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="n">
         <v>36</v>
@@ -5509,7 +5509,7 @@
         <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
@@ -5530,16 +5530,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
@@ -5554,29 +5554,29 @@
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF26" t="n">
-        <v>9.4</v>
+        <v>40</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="G27" t="n">
         <v>6.6</v>
@@ -5616,13 +5616,13 @@
         <v>1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5652,10 +5652,10 @@
         <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W27" t="n">
         <v>1.18</v>
@@ -5685,7 +5685,7 @@
         <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AG27" t="n">
         <v>30</v>
@@ -5754,23 +5754,23 @@
         <v>3.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE27" t="n">
         <v>3.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>1.22</v>
       </c>
       <c r="P28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
         <v>1.69</v>
@@ -5885,7 +5885,7 @@
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI28" t="n">
         <v>32</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
         <v>2.06</v>
@@ -6004,13 +6004,13 @@
         <v>3.3</v>
       </c>
       <c r="I29" t="n">
-        <v>110</v>
+        <v>12</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6219,10 +6219,10 @@
         <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R30" t="n">
         <v>1.39</v>
@@ -6231,7 +6231,7 @@
         <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U30" t="n">
         <v>2.28</v>
@@ -6255,10 +6255,10 @@
         <v>55</v>
       </c>
       <c r="AB30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>13.5</v>
@@ -6288,10 +6288,10 @@
         <v>38</v>
       </c>
       <c r="AM30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>30</v>
@@ -6309,40 +6309,40 @@
         <v>44</v>
       </c>
       <c r="AT30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
         <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
         <v>30</v>
       </c>
       <c r="AX30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>15</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15.5</v>
       </c>
       <c r="BA30" t="n">
         <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF30" t="n">
         <v>19</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6389,16 +6389,16 @@
         <v>1.28</v>
       </c>
       <c r="H31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L31" t="n">
         <v>1.27</v>
@@ -6431,10 +6431,10 @@
         <v>1.97</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="X31" t="n">
         <v>36</v>
@@ -6446,7 +6446,7 @@
         <v>130</v>
       </c>
       <c r="AA31" t="n">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AB31" t="n">
         <v>12.5</v>
@@ -6467,7 +6467,7 @@
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
         <v>130</v>
@@ -6485,19 +6485,19 @@
         <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AO31" t="n">
         <v>210</v>
       </c>
       <c r="AP31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AR31" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AS31" t="n">
         <v>110</v>
@@ -6521,7 +6521,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA31" t="n">
         <v>48</v>
@@ -6539,14 +6539,14 @@
         <v>65</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG31" t="n">
         <v>60</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6607,22 +6607,22 @@
         <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
@@ -6718,7 +6718,7 @@
         <v>17.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BB32" t="n">
         <v>11.5</v>
@@ -6733,14 +6733,14 @@
         <v>3.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG32" t="n">
         <v>3.2</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>2.28</v>
       </c>
       <c r="G33" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H33" t="n">
         <v>2.26</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.84</v>
       </c>
       <c r="G34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H34" t="n">
         <v>3.9</v>
@@ -6980,7 +6980,7 @@
         <v>4.2</v>
       </c>
       <c r="K34" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6995,13 +6995,13 @@
         <v>1.15</v>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
       </c>
       <c r="R34" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S34" t="n">
         <v>2.16</v>
@@ -7016,7 +7016,7 @@
         <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X34" t="n">
         <v>32</v>
@@ -7028,7 +7028,7 @@
         <v>38</v>
       </c>
       <c r="AA34" t="n">
-        <v>470</v>
+        <v>160</v>
       </c>
       <c r="AB34" t="n">
         <v>16.5</v>
@@ -7040,19 +7040,19 @@
         <v>18</v>
       </c>
       <c r="AE34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF34" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG34" t="n">
         <v>11.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ34" t="n">
         <v>22</v>
@@ -7070,7 +7070,7 @@
         <v>7.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP34" t="n">
         <v>16</v>
@@ -7079,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS34" t="n">
         <v>8.4</v>
@@ -7094,7 +7094,7 @@
         <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>30</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX34" t="n">
         <v>13.5</v>
@@ -7106,7 +7106,7 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB34" t="n">
         <v>18</v>
@@ -7118,7 +7118,7 @@
         <v>21</v>
       </c>
       <c r="BE34" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF34" t="n">
         <v>6</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7183,13 +7183,13 @@
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O35" t="n">
         <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
         <v>2.14</v>
@@ -7246,7 +7246,7 @@
         <v>60</v>
       </c>
       <c r="AI35" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
         <v>500</v>
@@ -7276,7 +7276,7 @@
         <v>11.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT35" t="n">
         <v>7.4</v>
@@ -7288,7 +7288,7 @@
         <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AX35" t="n">
         <v>6.4</v>
@@ -7300,29 +7300,29 @@
         <v>10.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB35" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BC35" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7577,13 +7577,13 @@
         <v>1.09</v>
       </c>
       <c r="P37" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q37" t="n">
         <v>1.29</v>
       </c>
       <c r="R37" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S37" t="n">
         <v>1.72</v>
@@ -7592,7 +7592,7 @@
         <v>1.87</v>
       </c>
       <c r="U37" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>1.04</v>
@@ -7631,7 +7631,7 @@
         <v>17</v>
       </c>
       <c r="AH37" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7649,22 +7649,22 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT37" t="n">
         <v>14.5</v>
@@ -7673,10 +7673,10 @@
         <v>19.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB37" t="n">
         <v>9.4</v>
@@ -7697,20 +7697,20 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF37" t="n">
         <v>2.46</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
         <v>1.59</v>
@@ -7861,10 +7861,10 @@
         <v>1.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AV38" t="n">
         <v>1.67</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
         <v>1.22</v>
       </c>
       <c r="P39" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q39" t="n">
         <v>1.7</v>
@@ -7974,7 +7974,7 @@
         <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T39" t="n">
         <v>1.74</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>1.91</v>
       </c>
       <c r="G40" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H40" t="n">
         <v>4.1</v>
@@ -8153,34 +8153,34 @@
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S40" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T40" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U40" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V40" t="n">
         <v>1.29</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X40" t="n">
         <v>21</v>
@@ -8207,7 +8207,7 @@
         <v>55</v>
       </c>
       <c r="AF40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG40" t="n">
         <v>10.5</v>
@@ -8231,7 +8231,7 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO40" t="n">
         <v>50</v>
@@ -8243,7 +8243,7 @@
         <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS40" t="n">
         <v>9</v>
@@ -8273,16 +8273,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF40" t="n">
         <v>9.6</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 21:52:36</t>
+          <t>2026-04-21 00:04:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
         <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.95</v>
       </c>
-      <c r="K2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.46</v>
+        <v>2.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="V2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z2" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>15</v>
-      </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AF2" t="n">
         <v>32</v>
@@ -841,86 +841,86 @@
         <v>16.5</v>
       </c>
       <c r="AH2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AP2" t="n">
         <v>15.5</v>
       </c>
-      <c r="AI2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AQ2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>12</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD2" t="n">
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BF2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT3" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
         <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BB3" t="n">
         <v>48</v>
       </c>
       <c r="BC3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD3" t="n">
         <v>36</v>
       </c>
       <c r="BE3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BF3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -1148,167 +1148,167 @@
         <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="K4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="R4" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="T4" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="Y4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Z4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AB4" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
         <v>13.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AO4" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AQ4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AS4" t="n">
         <v>46</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O5" t="n">
         <v>1.33</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X5" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
         <v>24</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AL5" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AM5" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -1533,76 +1533,76 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.85</v>
       </c>
-      <c r="G6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.27</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>11</v>
@@ -1611,92 +1611,92 @@
         <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG6" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
         <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
         <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW6" t="n">
         <v>17.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
         <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -1727,40 +1727,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
@@ -1769,19 +1769,19 @@
         <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
@@ -1793,34 +1793,34 @@
         <v>25</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
       </c>
       <c r="AF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
         <v>34</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>36</v>
       </c>
       <c r="AJ7" t="n">
         <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="n">
         <v>130</v>
@@ -1829,7 +1829,7 @@
         <v>500</v>
       </c>
       <c r="AN7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO7" t="n">
         <v>13</v>
@@ -1859,7 +1859,7 @@
         <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7" t="n">
         <v>12.5</v>
@@ -1868,29 +1868,29 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
         <v>9.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -1921,121 +1921,121 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="I8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="R8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V8" t="n">
         <v>2.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AA8" t="n">
         <v>20</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE8" t="n">
         <v>27</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AG8" t="n">
         <v>27</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI8" t="n">
         <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AK8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
         <v>240</v>
       </c>
       <c r="AO8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP8" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8" t="n">
         <v>17.5</v>
@@ -2044,47 +2044,47 @@
         <v>12</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BE8" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H9" t="n">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J9" t="n">
         <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>1.87</v>
+        <v>2.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,19 +2193,19 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -2309,43 +2309,43 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
         <v>2.32</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
         <v>1.82</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
         <v>3.05</v>
@@ -2354,10 +2354,10 @@
         <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
         <v>1.75</v>
@@ -2369,7 +2369,7 @@
         <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AA10" t="n">
         <v>65</v>
@@ -2384,7 +2384,7 @@
         <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
@@ -2396,7 +2396,7 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
@@ -2411,13 +2411,13 @@
         <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
@@ -2429,13 +2429,13 @@
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>7.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
         <v>15</v>
@@ -2447,16 +2447,16 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB10" t="n">
         <v>16.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
         <v>16</v>
@@ -2468,11 +2468,11 @@
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -2506,167 +2506,167 @@
         <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
         <v>17.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV11" t="n">
         <v>18</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
         <v>18</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.45</v>
-      </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.57</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>1.52</v>
+        <v>2.74</v>
       </c>
       <c r="O12" t="n">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>2.58</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AA12" t="n">
         <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AG12" t="n">
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AI12" t="n">
-        <v>460</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>420</v>
+        <v>230</v>
       </c>
       <c r="AK12" t="n">
         <v>290</v>
       </c>
       <c r="AL12" t="n">
-        <v>170</v>
+        <v>460</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT12" t="n">
         <v>7.8</v>
       </c>
-      <c r="AT12" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.9</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG12" t="n">
         <v>11</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -2894,49 +2894,49 @@
         <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H13" t="n">
         <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
         <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
         <v>1.37</v>
@@ -2948,34 +2948,34 @@
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AB13" t="n">
         <v>8.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
         <v>18</v>
       </c>
       <c r="AE13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
         <v>190</v>
@@ -2984,7 +2984,7 @@
         <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="n">
         <v>60</v>
@@ -2993,22 +2993,22 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>7.6</v>
@@ -3020,31 +3020,31 @@
         <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>12</v>
       </c>
       <c r="AY13" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AZ13" t="n">
         <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
         <v>20</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.4</v>
+        <v>29</v>
       </c>
       <c r="BF13" t="n">
         <v>18.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -3085,97 +3085,97 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="T14" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
         <v>1000</v>
       </c>
       <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
         <v>500</v>
       </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG14" t="n">
         <v>1000</v>
       </c>
       <c r="AH14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI14" t="n">
         <v>500</v>
       </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
@@ -3184,71 +3184,71 @@
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.43</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.41</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.42</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.44</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.36</v>
+        <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.42</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.44</v>
+        <v>13.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.41</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.36</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.37</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.44</v>
+        <v>7.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.44</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.42</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.44</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.44</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
         <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3312,13 +3312,13 @@
         <v>1.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
         <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
         <v>1.74</v>
@@ -3330,13 +3330,13 @@
         <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
         <v>16.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
         <v>18.5</v>
@@ -3369,22 +3369,22 @@
         <v>42</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK15" t="n">
         <v>44</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP15" t="n">
         <v>10</v>
@@ -3402,7 +3402,7 @@
         <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
         <v>9.6</v>
@@ -3411,7 +3411,7 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
@@ -3420,29 +3420,29 @@
         <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>5.7</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>5.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BG15" t="n">
         <v>18</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -3473,67 +3473,67 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="I16" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.32</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.05</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="n">
         <v>900</v>
@@ -3542,101 +3542,101 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>220</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
         <v>95</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
         <v>500</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AO16" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.79</v>
+        <v>7.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>5.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.84</v>
+        <v>8</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.71</v>
+        <v>6.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.84</v>
+        <v>2.74</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.88</v>
+        <v>2.66</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>3.5</v>
@@ -3688,25 +3688,25 @@
         <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T17" t="n">
         <v>1.96</v>
@@ -3718,61 +3718,61 @@
         <v>1.32</v>
       </c>
       <c r="W17" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AA17" t="n">
         <v>500</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>500</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="n">
         <v>500</v>
       </c>
       <c r="AJ17" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="n">
         <v>75</v>
       </c>
       <c r="AL17" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
         <v>9.4</v>
@@ -3784,7 +3784,7 @@
         <v>19.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>7.2</v>
@@ -3793,10 +3793,10 @@
         <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
         <v>9.800000000000001</v>
@@ -3805,10 +3805,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA17" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.7</v>
       </c>
       <c r="BB17" t="n">
         <v>13</v>
@@ -3817,20 +3817,20 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -3861,112 +3861,112 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
         <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="X18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
         <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
         <v>85</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AP18" t="n">
         <v>13</v>
@@ -3975,10 +3975,10 @@
         <v>11</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
         <v>9</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,29 +4002,29 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
         <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -4055,91 +4055,91 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="G19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.75</v>
       </c>
-      <c r="H19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K19" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.14</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="T19" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AA19" t="n">
         <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AC19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AE19" t="n">
         <v>500</v>
       </c>
       <c r="AF19" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
         <v>500</v>
@@ -4157,68 +4157,68 @@
         <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.98</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.94</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.88</v>
+        <v>10.5</v>
       </c>
       <c r="AX19" t="n">
         <v>11.5</v>
       </c>
       <c r="AY19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.96</v>
-      </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.98</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.05</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H20" t="n">
         <v>5</v>
@@ -4267,10 +4267,10 @@
         <v>3.65</v>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
         <v>3.5</v>
@@ -4291,7 +4291,7 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
@@ -4312,19 +4312,19 @@
         <v>36</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
         <v>8</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
         <v>19.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
         <v>10.5</v>
@@ -4372,28 +4372,28 @@
         <v>7.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW20" t="n">
         <v>60</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>70</v>
       </c>
       <c r="BB20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC20" t="n">
         <v>19.5</v>
@@ -4402,7 +4402,7 @@
         <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF20" t="n">
         <v>14</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -4446,13 +4446,13 @@
         <v>1.99</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J21" t="n">
         <v>3.6</v>
@@ -4467,22 +4467,22 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
         <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
         <v>1.9</v>
@@ -4494,13 +4494,13 @@
         <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
         <v>32</v>
@@ -4509,7 +4509,7 @@
         <v>110</v>
       </c>
       <c r="AB21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
@@ -4518,10 +4518,10 @@
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -4530,10 +4530,10 @@
         <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AJ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
@@ -4545,7 +4545,7 @@
         <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>80</v>
@@ -4557,34 +4557,34 @@
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU21" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU21" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
         <v>18.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4596,17 +4596,17 @@
         <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF21" t="n">
         <v>15</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.25</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
@@ -4661,7 +4661,7 @@
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.42</v>
@@ -4679,16 +4679,16 @@
         <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
         <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4703,19 +4703,19 @@
         <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -4730,7 +4730,7 @@
         <v>38</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4751,10 +4751,10 @@
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -4769,7 +4769,7 @@
         <v>34</v>
       </c>
       <c r="AX22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY22" t="n">
         <v>11</v>
@@ -4796,11 +4796,11 @@
         <v>27</v>
       </c>
       <c r="BG22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -4834,43 +4834,43 @@
         <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="I23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
         <v>1.75</v>
@@ -4879,10 +4879,10 @@
         <v>1.98</v>
       </c>
       <c r="V23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W23" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4972,7 +4972,7 @@
         <v>1.41</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BB23" t="n">
         <v>1.44</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5025,82 +5025,82 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="n">
         <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AF24" t="n">
         <v>17</v>
@@ -5133,7 +5133,7 @@
         <v>500</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
         <v>10.5</v>
@@ -5142,10 +5142,10 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
         <v>6.8</v>
@@ -5154,7 +5154,7 @@
         <v>8.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX24" t="n">
         <v>7</v>
@@ -5163,22 +5163,22 @@
         <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BC24" t="n">
         <v>19.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BF24" t="n">
         <v>16.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5219,58 +5219,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G25" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
         <v>3.9</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="M25" t="n">
         <v>1.12</v>
       </c>
       <c r="N25" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
         <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="X25" t="n">
         <v>16.5</v>
@@ -5279,7 +5279,7 @@
         <v>500</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5303,19 +5303,19 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT25" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BA25" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.55</v>
+        <v>50</v>
       </c>
       <c r="BE25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF25" t="n">
         <v>6.8</v>
       </c>
-      <c r="BF25" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BG25" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5422,37 +5422,37 @@
         <v>1.91</v>
       </c>
       <c r="I26" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
         <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
         <v>1.72</v>
@@ -5461,7 +5461,7 @@
         <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
         <v>1.27</v>
@@ -5470,7 +5470,7 @@
         <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z26" t="n">
         <v>500</v>
@@ -5482,7 +5482,7 @@
         <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>36</v>
@@ -5530,7 +5530,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AT26" t="n">
         <v>9</v>
@@ -5539,7 +5539,7 @@
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW26" t="n">
         <v>15.5</v>
@@ -5548,35 +5548,35 @@
         <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ26" t="n">
         <v>13.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE26" t="n">
         <v>3.5</v>
       </c>
-      <c r="BC26" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>9</v>
-      </c>
       <c r="BF26" t="n">
-        <v>40</v>
+        <v>9.4</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5610,61 +5610,61 @@
         <v>4.8</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="I27" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
         <v>1.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="X27" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,28 +5673,28 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
         <v>65</v>
       </c>
       <c r="AF27" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
         <v>1000</v>
@@ -5715,19 +5715,19 @@
         <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>2.82</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.6</v>
+        <v>2.8</v>
       </c>
       <c r="AU27" t="n">
         <v>4.9</v>
@@ -5736,41 +5736,41 @@
         <v>6.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>12.5</v>
+        <v>2.86</v>
       </c>
       <c r="AX27" t="n">
-        <v>16</v>
+        <v>2.8</v>
       </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>2.9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>2.72</v>
       </c>
       <c r="BA27" t="n">
-        <v>20</v>
+        <v>2.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BE27" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G28" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>2.82</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.84</v>
       </c>
       <c r="J28" t="n">
         <v>3.85</v>
@@ -5834,13 +5834,13 @@
         <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S28" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T28" t="n">
         <v>1.6</v>
@@ -5852,19 +5852,19 @@
         <v>1.54</v>
       </c>
       <c r="W28" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
         <v>15.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB28" t="n">
         <v>14</v>
@@ -5903,13 +5903,13 @@
         <v>60</v>
       </c>
       <c r="AN28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO28" t="n">
         <v>18.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>14.5</v>
@@ -5921,7 +5921,7 @@
         <v>40</v>
       </c>
       <c r="AT28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU28" t="n">
         <v>8.6</v>
@@ -5939,7 +5939,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA28" t="n">
         <v>30</v>
@@ -5948,7 +5948,7 @@
         <v>34</v>
       </c>
       <c r="BC28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
         <v>28</v>
@@ -5957,14 +5957,14 @@
         <v>55</v>
       </c>
       <c r="BF28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG28" t="n">
         <v>17.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -5995,46 +5995,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="G29" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.14</v>
+        <v>1.56</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>1.82</v>
+        <v>2.42</v>
       </c>
       <c r="T29" t="n">
         <v>1.01</v>
@@ -6043,10 +6043,10 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BG29" t="n">
         <v>1.55</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -6189,10 +6189,10 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.52</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.54</v>
       </c>
       <c r="H30" t="n">
         <v>3.1</v>
@@ -6207,40 +6207,40 @@
         <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M30" t="n">
         <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O30" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V30" t="n">
         <v>1.46</v>
       </c>
       <c r="W30" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
         <v>14.5</v>
@@ -6252,7 +6252,7 @@
         <v>21</v>
       </c>
       <c r="AA30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB30" t="n">
         <v>11</v>
@@ -6273,7 +6273,7 @@
         <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>44</v>
@@ -6309,10 +6309,10 @@
         <v>44</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
         <v>12.5</v>
@@ -6321,7 +6321,7 @@
         <v>30</v>
       </c>
       <c r="AX30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>10.5</v>
@@ -6333,7 +6333,7 @@
         <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC30" t="n">
         <v>24</v>
@@ -6342,17 +6342,17 @@
         <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BF30" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>13.5</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
@@ -6401,13 +6401,13 @@
         <v>7.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M31" t="n">
         <v>1.03</v>
       </c>
       <c r="N31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.14</v>
@@ -6416,19 +6416,19 @@
         <v>3.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T31" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
         <v>1.07</v>
@@ -6440,7 +6440,7 @@
         <v>36</v>
       </c>
       <c r="Y31" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z31" t="n">
         <v>130</v>
@@ -6458,7 +6458,7 @@
         <v>46</v>
       </c>
       <c r="AE31" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF31" t="n">
         <v>9.199999999999999</v>
@@ -6467,19 +6467,19 @@
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI31" t="n">
         <v>130</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK31" t="n">
         <v>13</v>
       </c>
       <c r="AL31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM31" t="n">
         <v>130</v>
@@ -6488,16 +6488,16 @@
         <v>3.6</v>
       </c>
       <c r="AO31" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ31" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AR31" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AS31" t="n">
         <v>110</v>
@@ -6512,7 +6512,7 @@
         <v>42</v>
       </c>
       <c r="AW31" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AX31" t="n">
         <v>8.800000000000001</v>
@@ -6521,13 +6521,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BB31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC31" t="n">
         <v>12</v>
@@ -6536,17 +6536,17 @@
         <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="BF31" t="n">
         <v>3.45</v>
       </c>
       <c r="BG31" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -6580,61 +6580,61 @@
         <v>4.8</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H32" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="I32" t="n">
         <v>1.99</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O32" t="n">
         <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
         <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="Z32" t="n">
         <v>11.5</v>
@@ -6646,10 +6646,10 @@
         <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD32" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6694,10 +6694,10 @@
         <v>8.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU32" t="n">
         <v>6.6</v>
@@ -6709,7 +6709,7 @@
         <v>16.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AY32" t="n">
         <v>15.5</v>
@@ -6721,26 +6721,26 @@
         <v>15.5</v>
       </c>
       <c r="BB32" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -6771,46 +6771,46 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.25</v>
       </c>
-      <c r="H33" t="n">
+      <c r="L33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N33" t="n">
         <v>2.26</v>
       </c>
-      <c r="I33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="K33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.29</v>
-      </c>
       <c r="O33" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,10 +6819,10 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6885,10 +6885,10 @@
         <v>4.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AT33" t="n">
         <v>4.2</v>
@@ -6897,44 +6897,44 @@
         <v>4.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.37</v>
+        <v>1.19</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.59</v>
+        <v>1.19</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -6965,97 +6965,97 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H34" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I34" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K34" t="n">
         <v>4.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O34" t="n">
         <v>1.15</v>
       </c>
       <c r="P34" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="Q34" t="n">
         <v>1.47</v>
       </c>
       <c r="R34" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T34" t="n">
         <v>1.5</v>
       </c>
       <c r="U34" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X34" t="n">
         <v>32</v>
       </c>
       <c r="Y34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z34" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA34" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
         <v>16.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD34" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF34" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG34" t="n">
         <v>11.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI34" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ34" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK34" t="n">
         <v>19</v>
@@ -7064,25 +7064,25 @@
         <v>26</v>
       </c>
       <c r="AM34" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AP34" t="n">
         <v>16</v>
       </c>
       <c r="AQ34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT34" t="n">
         <v>13</v>
@@ -7091,10 +7091,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV34" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX34" t="n">
         <v>13.5</v>
@@ -7106,29 +7106,29 @@
         <v>13.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
         <v>18</v>
       </c>
       <c r="BC34" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BD34" t="n">
         <v>21</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -7159,61 +7159,61 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G35" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H35" t="n">
         <v>3.55</v>
       </c>
       <c r="I35" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J35" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
         <v>3.55</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
         <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
         <v>1.39</v>
       </c>
       <c r="P35" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T35" t="n">
         <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W35" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X35" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="n">
         <v>25</v>
@@ -7228,7 +7228,7 @@
         <v>10</v>
       </c>
       <c r="AC35" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD35" t="n">
         <v>1000</v>
@@ -7249,10 +7249,10 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK35" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7267,19 +7267,19 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ35" t="n">
         <v>7</v>
       </c>
       <c r="AR35" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS35" t="n">
-        <v>9</v>
+        <v>3.95</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU35" t="n">
         <v>6.6</v>
@@ -7288,41 +7288,41 @@
         <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AX35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ35" t="n">
         <v>10.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB35" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC35" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>9.4</v>
+        <v>3.9</v>
       </c>
       <c r="BF35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG35" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.29</v>
       </c>
       <c r="G36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H36" t="n">
         <v>10.5</v>
@@ -7377,22 +7377,22 @@
         <v>1.06</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
         <v>1.31</v>
       </c>
       <c r="P36" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R36" t="n">
         <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
         <v>2.44</v>
@@ -7488,7 +7488,7 @@
         <v>3.9</v>
       </c>
       <c r="AY36" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="AZ36" t="n">
         <v>7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -7550,43 +7550,43 @@
         <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H37" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
         <v>8.6</v>
       </c>
       <c r="K37" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O37" t="n">
         <v>1.09</v>
       </c>
       <c r="P37" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="S37" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="T37" t="n">
         <v>1.87</v>
@@ -7595,10 +7595,10 @@
         <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X37" t="n">
         <v>65</v>
@@ -7613,37 +7613,37 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC37" t="n">
         <v>23</v>
       </c>
       <c r="AD37" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK37" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
@@ -7655,16 +7655,16 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT37" t="n">
         <v>14.5</v>
@@ -7673,10 +7673,10 @@
         <v>19.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX37" t="n">
         <v>10</v>
@@ -7685,10 +7685,10 @@
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA37" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB37" t="n">
         <v>9.4</v>
@@ -7697,20 +7697,20 @@
         <v>12</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="BG37" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -7744,43 +7744,43 @@
         <v>2.54</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H38" t="n">
         <v>3.35</v>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N38" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="O38" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P38" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7789,13 +7789,13 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
         <v>1000</v>
@@ -7819,7 +7819,7 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AX38" t="n">
         <v>10</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -7935,52 +7935,52 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G39" t="n">
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="I39" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J39" t="n">
         <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="O39" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P39" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U39" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V39" t="n">
         <v>2.2</v>
@@ -7992,43 +7992,43 @@
         <v>20</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AA39" t="n">
         <v>20</v>
       </c>
       <c r="AB39" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC39" t="n">
         <v>9.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF39" t="n">
         <v>44</v>
       </c>
       <c r="AG39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH39" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ39" t="n">
         <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
         <v>1000</v>
@@ -8037,16 +8037,16 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO39" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AP39" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR39" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
         <v>15</v>
       </c>
       <c r="AX39" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AY39" t="n">
         <v>16</v>
@@ -8076,29 +8076,29 @@
         <v>15</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC39" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BE39" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG39" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>
@@ -8129,58 +8129,58 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G40" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I40" t="n">
         <v>4.4</v>
       </c>
       <c r="J40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K40" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M40" t="n">
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O40" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T40" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U40" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V40" t="n">
         <v>1.29</v>
       </c>
       <c r="W40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X40" t="n">
         <v>21</v>
@@ -8195,7 +8195,7 @@
         <v>100</v>
       </c>
       <c r="AB40" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC40" t="n">
         <v>10.5</v>
@@ -8213,19 +8213,19 @@
         <v>10.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK40" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
@@ -8234,7 +8234,7 @@
         <v>10.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP40" t="n">
         <v>16</v>
@@ -8243,10 +8243,10 @@
         <v>15</v>
       </c>
       <c r="AR40" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AS40" t="n">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="AT40" t="n">
         <v>10</v>
@@ -8270,29 +8270,29 @@
         <v>14.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB40" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC40" t="n">
         <v>16</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF40" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 00:04:55</t>
+          <t>2026-04-21 02:18:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH42"/>
+  <dimension ref="A1:BH43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -784,10 +784,10 @@
         <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>1.91</v>
@@ -796,28 +796,28 @@
         <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA2" t="n">
         <v>25</v>
@@ -826,7 +826,7 @@
         <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>10.5</v>
@@ -835,10 +835,10 @@
         <v>21</v>
       </c>
       <c r="AF2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG2" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
         <v>17.5</v>
@@ -859,7 +859,7 @@
         <v>90</v>
       </c>
       <c r="AN2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
         <v>14</v>
@@ -868,59 +868,59 @@
         <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
         <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>14</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AY2" t="n">
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BC2" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -951,115 +951,115 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G3" t="n">
         <v>3.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I3" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.33</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
         <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T3" t="n">
         <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AB3" t="n">
         <v>17</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
         <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
         <v>65</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>13</v>
       </c>
       <c r="AP3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
@@ -1068,16 +1068,16 @@
         <v>15.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
         <v>19.5</v>
@@ -1095,26 +1095,26 @@
         <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BC3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD3" t="n">
         <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG3" t="n">
         <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1145,97 +1145,97 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G4" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S4" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="X4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y4" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="Z4" t="n">
-        <v>450</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AB4" t="n">
         <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK4" t="n">
         <v>13.5</v>
@@ -1244,55 +1244,55 @@
         <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
         <v>36</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AR4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AS4" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AT4" t="n">
         <v>14.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
         <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BB4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD4" t="n">
         <v>20</v>
@@ -1301,14 +1301,14 @@
         <v>55</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1339,73 +1339,73 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G5" t="n">
         <v>2.06</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.34</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
         <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
         <v>8</v>
@@ -1417,67 +1417,67 @@
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
         <v>70</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
         <v>50</v>
@@ -1486,23 +1486,23 @@
         <v>22</v>
       </c>
       <c r="BC5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE5" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BF5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="I6" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.42</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC6" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
         <v>170</v>
       </c>
       <c r="AK6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM6" t="n">
         <v>100</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>70</v>
       </c>
-      <c r="AM6" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>75</v>
-      </c>
       <c r="AO6" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
         <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AY6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="BD6" t="n">
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BG6" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.54</v>
@@ -1751,146 +1751,146 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
       </c>
       <c r="P7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>18</v>
+        <v>3.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>55</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>38</v>
+        <v>4.1</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>100</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG7" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -1921,40 +1921,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>1.33</v>
@@ -1966,125 +1966,125 @@
         <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>15.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC8" t="n">
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
         <v>60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>70</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>17</v>
+        <v>4.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>27</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.88</v>
@@ -2154,13 +2154,13 @@
         <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
         <v>2.06</v>
@@ -2220,7 +2220,7 @@
         <v>60</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
@@ -2247,7 +2247,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY9" t="n">
         <v>12.5</v>
@@ -2259,26 +2259,26 @@
         <v>13.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE9" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
         <v>9.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>1.61</v>
@@ -2336,13 +2336,13 @@
         <v>2.58</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P10" t="n">
         <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
@@ -2351,82 +2351,82 @@
         <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
         <v>11.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AG10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI10" t="n">
         <v>70</v>
       </c>
       <c r="AJ10" t="n">
-        <v>210</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT10" t="n">
         <v>12</v>
@@ -2441,38 +2441,38 @@
         <v>23</v>
       </c>
       <c r="AX10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA10" t="n">
         <v>55</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD10" t="n">
         <v>14.5</v>
       </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
       <c r="BE10" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I11" t="n">
         <v>6</v>
       </c>
-      <c r="I11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="J11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="X11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
         <v>38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
         <v>2.44</v>
@@ -2709,40 +2709,40 @@
         <v>3.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.47</v>
@@ -2751,13 +2751,13 @@
         <v>1.69</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
         <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
@@ -2766,58 +2766,58 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
       </c>
       <c r="AF12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ12" t="n">
         <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.8</v>
@@ -2826,41 +2826,41 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC12" t="n">
         <v>20</v>
       </c>
-      <c r="BB12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>21</v>
-      </c>
       <c r="BD12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
         <v>30</v>
       </c>
       <c r="BF12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
         <v>20</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
         <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K13" t="n">
         <v>5.3</v>
@@ -2912,13 +2912,13 @@
         <v>1.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P13" t="n">
         <v>2.8</v>
@@ -2927,13 +2927,13 @@
         <v>1.49</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
         <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
         <v>2.44</v>
@@ -2942,7 +2942,7 @@
         <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -2951,13 +2951,13 @@
         <v>29</v>
       </c>
       <c r="Z13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC13" t="n">
         <v>12</v>
@@ -2966,7 +2966,7 @@
         <v>22</v>
       </c>
       <c r="AE13" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
         <v>14</v>
@@ -2981,7 +2981,7 @@
         <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK13" t="n">
         <v>16</v>
@@ -2996,10 +2996,10 @@
         <v>6.2</v>
       </c>
       <c r="AO13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -3008,7 +3008,7 @@
         <v>38</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
         <v>11.5</v>
@@ -3020,7 +3020,7 @@
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3032,10 +3032,10 @@
         <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC13" t="n">
         <v>13</v>
@@ -3044,17 +3044,17 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
         <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
         <v>2.86</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I14" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
@@ -3112,13 +3112,13 @@
         <v>2.74</v>
       </c>
       <c r="O14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R14" t="n">
         <v>1.2</v>
@@ -3130,125 +3130,125 @@
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>14</v>
-      </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>460</v>
+        <v>130</v>
       </c>
       <c r="AJ14" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
         <v>7.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC14" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BE14" t="n">
         <v>13</v>
       </c>
       <c r="BF14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3279,70 +3279,70 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.94</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AB15" t="n">
         <v>10.5</v>
@@ -3351,10 +3351,10 @@
         <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AF15" t="n">
         <v>15.5</v>
@@ -3363,7 +3363,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI15" t="n">
         <v>190</v>
@@ -3372,46 +3372,46 @@
         <v>32</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
@@ -3420,29 +3420,29 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE15" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="BF15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG15" t="n">
         <v>16</v>
       </c>
-      <c r="BG15" t="n">
-        <v>30</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3473,34 +3473,34 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.84</v>
       </c>
       <c r="I16" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
         <v>2.34</v>
@@ -3509,134 +3509,134 @@
         <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
         <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Y16" t="n">
-        <v>110</v>
+        <v>15.5</v>
       </c>
       <c r="Z16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA16" t="n">
         <v>500</v>
       </c>
-      <c r="AA16" t="n">
-        <v>900</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL16" t="n">
         <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
       </c>
       <c r="AQ16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT16" t="n">
         <v>11</v>
       </c>
-      <c r="AR16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>12</v>
-      </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC16" t="n">
         <v>16</v>
       </c>
-      <c r="BC16" t="n">
-        <v>15</v>
-      </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG16" t="n">
         <v>17.5</v>
       </c>
-      <c r="BG16" t="n">
-        <v>15</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3694,13 +3694,13 @@
         <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3712,7 +3712,7 @@
         <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
         <v>1.67</v>
@@ -3730,10 +3730,10 @@
         <v>18.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
         <v>8.199999999999999</v>
@@ -3742,7 +3742,7 @@
         <v>14</v>
       </c>
       <c r="AE17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
         <v>25</v>
@@ -3763,74 +3763,74 @@
         <v>44</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>8.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
         <v>14.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
         <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AX17" t="n">
         <v>19.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
         <v>17.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
         <v>16</v>
       </c>
       <c r="BD17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE17" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>28</v>
       </c>
       <c r="BF17" t="n">
         <v>6.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="G18" t="n">
         <v>5.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="I18" t="n">
         <v>1.8</v>
@@ -3876,16 +3876,16 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
@@ -3900,7 +3900,7 @@
         <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
         <v>1.73</v>
@@ -3930,7 +3930,7 @@
         <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AD18" t="n">
         <v>500</v>
@@ -3939,13 +3939,13 @@
         <v>65</v>
       </c>
       <c r="AF18" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
@@ -3957,13 +3957,13 @@
         <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
@@ -3972,7 +3972,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AR18" t="n">
         <v>10</v>
@@ -3981,7 +3981,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
         <v>8.4</v>
@@ -3993,38 +3993,38 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4055,103 +4055,103 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G19" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>500</v>
+        <v>270</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
         <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM19" t="n">
         <v>580</v>
@@ -4160,28 +4160,28 @@
         <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV19" t="n">
         <v>14</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>13</v>
       </c>
       <c r="AW19" t="n">
         <v>20</v>
@@ -4190,19 +4190,19 @@
         <v>12.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="BB19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>23</v>
@@ -4211,14 +4211,14 @@
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BG19" t="n">
         <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G20" t="n">
         <v>2.1</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
         <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
         <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X20" t="n">
         <v>15.5</v>
@@ -4309,28 +4309,28 @@
         <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA20" t="n">
         <v>80</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>17.5</v>
@@ -4339,80 +4339,80 @@
         <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM20" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO20" t="n">
         <v>210</v>
       </c>
       <c r="AP20" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX20" t="n">
         <v>12</v>
       </c>
-      <c r="AS20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>18.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="BE20" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="BF20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG20" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG20" t="n">
-        <v>36</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>3.25</v>
       </c>
       <c r="H21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I21" t="n">
         <v>2.4</v>
@@ -4497,7 +4497,7 @@
         <v>1.44</v>
       </c>
       <c r="X21" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y21" t="n">
         <v>17</v>
@@ -4506,10 +4506,10 @@
         <v>500</v>
       </c>
       <c r="AA21" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AC21" t="n">
         <v>9.199999999999999</v>
@@ -4518,95 +4518,95 @@
         <v>13.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>500</v>
       </c>
-      <c r="AG21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>900</v>
-      </c>
       <c r="AK21" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>15.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS21" t="n">
         <v>21</v>
       </c>
       <c r="AT21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
         <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE21" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BF21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG21" t="n">
         <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -4655,22 +4655,22 @@
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
@@ -4679,16 +4679,16 @@
         <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -4718,13 +4718,13 @@
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
         <v>20</v>
@@ -4745,10 +4745,10 @@
         <v>90</v>
       </c>
       <c r="AP22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>32</v>
@@ -4766,7 +4766,7 @@
         <v>17.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
@@ -4778,7 +4778,7 @@
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB22" t="n">
         <v>19.5</v>
@@ -4790,7 +4790,7 @@
         <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="BF22" t="n">
         <v>12.5</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Hvidovre</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Kolding IF</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2.72</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.51</v>
@@ -4855,153 +4855,153 @@
         <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG23" t="n">
         <v>11</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>11</v>
       </c>
-      <c r="Z23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AR23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU23" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AV23" t="n">
         <v>16</v>
       </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="AW23" t="n">
         <v>30</v>
       </c>
-      <c r="AO23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>34</v>
-      </c>
       <c r="AX23" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BD23" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BE23" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="BG23" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hvidovre</t>
+          <t>SV Schwechat</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kolding IF</t>
+          <t>Red Star Penzing</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.02</v>
+        <v>2.92</v>
       </c>
       <c r="G24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H24" t="n">
         <v>2.08</v>
       </c>
-      <c r="H24" t="n">
-        <v>4.2</v>
-      </c>
       <c r="I24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
         <v>4.4</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L24" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.32</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="X24" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY24" t="n">
         <v>11</v>
       </c>
-      <c r="Y24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AZ24" t="n">
         <v>11</v>
       </c>
-      <c r="AH24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>20</v>
-      </c>
       <c r="BA24" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>24</v>
+        <v>3.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>29</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>17</v>
+        <v>8.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hillerod Fodbold</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="G25" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="H25" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="I25" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T25" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.83</v>
       </c>
       <c r="U25" t="n">
         <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="X25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD25" t="n">
         <v>13</v>
       </c>
-      <c r="Y25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY25" t="n">
         <v>11</v>
       </c>
-      <c r="AE25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BB25" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BD25" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>29</v>
       </c>
       <c r="BG25" t="n">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SV Ried</t>
+          <t>Hillerod Fodbold</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP26" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y26" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AQ26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS26" t="n">
         <v>13</v>
       </c>
-      <c r="AH26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>50</v>
-      </c>
       <c r="AT26" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AW26" t="n">
         <v>20</v>
       </c>
       <c r="AX26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB26" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>27</v>
-      </c>
       <c r="BC26" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bosnian Premier League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FK Velez Mostar</t>
+          <t>SV Ried</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Siroki Brijeg</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="H27" t="n">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="P27" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="X27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>230</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Y27" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>460</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AQ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE27" t="n">
         <v>14</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="BF27" t="n">
         <v>21</v>
       </c>
-      <c r="AS27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>14</v>
-      </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Bosnian Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,102 +5787,102 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>FK Velez Mostar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>1.66</v>
       </c>
       <c r="G28" t="n">
-        <v>4.7</v>
+        <v>1.73</v>
       </c>
       <c r="H28" t="n">
-        <v>1.91</v>
+        <v>6.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.99</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M28" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.87</v>
+        <v>2.52</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="U28" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>1.27</v>
+        <v>2.36</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="Z28" t="n">
         <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1000</v>
       </c>
-      <c r="AC28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>500</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>60</v>
@@ -5891,87 +5891,87 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL28" t="n">
         <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO28" t="n">
         <v>1000</v>
       </c>
-      <c r="AO28" t="n">
-        <v>55</v>
-      </c>
       <c r="AP28" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AS28" t="n">
         <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.25</v>
+        <v>15</v>
       </c>
       <c r="BC28" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BD28" t="n">
         <v>10.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="G29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>250</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>5.7</v>
       </c>
-      <c r="H29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X29" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AR29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV29" t="n">
         <v>8</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AW29" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AX29" t="n">
         <v>22</v>
       </c>
-      <c r="AF29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AY29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD29" t="n">
         <v>23</v>
       </c>
-      <c r="AH29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="BE29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BF29" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>70</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>75</v>
-      </c>
       <c r="BG29" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Academia de Balompie Bol</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.79</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.56</v>
-      </c>
       <c r="Q30" t="n">
-        <v>1.59</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="Z30" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>900</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>19.5</v>
+        <v>9.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="AG30" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>460</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="AK30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS30" t="n">
         <v>18</v>
       </c>
-      <c r="AL30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>500</v>
-      </c>
-      <c r="AP30" t="n">
+      <c r="AT30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA30" t="n">
         <v>20</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BB30" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BC30" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF30" t="n">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H31" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="J31" t="n">
         <v>3.85</v>
@@ -6401,7 +6401,7 @@
         <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -6410,19 +6410,19 @@
         <v>5.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P31" t="n">
         <v>2.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R31" t="n">
         <v>1.56</v>
       </c>
       <c r="S31" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T31" t="n">
         <v>1.6</v>
@@ -6431,28 +6431,28 @@
         <v>2.6</v>
       </c>
       <c r="V31" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
         <v>12.5</v>
@@ -6461,7 +6461,7 @@
         <v>26</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG31" t="n">
         <v>12</v>
@@ -6473,7 +6473,7 @@
         <v>32</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6488,22 +6488,22 @@
         <v>16</v>
       </c>
       <c r="AO31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU31" t="n">
         <v>8.6</v>
@@ -6515,7 +6515,7 @@
         <v>25</v>
       </c>
       <c r="AX31" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AY31" t="n">
         <v>11.5</v>
@@ -6527,7 +6527,7 @@
         <v>30</v>
       </c>
       <c r="BB31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC31" t="n">
         <v>22</v>
@@ -6542,18 +6542,18 @@
         <v>15</v>
       </c>
       <c r="BG31" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,184 +6563,184 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Academia de Balompie Bol</t>
         </is>
       </c>
       <c r="F32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S32" t="n">
         <v>2.5</v>
       </c>
-      <c r="G32" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.35</v>
-      </c>
       <c r="T32" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="U32" t="n">
         <v>2.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="Y32" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="AA32" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="n">
         <v>55</v>
       </c>
-      <c r="AB32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>34</v>
-      </c>
       <c r="AF32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>44</v>
+        <v>460</v>
       </c>
       <c r="AJ32" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AL32" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AM32" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>500</v>
+      </c>
+      <c r="AP32" t="n">
         <v>20</v>
       </c>
-      <c r="AO32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AR32" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AS32" t="n">
-        <v>44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT32" t="n">
         <v>10.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AW32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX32" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ32" t="n">
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="BB32" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="BD32" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BE32" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="BF32" t="n">
-        <v>17.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG32" t="n">
-        <v>27</v>
+        <v>8.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.26</v>
+        <v>2.48</v>
       </c>
       <c r="G33" t="n">
-        <v>1.27</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
         <v>13.5</v>
       </c>
-      <c r="I33" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="AE33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU33" t="n">
         <v>7.4</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="X33" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>570</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AV33" t="n">
         <v>12.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>180</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>50</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU33" t="n">
+      <c r="AW33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX33" t="n">
         <v>15</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>42</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY33" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="BB33" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BC33" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BD33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE33" t="n">
         <v>70</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="BG33" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.8</v>
+        <v>1.26</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="H34" t="n">
-        <v>1.95</v>
+        <v>13.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1.99</v>
+        <v>14</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="K34" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>7.4</v>
       </c>
       <c r="O34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1.44</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.32</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="S34" t="n">
-        <v>4.4</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U34" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>4.7</v>
       </c>
       <c r="X34" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>190</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG34" t="n">
         <v>11</v>
       </c>
-      <c r="Y34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AH34" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="AO34" t="n">
-        <v>18.5</v>
+        <v>200</v>
       </c>
       <c r="AP34" t="n">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.199999999999999</v>
+        <v>100</v>
       </c>
       <c r="AS34" t="n">
-        <v>15.5</v>
+        <v>110</v>
       </c>
       <c r="AT34" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AW34" t="n">
-        <v>16.5</v>
+        <v>75</v>
       </c>
       <c r="AX34" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BA34" t="n">
-        <v>9.6</v>
+        <v>100</v>
       </c>
       <c r="BB34" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD34" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="BE34" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="BF34" t="n">
-        <v>9.199999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.2</v>
+        <v>80</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Argentinian Primera B Metropolitana</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,117 +7145,117 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Deportivo Merlo</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Comunicaciones B Aires</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="G35" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>1.98</v>
       </c>
       <c r="J35" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="L35" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="N35" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P35" t="n">
         <v>1.67</v>
       </c>
-      <c r="P35" t="n">
-        <v>1.41</v>
-      </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="R35" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y35" t="n">
         <v>7.2</v>
       </c>
-      <c r="Y35" t="n">
-        <v>9</v>
-      </c>
       <c r="Z35" t="n">
-        <v>65</v>
+        <v>10.5</v>
       </c>
       <c r="AA35" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE35" t="n">
         <v>1000</v>
       </c>
-      <c r="AB35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>500</v>
-      </c>
       <c r="AF35" t="n">
-        <v>16.5</v>
+        <v>80</v>
       </c>
       <c r="AG35" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AI35" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
         <v>1000</v>
@@ -7264,72 +7264,72 @@
         <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AT35" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AU35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA35" t="n">
         <v>13</v>
       </c>
-      <c r="AY35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>9</v>
-      </c>
       <c r="BB35" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="BC35" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BD35" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BE35" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Argentinian Primera B Metropolitana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,186 +7344,186 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CD Gualberto Villarroel</t>
+          <t>Deportivo Merlo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Comunicaciones B Aires</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.04</v>
+        <v>2.58</v>
       </c>
       <c r="G36" t="n">
-        <v>2.16</v>
+        <v>2.9</v>
       </c>
       <c r="H36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J36" t="n">
-        <v>4.2</v>
+        <v>2.74</v>
       </c>
       <c r="K36" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="M36" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="N36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X36" t="n">
         <v>7.2</v>
       </c>
-      <c r="O36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X36" t="n">
-        <v>36</v>
-      </c>
       <c r="Y36" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AA36" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB36" t="n">
-        <v>18.5</v>
+        <v>7.4</v>
       </c>
       <c r="AC36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW36" t="n">
         <v>11</v>
       </c>
-      <c r="AD36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF36" t="n">
+      <c r="AX36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>19.5</v>
       </c>
-      <c r="AG36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN36" t="n">
+      <c r="BA36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD36" t="n">
         <v>9</v>
       </c>
-      <c r="AO36" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>7</v>
-      </c>
       <c r="BE36" t="n">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>CD Gualberto Villarroel</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="H37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I37" t="n">
         <v>3.65</v>
       </c>
-      <c r="I37" t="n">
-        <v>3.95</v>
-      </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K37" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="M37" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="O37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V37" t="n">
         <v>1.39</v>
       </c>
-      <c r="P37" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.35</v>
-      </c>
       <c r="W37" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="X37" t="n">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="Y37" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK37" t="n">
         <v>21</v>
       </c>
-      <c r="Z37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>500</v>
-      </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN37" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP37" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="AS37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU37" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV37" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY37" t="n">
         <v>6.2</v>
       </c>
       <c r="AZ37" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA37" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BB37" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC37" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>8.199999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="BG37" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7732,73 +7732,73 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Puerto Cabello</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trujillanos</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="H38" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>3.95</v>
       </c>
       <c r="J38" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
         <v>3.35</v>
       </c>
       <c r="O38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.34</v>
       </c>
-      <c r="P38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
       <c r="W38" t="n">
-        <v>3.9</v>
+        <v>1.78</v>
       </c>
       <c r="X38" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
@@ -7807,111 +7807,111 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF38" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="AG38" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="AH38" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>10.5</v>
+        <v>500</v>
       </c>
       <c r="AK38" t="n">
-        <v>19.5</v>
+        <v>500</v>
       </c>
       <c r="AL38" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ38" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AS38" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT38" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY38" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BC38" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BE38" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,78 +7921,78 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bolivar</t>
+          <t>Puerto Cabello</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Independiente Petrolero</t>
+          <t>Trujillanos</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="G39" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="H39" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="I39" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="K39" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="O39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.07</v>
       </c>
-      <c r="P39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.04</v>
-      </c>
       <c r="W39" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="X39" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="Z39" t="n">
         <v>1000</v>
@@ -8001,111 +8001,111 @@
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="AG39" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AH39" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="AM39" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.36</v>
+        <v>8</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.92</v>
+        <v>5.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.93</v>
+        <v>7.2</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.95</v>
+        <v>8</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.97</v>
+        <v>8.4</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.83</v>
+        <v>6.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.95</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.72</v>
+        <v>3.85</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.74</v>
+        <v>5.4</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.87</v>
+        <v>7.2</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.94</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.85</v>
+        <v>7.6</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.94</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF39" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BG39" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,191 +8115,191 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tecnico Universitario</t>
+          <t>Bolivar</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Independiente Petrolero</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.54</v>
+        <v>1.17</v>
       </c>
       <c r="G40" t="n">
-        <v>2.64</v>
+        <v>1.19</v>
       </c>
       <c r="H40" t="n">
-        <v>3.35</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>3.55</v>
+        <v>18.5</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="L40" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="M40" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.78</v>
+        <v>11</v>
       </c>
       <c r="O40" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="P40" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.62</v>
+        <v>1.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.61</v>
+        <v>6</v>
       </c>
       <c r="X40" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="Y40" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="Z40" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AC40" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
-        <v>970</v>
+        <v>75</v>
       </c>
       <c r="AE40" t="n">
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AG40" t="n">
         <v>15.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>4.4</v>
+        <v>1.91</v>
       </c>
       <c r="AQ40" t="n">
-        <v>8.6</v>
+        <v>1.92</v>
       </c>
       <c r="AR40" t="n">
-        <v>5.6</v>
+        <v>1.93</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.4</v>
+        <v>1.95</v>
       </c>
       <c r="AT40" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="AU40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BB40" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV40" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BC40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>6.4</v>
+        <v>1.83</v>
       </c>
       <c r="BE40" t="n">
-        <v>6.8</v>
+        <v>1.92</v>
       </c>
       <c r="BF40" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.4</v>
+        <v>1.93</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,108 +8309,108 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Tecnico Universitario</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cruz Azul</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4.7</v>
+        <v>2.54</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>2.64</v>
       </c>
       <c r="H41" t="n">
-        <v>1.78</v>
+        <v>3.35</v>
       </c>
       <c r="I41" t="n">
-        <v>1.81</v>
+        <v>3.55</v>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="M41" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N41" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="P41" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.77</v>
+        <v>2.62</v>
       </c>
       <c r="R41" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="S41" t="n">
-        <v>2.96</v>
+        <v>5.3</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="X41" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Y41" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="AA41" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD41" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="AG41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH41" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AI41" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
         <v>1000</v>
@@ -8425,68 +8425,68 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>16.5</v>
+        <v>4</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AY41" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>15</v>
+        <v>5.8</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="BB41" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BD41" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 04:33:11</t>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>
@@ -8508,179 +8508,373 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pumas UNAM</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Cruz Azul</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="G42" t="n">
-        <v>1.95</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>4.4</v>
+        <v>1.82</v>
       </c>
       <c r="J42" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
         <v>4.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
         <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P42" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="U42" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="W42" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="X42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Z42" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AB42" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AF42" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AG42" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AH42" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AI42" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ42" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>18.5</v>
+        <v>75</v>
       </c>
       <c r="AL42" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO42" t="n">
         <v>10.5</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-04-21 06:47:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X43" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI43" t="n">
         <v>1000</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AJ43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP43" t="n">
         <v>16</v>
       </c>
-      <c r="AQ42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR42" t="n">
+      <c r="AQ43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR43" t="n">
         <v>30</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AS43" t="n">
         <v>75</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AT43" t="n">
         <v>10</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AU43" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AV43" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AW43" t="n">
         <v>34</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AX43" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ42" t="n">
+      <c r="AY43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ43" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA42" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC42" t="n">
+      <c r="BA43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC43" t="n">
         <v>16</v>
       </c>
-      <c r="BD42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG42" t="n">
+      <c r="BD43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG43" t="n">
         <v>34</v>
       </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>2026-04-21 04:33:11</t>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-04-21 06:47:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-21.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>1.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>2.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>1.52</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AE2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>240</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
         <v>13.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AW2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC2" t="n">
         <v>80</v>
       </c>
-      <c r="AK2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>38</v>
-      </c>
       <c r="BD2" t="n">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="BE2" t="n">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="BG2" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="U3" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W3" t="n">
         <v>1.46</v>
       </c>
       <c r="X3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
         <v>22</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>24</v>
       </c>
       <c r="AG3" t="n">
         <v>13.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AJ3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="n">
         <v>55</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="n">
         <v>32</v>
       </c>
-      <c r="AL3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>22</v>
-      </c>
       <c r="AO3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT3" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BB3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BC3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="BF3" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="H4" t="n">
         <v>6</v>
@@ -1157,158 +1157,158 @@
         <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.56</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="X4" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="Z4" t="n">
         <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
         <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK4" t="n">
         <v>16</v>
       </c>
-      <c r="AK4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AL4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AS4" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AT4" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1339,142 +1339,142 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.02</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
         <v>14</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX5" t="n">
         <v>14</v>
       </c>
-      <c r="Z5" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>11</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
@@ -1483,26 +1483,26 @@
         <v>50</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
         <v>17</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>10.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW6" t="n">
         <v>19</v>
       </c>
-      <c r="AF6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK6" t="n">
+      <c r="AX6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE6" t="n">
         <v>65</v>
       </c>
-      <c r="AL6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="BF6" t="n">
         <v>26</v>
       </c>
-      <c r="AY6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>30</v>
-      </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>2.1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
         <v>4.4</v>
@@ -1751,7 +1751,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
         <v>1.46</v>
@@ -1760,7 +1760,7 @@
         <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.22</v>
@@ -1772,19 +1772,19 @@
         <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X7" t="n">
         <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>36</v>
@@ -1793,58 +1793,58 @@
         <v>120</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1856,7 +1856,7 @@
         <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
         <v>10.5</v>
@@ -1868,29 +1868,29 @@
         <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BC7" t="n">
         <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF7" t="n">
         <v>21</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="H8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.44</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.45</v>
-      </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
         <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AO8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
         <v>4.6</v>
@@ -2142,10 +2142,10 @@
         <v>4.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q9" t="n">
         <v>1.8</v>
@@ -2169,7 +2169,7 @@
         <v>1.28</v>
       </c>
       <c r="X9" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>38</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>19.5</v>
@@ -2205,7 +2205,7 @@
         <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>440</v>
       </c>
       <c r="AK9" t="n">
         <v>55</v>
@@ -2214,7 +2214,7 @@
         <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN9" t="n">
         <v>60</v>
@@ -2223,10 +2223,10 @@
         <v>11.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>10</v>
@@ -2235,50 +2235,50 @@
         <v>17.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU9" t="n">
         <v>7.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="BG9" t="n">
         <v>9.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I10" t="n">
         <v>1.99</v>
@@ -2339,7 +2339,7 @@
         <v>1.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
         <v>2.8</v>
@@ -2351,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
         <v>1.64</v>
@@ -2369,10 +2369,10 @@
         <v>6.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB10" t="n">
         <v>13.5</v>
@@ -2390,7 +2390,7 @@
         <v>40</v>
       </c>
       <c r="AG10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
         <v>29</v>
@@ -2399,7 +2399,7 @@
         <v>70</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>170</v>
       </c>
       <c r="AK10" t="n">
         <v>120</v>
@@ -2414,7 +2414,7 @@
         <v>210</v>
       </c>
       <c r="AO10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP10" t="n">
         <v>7.4</v>
@@ -2426,10 +2426,10 @@
         <v>8.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2441,10 +2441,10 @@
         <v>23</v>
       </c>
       <c r="AX10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2453,26 +2453,26 @@
         <v>55</v>
       </c>
       <c r="BB10" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC10" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BD10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2503,148 +2503,148 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y11" t="n">
         <v>22</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH11" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>75</v>
       </c>
       <c r="AJ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>18.5</v>
       </c>
-      <c r="AK11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>15</v>
-      </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AS11" t="n">
         <v>85</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
         <v>15</v>
@@ -2653,20 +2653,20 @@
         <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
         <v>65</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
         <v>2.44</v>
@@ -2712,49 +2712,49 @@
         <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V12" t="n">
         <v>1.47</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
         <v>23</v>
@@ -2763,22 +2763,22 @@
         <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
         <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>16.5</v>
@@ -2790,7 +2790,7 @@
         <v>34</v>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
@@ -2799,13 +2799,13 @@
         <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>13</v>
@@ -2814,7 +2814,7 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
@@ -2829,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -2838,29 +2838,29 @@
         <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB12" t="n">
         <v>29</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF12" t="n">
         <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="n">
         <v>4.8</v>
@@ -2918,10 +2918,10 @@
         <v>6.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
         <v>1.49</v>
@@ -2930,10 +2930,10 @@
         <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
         <v>2.44</v>
@@ -2942,7 +2942,7 @@
         <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X13" t="n">
         <v>32</v>
@@ -3044,17 +3044,17 @@
         <v>21</v>
       </c>
       <c r="BE13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BF13" t="n">
         <v>5.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="H14" t="n">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>1.57</v>
@@ -3115,13 +3115,13 @@
         <v>1.52</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S14" t="n">
         <v>5.3</v>
@@ -3130,55 +3130,55 @@
         <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB14" t="n">
         <v>9</v>
       </c>
-      <c r="Y14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AI14" t="n">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
@@ -3190,65 +3190,65 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU14" t="n">
         <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AW14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB14" t="n">
         <v>20</v>
       </c>
-      <c r="AX14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY14" t="n">
+      <c r="BC14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>13</v>
-      </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG14" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
         <v>3.65</v>
@@ -3303,7 +3303,7 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>1.33</v>
@@ -3321,7 +3321,7 @@
         <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
         <v>2.14</v>
@@ -3342,10 +3342,10 @@
         <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
         <v>8</v>
@@ -3357,7 +3357,7 @@
         <v>40</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>11.5</v>
@@ -3381,7 +3381,7 @@
         <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO15" t="n">
         <v>38</v>
@@ -3399,7 +3399,7 @@
         <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
@@ -3420,29 +3420,29 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE15" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="BF15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
         <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="H16" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
         <v>3.15</v>
@@ -3488,7 +3488,7 @@
         <v>3.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.29</v>
@@ -3497,7 +3497,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
@@ -3515,7 +3515,7 @@
         <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.36</v>
@@ -3524,7 +3524,7 @@
         <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X16" t="n">
         <v>30</v>
@@ -3539,7 +3539,7 @@
         <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AC16" t="n">
         <v>9.199999999999999</v>
@@ -3596,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>11.5</v>
@@ -3626,7 +3626,7 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>13.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H17" t="n">
         <v>2.28</v>
@@ -3700,7 +3700,7 @@
         <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3709,16 +3709,16 @@
         <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
         <v>16.5</v>
@@ -3739,7 +3739,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>28</v>
@@ -3766,7 +3766,7 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
         <v>40</v>
@@ -3817,20 +3817,20 @@
         <v>16</v>
       </c>
       <c r="BD17" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BG17" t="n">
         <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -3867,73 +3867,73 @@
         <v>5.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="T18" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="W18" t="n">
         <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC18" t="n">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>65</v>
@@ -3945,10 +3945,10 @@
         <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ18" t="n">
         <v>1000</v>
@@ -3957,7 +3957,7 @@
         <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="AP18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AS18" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV18" t="n">
         <v>6.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>14</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.42</v>
+        <v>10.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.66</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>3.3</v>
@@ -4079,7 +4079,7 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
         <v>1.49</v>
@@ -4091,34 +4091,34 @@
         <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
         <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
-        <v>270</v>
+        <v>75</v>
       </c>
       <c r="AB19" t="n">
         <v>8</v>
@@ -4130,61 +4130,61 @@
         <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>95</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AP19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS19" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4193,32 +4193,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BC19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BD19" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE19" t="n">
         <v>29</v>
       </c>
       <c r="BF19" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H20" t="n">
         <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
         <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4276,7 +4276,7 @@
         <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
@@ -4285,22 +4285,22 @@
         <v>1.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
         <v>3.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
         <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X20" t="n">
         <v>15.5</v>
@@ -4324,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
@@ -4354,10 +4354,10 @@
         <v>15</v>
       </c>
       <c r="AO20" t="n">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="AP20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
         <v>13</v>
@@ -4366,10 +4366,10 @@
         <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20" t="n">
         <v>7.4</v>
@@ -4378,10 +4378,10 @@
         <v>14.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>9.6</v>
@@ -4390,7 +4390,7 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
         <v>22</v>
@@ -4402,17 +4402,17 @@
         <v>30</v>
       </c>
       <c r="BE20" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BF20" t="n">
         <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="G21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="H21" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>500</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AB21" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT21" t="n">
         <v>13.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN21" t="n">
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF21" t="n">
         <v>27</v>
       </c>
-      <c r="AO21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>16</v>
-      </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="G22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -4655,16 +4655,16 @@
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P22" t="n">
         <v>1.93</v>
@@ -4673,28 +4673,28 @@
         <v>2.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
         <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
         <v>36</v>
@@ -4706,46 +4706,46 @@
         <v>8.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22" t="n">
         <v>18.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
         <v>70</v>
       </c>
       <c r="AJ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="n">
         <v>20</v>
       </c>
-      <c r="AK22" t="n">
-        <v>21</v>
-      </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
         <v>110</v>
       </c>
       <c r="AN22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>15</v>
@@ -4754,7 +4754,7 @@
         <v>32</v>
       </c>
       <c r="AS22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
@@ -4763,22 +4763,22 @@
         <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB22" t="n">
         <v>19.5</v>
@@ -4787,20 +4787,20 @@
         <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BF22" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -4837,46 +4837,46 @@
         <v>2.06</v>
       </c>
       <c r="H23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
         <v>4.3</v>
       </c>
-      <c r="I23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.6</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
@@ -4885,10 +4885,10 @@
         <v>1.94</v>
       </c>
       <c r="X23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z23" t="n">
         <v>32</v>
@@ -4897,16 +4897,16 @@
         <v>110</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
         <v>11.5</v>
@@ -4915,7 +4915,7 @@
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI23" t="n">
         <v>80</v>
@@ -4924,25 +4924,25 @@
         <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
@@ -4951,7 +4951,7 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>7.2</v>
@@ -4960,7 +4960,7 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AX23" t="n">
         <v>10.5</v>
@@ -4969,32 +4969,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE23" t="n">
         <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="G24" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.31</v>
@@ -5049,34 +5049,34 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.48</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.38</v>
       </c>
       <c r="X24" t="n">
         <v>90</v>
@@ -5088,10 +5088,10 @@
         <v>970</v>
       </c>
       <c r="AA24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
         <v>11.5</v>
@@ -5100,10 +5100,10 @@
         <v>970</v>
       </c>
       <c r="AE24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF24" t="n">
         <v>25</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>34</v>
       </c>
       <c r="AG24" t="n">
         <v>970</v>
@@ -5115,80 +5115,80 @@
         <v>36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AK24" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="n">
         <v>970</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AQ24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY24" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.8</v>
+        <v>11.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5231,22 +5231,22 @@
         <v>3.1</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
         <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
         <v>1.78</v>
@@ -5258,13 +5258,13 @@
         <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
         <v>1.9</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
         <v>1.47</v>
@@ -5294,13 +5294,13 @@
         <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>18</v>
@@ -5312,7 +5312,7 @@
         <v>38</v>
       </c>
       <c r="AK25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL25" t="n">
         <v>46</v>
@@ -5333,10 +5333,10 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT25" t="n">
         <v>9</v>
@@ -5360,7 +5360,7 @@
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB25" t="n">
         <v>36</v>
@@ -5369,20 +5369,20 @@
         <v>29</v>
       </c>
       <c r="BD25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE25" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="BF25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BG25" t="n">
         <v>38</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5443,13 +5443,13 @@
         <v>1.35</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q26" t="n">
         <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
         <v>3.75</v>
@@ -5479,7 +5479,7 @@
         <v>85</v>
       </c>
       <c r="AB26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC26" t="n">
         <v>8</v>
@@ -5488,13 +5488,13 @@
         <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
         <v>26</v>
       </c>
       <c r="AG26" t="n">
-        <v>500</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
         <v>25</v>
@@ -5503,7 +5503,7 @@
         <v>200</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
         <v>1000</v>
@@ -5527,7 +5527,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS26" t="n">
         <v>13</v>
@@ -5542,10 +5542,10 @@
         <v>9.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AY26" t="n">
         <v>13.5</v>
@@ -5554,10 +5554,10 @@
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5566,17 +5566,17 @@
         <v>11.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
         <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>2.26</v>
       </c>
       <c r="G27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
         <v>3.75</v>
@@ -5634,19 +5634,19 @@
         <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R27" t="n">
         <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
         <v>1.95</v>
@@ -5658,7 +5658,7 @@
         <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
@@ -5679,31 +5679,31 @@
         <v>7.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AF27" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AI27" t="n">
         <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AK27" t="n">
         <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
         <v>580</v>
@@ -5721,10 +5721,10 @@
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
         <v>7.4</v>
@@ -5736,7 +5736,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5745,10 +5745,10 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
         <v>27</v>
@@ -5757,20 +5757,20 @@
         <v>24</v>
       </c>
       <c r="BD27" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BE27" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BF27" t="n">
         <v>21</v>
       </c>
       <c r="BG27" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G28" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="H28" t="n">
         <v>6.8</v>
@@ -5813,55 +5813,55 @@
         <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R28" t="n">
         <v>1.2</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="X28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="Z28" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
@@ -5873,37 +5873,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AE28" t="n">
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG28" t="n">
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
@@ -5912,7 +5912,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR28" t="n">
         <v>22</v>
@@ -5921,7 +5921,7 @@
         <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
@@ -5930,7 +5930,7 @@
         <v>17.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX28" t="n">
         <v>7.2</v>
@@ -5942,16 +5942,16 @@
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>10.5</v>
+        <v>26</v>
       </c>
       <c r="BE28" t="n">
         <v>10.5</v>
@@ -5960,11 +5960,11 @@
         <v>14</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G29" t="n">
         <v>4.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
         <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -6022,16 +6022,16 @@
         <v>4.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
         <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
         <v>3.25</v>
@@ -6049,49 +6049,49 @@
         <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y29" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB29" t="n">
         <v>500</v>
       </c>
-      <c r="AA29" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD29" t="n">
         <v>36</v>
       </c>
       <c r="AE29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF29" t="n">
         <v>500</v>
       </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG29" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AH29" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL29" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
@@ -6115,13 +6115,13 @@
         <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AW29" t="n">
         <v>10.5</v>
@@ -6136,19 +6136,19 @@
         <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB29" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD29" t="n">
         <v>23</v>
       </c>
       <c r="BE29" t="n">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
         <v>9.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -6195,16 +6195,16 @@
         <v>5.7</v>
       </c>
       <c r="H30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I30" t="n">
         <v>1.91</v>
       </c>
       <c r="J30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
@@ -6216,7 +6216,7 @@
         <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
         <v>1.79</v>
@@ -6228,7 +6228,7 @@
         <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T30" t="n">
         <v>1.96</v>
@@ -6237,7 +6237,7 @@
         <v>1.92</v>
       </c>
       <c r="V30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="W30" t="n">
         <v>1.21</v>
@@ -6246,7 +6246,7 @@
         <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z30" t="n">
         <v>11</v>
@@ -6273,25 +6273,25 @@
         <v>21</v>
       </c>
       <c r="AH30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK30" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL30" t="n">
         <v>90</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>95</v>
       </c>
       <c r="AM30" t="n">
         <v>150</v>
       </c>
       <c r="AN30" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="AO30" t="n">
         <v>15</v>
@@ -6333,16 +6333,16 @@
         <v>20</v>
       </c>
       <c r="BB30" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BC30" t="n">
         <v>65</v>
       </c>
       <c r="BD30" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BF30" t="n">
         <v>75</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.9</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.05</v>
@@ -6425,10 +6425,10 @@
         <v>2.74</v>
       </c>
       <c r="T31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V31" t="n">
         <v>1.53</v>
@@ -6440,7 +6440,7 @@
         <v>21</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -6464,7 +6464,7 @@
         <v>18.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
         <v>14.5</v>
@@ -6476,7 +6476,7 @@
         <v>36</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
         <v>29</v>
@@ -6491,16 +6491,16 @@
         <v>17.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT31" t="n">
         <v>13.5</v>
@@ -6518,7 +6518,7 @@
         <v>17.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>14</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.73</v>
       </c>
       <c r="G32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
         <v>4.5</v>
@@ -6589,7 +6589,7 @@
         <v>5.1</v>
       </c>
       <c r="J32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K32" t="n">
         <v>4.6</v>
@@ -6607,55 +6607,55 @@
         <v>1.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q32" t="n">
         <v>1.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U32" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V32" t="n">
         <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X32" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Y32" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z32" t="n">
         <v>42</v>
       </c>
-      <c r="Z32" t="n">
-        <v>140</v>
-      </c>
       <c r="AA32" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC32" t="n">
         <v>11</v>
       </c>
       <c r="AD32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AF32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
@@ -6664,25 +6664,25 @@
         <v>17.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="AJ32" t="n">
         <v>20</v>
       </c>
       <c r="AK32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL32" t="n">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="AM32" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
         <v>8</v>
       </c>
       <c r="AO32" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AP32" t="n">
         <v>20</v>
@@ -6691,10 +6691,10 @@
         <v>19</v>
       </c>
       <c r="AR32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT32" t="n">
         <v>10.5</v>
@@ -6703,7 +6703,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW32" t="n">
         <v>22</v>
@@ -6715,10 +6715,10 @@
         <v>9</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="BB32" t="n">
         <v>16.5</v>
@@ -6730,7 +6730,7 @@
         <v>12</v>
       </c>
       <c r="BE32" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BF32" t="n">
         <v>6.8</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I33" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.2</v>
       </c>
       <c r="J33" t="n">
         <v>3.5</v>
@@ -6801,10 +6801,10 @@
         <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R33" t="n">
         <v>1.41</v>
@@ -6819,7 +6819,7 @@
         <v>2.3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W33" t="n">
         <v>1.66</v>
@@ -6873,7 +6873,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO33" t="n">
         <v>29</v>
@@ -6912,7 +6912,7 @@
         <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
         <v>30</v>
@@ -6924,17 +6924,17 @@
         <v>32</v>
       </c>
       <c r="BE33" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF33" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG33" t="n">
         <v>26</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G34" t="n">
         <v>1.26</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.27</v>
       </c>
       <c r="H34" t="n">
         <v>13.5</v>
@@ -6998,10 +6998,10 @@
         <v>3.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R34" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S34" t="n">
         <v>2.16</v>
@@ -7028,28 +7028,28 @@
         <v>130</v>
       </c>
       <c r="AA34" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="AB34" t="n">
         <v>12.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD34" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AE34" t="n">
         <v>190</v>
       </c>
       <c r="AF34" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG34" t="n">
         <v>11</v>
       </c>
       <c r="AH34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI34" t="n">
         <v>130</v>
@@ -7064,13 +7064,13 @@
         <v>32</v>
       </c>
       <c r="AM34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AO34" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AP34" t="n">
         <v>34</v>
@@ -7094,10 +7094,10 @@
         <v>42</v>
       </c>
       <c r="AW34" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY34" t="n">
         <v>10.5</v>
@@ -7124,11 +7124,11 @@
         <v>3.45</v>
       </c>
       <c r="BG34" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>4.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H35" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I35" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J35" t="n">
         <v>3.5</v>
       </c>
       <c r="K35" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
         <v>1.52</v>
@@ -7192,7 +7192,7 @@
         <v>1.67</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R35" t="n">
         <v>1.25</v>
@@ -7237,7 +7237,7 @@
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AG35" t="n">
         <v>1000</v>
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW35" t="n">
         <v>18.5</v>
@@ -7294,25 +7294,25 @@
         <v>30</v>
       </c>
       <c r="AY35" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ35" t="n">
         <v>23</v>
       </c>
       <c r="BA35" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BB35" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BC35" t="n">
         <v>15</v>
       </c>
       <c r="BD35" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BE35" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="BF35" t="n">
         <v>15.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H36" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I36" t="n">
         <v>3.75</v>
@@ -7377,7 +7377,7 @@
         <v>1.16</v>
       </c>
       <c r="N36" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
         <v>1.67</v>
@@ -7389,22 +7389,22 @@
         <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S36" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U36" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V36" t="n">
         <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X36" t="n">
         <v>7.2</v>
@@ -7428,7 +7428,7 @@
         <v>17.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AF36" t="n">
         <v>16.5</v>
@@ -7473,7 +7473,7 @@
         <v>9</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU36" t="n">
         <v>6</v>
@@ -7482,7 +7482,7 @@
         <v>9</v>
       </c>
       <c r="AW36" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AX36" t="n">
         <v>13</v>
@@ -7494,29 +7494,29 @@
         <v>19.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BC36" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="BD36" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE36" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF36" t="n">
         <v>9.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -7547,170 +7547,170 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="G37" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="H37" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="I37" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K37" t="n">
         <v>4.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
         <v>1.02</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="O37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P37" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R37" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="S37" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T37" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="U37" t="n">
         <v>2.78</v>
       </c>
       <c r="V37" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W37" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y37" t="n">
         <v>24</v>
       </c>
       <c r="Z37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA37" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AB37" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC37" t="n">
         <v>11</v>
       </c>
       <c r="AD37" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF37" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH37" t="n">
         <v>15.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ37" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK37" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>25</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>21</v>
       </c>
-      <c r="AL37" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO37" t="n">
+      <c r="AR37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD37" t="n">
         <v>20</v>
       </c>
-      <c r="AP37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ37" t="n">
+      <c r="BE37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF37" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG37" t="n">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H38" t="n">
         <v>3.7</v>
@@ -7786,13 +7786,13 @@
         <v>1.87</v>
       </c>
       <c r="U38" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V38" t="n">
         <v>1.34</v>
       </c>
       <c r="W38" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X38" t="n">
         <v>19.5</v>
@@ -7810,10 +7810,10 @@
         <v>8.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
         <v>500</v>
@@ -7831,7 +7831,7 @@
         <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK38" t="n">
         <v>500</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AQ38" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR38" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.6</v>
+        <v>11</v>
       </c>
       <c r="AT38" t="n">
         <v>7.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV38" t="n">
         <v>9</v>
       </c>
       <c r="AW38" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AX38" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ38" t="n">
         <v>10.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC38" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG38" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
         <v>10.5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>5.4</v>
@@ -7959,28 +7959,28 @@
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
         <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T39" t="n">
         <v>2.6</v>
       </c>
       <c r="U39" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V39" t="n">
         <v>1.07</v>
@@ -8007,7 +8007,7 @@
         <v>13.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
@@ -8031,7 +8031,7 @@
         <v>19.5</v>
       </c>
       <c r="AL39" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -8067,10 +8067,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY39" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ39" t="n">
         <v>7.2</v>
@@ -8082,7 +8082,7 @@
         <v>5.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD39" t="n">
         <v>7.6</v>
@@ -8091,14 +8091,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BG39" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -8138,10 +8138,10 @@
         <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="K40" t="n">
         <v>11</v>
@@ -8171,10 +8171,10 @@
         <v>1.59</v>
       </c>
       <c r="T40" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U40" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V40" t="n">
         <v>1.05</v>
@@ -8195,7 +8195,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC40" t="n">
         <v>1000</v>
@@ -8207,7 +8207,7 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG40" t="n">
         <v>15.5</v>
@@ -8222,7 +8222,7 @@
         <v>12</v>
       </c>
       <c r="AK40" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL40" t="n">
         <v>30</v>
@@ -8237,62 +8237,62 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AQ40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV40" t="n">
         <v>1.92</v>
       </c>
-      <c r="AR40" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS40" t="n">
+      <c r="AW40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BA40" t="n">
         <v>1.95</v>
       </c>
-      <c r="AT40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BB40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC40" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="BF40" t="n">
         <v>2.12</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v>3.35</v>
       </c>
       <c r="I41" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -8371,7 +8371,7 @@
         <v>1.83</v>
       </c>
       <c r="V41" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W41" t="n">
         <v>1.61</v>
@@ -8392,7 +8392,7 @@
         <v>970</v>
       </c>
       <c r="AC41" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD41" t="n">
         <v>970</v>
@@ -8431,13 +8431,13 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ41" t="n">
         <v>8.6</v>
       </c>
       <c r="AR41" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AS41" t="n">
         <v>6.6</v>
@@ -8452,13 +8452,13 @@
         <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="AX41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AY41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ41" t="n">
         <v>5.8</v>
@@ -8470,7 +8470,7 @@
         <v>6.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BD41" t="n">
         <v>6.6</v>
@@ -8479,14 +8479,14 @@
         <v>7.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG41" t="n">
         <v>6.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-21 06:47:08</t>
+          <t>2026-04-21 09:02:28</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>5</v>
       </c>
       <c r="H42" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I42" t="n">
         <v>1.82</v>
@@ -8550,19 +8550,19 @@
         <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R42" t="n">
         <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T42" t="n">
         <v>1.79</v>
       </c>
       <c r="U42" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V42" t="n">
         <v>2.2</v>
@@ -8580,10 +8580,10 @@
         <v>11.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC42" t="n">
         <v>9.199999999999999</v>
@@ -8592,7 +8592,7 @@
         <v>10.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AF42" t="n">
         <v>42</v>
@@ -8601,34 +8601,34 @@
         <v>20</v>
       </c>
       <c r="AH42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ42" t="n">
         <v>1000</v>
       </c>
       <c r="AK42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL42" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AO42" t="n">
         <v>10.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>15.5</v>
+        <